--- a/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -558,7 +558,7 @@
         <v>19</v>
       </c>
       <c r="B2">
-        <v>73.76000000000001</v>
+        <v>73.759765625</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -566,7 +566,7 @@
         <v>20</v>
       </c>
       <c r="B3">
-        <v>61.56</v>
+        <v>61.56005859375</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -574,7 +574,7 @@
         <v>21</v>
       </c>
       <c r="B4">
-        <v>72.7</v>
+        <v>72.7001953125</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -582,7 +582,7 @@
         <v>22</v>
       </c>
       <c r="B5">
-        <v>53.66</v>
+        <v>53.659912109375</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -590,7 +590,7 @@
         <v>23</v>
       </c>
       <c r="B6">
-        <v>63.9</v>
+        <v>63.89990234375</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -598,7 +598,7 @@
         <v>24</v>
       </c>
       <c r="B7">
-        <v>57.45</v>
+        <v>57.449951171875</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -606,7 +606,7 @@
         <v>25</v>
       </c>
       <c r="B8">
-        <v>47.86</v>
+        <v>47.860107421875</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -614,7 +614,7 @@
         <v>26</v>
       </c>
       <c r="B9">
-        <v>62.56</v>
+        <v>62.56005859375</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -622,7 +622,7 @@
         <v>27</v>
       </c>
       <c r="B10">
-        <v>73.95999999999999</v>
+        <v>73.9599609375</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -630,7 +630,7 @@
         <v>28</v>
       </c>
       <c r="B11">
-        <v>84.26000000000001</v>
+        <v>84.259765625</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -638,7 +638,7 @@
         <v>29</v>
       </c>
       <c r="B12">
-        <v>64.56</v>
+        <v>64.56005859375</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -646,7 +646,7 @@
         <v>30</v>
       </c>
       <c r="B13">
-        <v>50.26</v>
+        <v>50.260009765625</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -654,7 +654,7 @@
         <v>31</v>
       </c>
       <c r="B14">
-        <v>64.56</v>
+        <v>64.56005859375</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -670,7 +670,7 @@
         <v>33</v>
       </c>
       <c r="B16">
-        <v>60.16</v>
+        <v>60.159912109375</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -678,7 +678,7 @@
         <v>34</v>
       </c>
       <c r="B17">
-        <v>61.66</v>
+        <v>61.659912109375</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -686,7 +686,7 @@
         <v>35</v>
       </c>
       <c r="B18">
-        <v>66.86</v>
+        <v>66.85986328125</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -694,7 +694,7 @@
         <v>36</v>
       </c>
       <c r="B19">
-        <v>58.96</v>
+        <v>58.9599609375</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -702,7 +702,7 @@
         <v>37</v>
       </c>
       <c r="B20">
-        <v>68.06</v>
+        <v>68.06005859375</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -710,7 +710,7 @@
         <v>38</v>
       </c>
       <c r="B21">
-        <v>51.26</v>
+        <v>51.260009765625</v>
       </c>
     </row>
     <row r="22" spans="1:2">

--- a/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="40">
   <si>
     <t>Rodada 1</t>
   </si>
@@ -560,6 +560,9 @@
       <c r="B2">
         <v>73.759765625</v>
       </c>
+      <c r="C2">
+        <v>53.9</v>
+      </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" s="1" t="s">
@@ -568,6 +571,9 @@
       <c r="B3">
         <v>61.56005859375</v>
       </c>
+      <c r="C3">
+        <v>41.7</v>
+      </c>
     </row>
     <row r="4" spans="1:20">
       <c r="A4" s="1" t="s">
@@ -576,6 +582,9 @@
       <c r="B4">
         <v>72.7001953125</v>
       </c>
+      <c r="C4">
+        <v>15.7</v>
+      </c>
     </row>
     <row r="5" spans="1:20">
       <c r="A5" s="1" t="s">
@@ -584,6 +593,9 @@
       <c r="B5">
         <v>53.659912109375</v>
       </c>
+      <c r="C5">
+        <v>49.8</v>
+      </c>
     </row>
     <row r="6" spans="1:20">
       <c r="A6" s="1" t="s">
@@ -592,6 +604,9 @@
       <c r="B6">
         <v>63.89990234375</v>
       </c>
+      <c r="C6">
+        <v>63.55</v>
+      </c>
     </row>
     <row r="7" spans="1:20">
       <c r="A7" s="1" t="s">
@@ -600,6 +615,9 @@
       <c r="B7">
         <v>57.449951171875</v>
       </c>
+      <c r="C7">
+        <v>35.75</v>
+      </c>
     </row>
     <row r="8" spans="1:20">
       <c r="A8" s="1" t="s">
@@ -608,6 +626,9 @@
       <c r="B8">
         <v>47.860107421875</v>
       </c>
+      <c r="C8">
+        <v>52.8</v>
+      </c>
     </row>
     <row r="9" spans="1:20">
       <c r="A9" s="1" t="s">
@@ -616,6 +637,9 @@
       <c r="B9">
         <v>62.56005859375</v>
       </c>
+      <c r="C9">
+        <v>55.9</v>
+      </c>
     </row>
     <row r="10" spans="1:20">
       <c r="A10" s="1" t="s">
@@ -624,6 +648,9 @@
       <c r="B10">
         <v>73.9599609375</v>
       </c>
+      <c r="C10">
+        <v>65.40000000000001</v>
+      </c>
     </row>
     <row r="11" spans="1:20">
       <c r="A11" s="1" t="s">
@@ -632,6 +659,9 @@
       <c r="B11">
         <v>84.259765625</v>
       </c>
+      <c r="C11">
+        <v>50.3</v>
+      </c>
     </row>
     <row r="12" spans="1:20">
       <c r="A12" s="1" t="s">
@@ -640,6 +670,9 @@
       <c r="B12">
         <v>64.56005859375</v>
       </c>
+      <c r="C12">
+        <v>74.25</v>
+      </c>
     </row>
     <row r="13" spans="1:20">
       <c r="A13" s="1" t="s">
@@ -648,6 +681,9 @@
       <c r="B13">
         <v>50.260009765625</v>
       </c>
+      <c r="C13">
+        <v>37.55</v>
+      </c>
     </row>
     <row r="14" spans="1:20">
       <c r="A14" s="1" t="s">
@@ -656,6 +692,9 @@
       <c r="B14">
         <v>64.56005859375</v>
       </c>
+      <c r="C14">
+        <v>62.25</v>
+      </c>
     </row>
     <row r="15" spans="1:20">
       <c r="A15" s="1" t="s">
@@ -664,6 +703,9 @@
       <c r="B15">
         <v>59.25</v>
       </c>
+      <c r="C15">
+        <v>37.8</v>
+      </c>
     </row>
     <row r="16" spans="1:20">
       <c r="A16" s="1" t="s">
@@ -672,53 +714,74 @@
       <c r="B16">
         <v>60.159912109375</v>
       </c>
-    </row>
-    <row r="17" spans="1:2">
+      <c r="C16">
+        <v>26.1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
       <c r="A17" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B17">
         <v>61.659912109375</v>
       </c>
-    </row>
-    <row r="18" spans="1:2">
+      <c r="C17">
+        <v>28.65</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
       <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B18">
         <v>66.85986328125</v>
       </c>
-    </row>
-    <row r="19" spans="1:2">
+      <c r="C18">
+        <v>50.35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
       <c r="A19" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B19">
         <v>58.9599609375</v>
       </c>
-    </row>
-    <row r="20" spans="1:2">
+      <c r="C19">
+        <v>38.8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
       <c r="A20" s="1" t="s">
         <v>37</v>
       </c>
       <c r="B20">
         <v>68.06005859375</v>
       </c>
-    </row>
-    <row r="21" spans="1:2">
+      <c r="C20">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
       <c r="A21" s="1" t="s">
         <v>38</v>
       </c>
       <c r="B21">
         <v>51.260009765625</v>
       </c>
-    </row>
-    <row r="22" spans="1:2">
+      <c r="C21">
+        <v>71.65000000000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
       <c r="A22" s="1" t="s">
         <v>39</v>
       </c>
       <c r="B22" t="s">
         <v>28</v>
+      </c>
+      <c r="C22" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -627,7 +627,7 @@
         <v>47.860107421875</v>
       </c>
       <c r="C8">
-        <v>52.8</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -671,7 +671,7 @@
         <v>64.56005859375</v>
       </c>
       <c r="C12">
-        <v>74.25</v>
+        <v>78.75</v>
       </c>
     </row>
     <row r="13" spans="1:20">

--- a/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -561,7 +561,7 @@
         <v>73.759765625</v>
       </c>
       <c r="C2">
-        <v>53.9</v>
+        <v>58.2</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -572,7 +572,7 @@
         <v>61.56005859375</v>
       </c>
       <c r="C3">
-        <v>41.7</v>
+        <v>59.81</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -583,7 +583,7 @@
         <v>72.7001953125</v>
       </c>
       <c r="C4">
-        <v>15.7</v>
+        <v>39.71</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -594,7 +594,7 @@
         <v>53.659912109375</v>
       </c>
       <c r="C5">
-        <v>49.8</v>
+        <v>61.41</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -605,7 +605,7 @@
         <v>63.89990234375</v>
       </c>
       <c r="C6">
-        <v>63.55</v>
+        <v>75.16</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -616,7 +616,7 @@
         <v>57.449951171875</v>
       </c>
       <c r="C7">
-        <v>35.75</v>
+        <v>49.15</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -627,7 +627,7 @@
         <v>47.860107421875</v>
       </c>
       <c r="C8">
-        <v>56.2</v>
+        <v>61.91</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -638,7 +638,7 @@
         <v>62.56005859375</v>
       </c>
       <c r="C9">
-        <v>55.9</v>
+        <v>74.01000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -649,7 +649,7 @@
         <v>73.9599609375</v>
       </c>
       <c r="C10">
-        <v>65.40000000000001</v>
+        <v>69.7</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -660,7 +660,7 @@
         <v>84.259765625</v>
       </c>
       <c r="C11">
-        <v>50.3</v>
+        <v>77.52</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -671,7 +671,7 @@
         <v>64.56005859375</v>
       </c>
       <c r="C12">
-        <v>78.75</v>
+        <v>82.75</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -682,7 +682,7 @@
         <v>50.260009765625</v>
       </c>
       <c r="C13">
-        <v>37.55</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -693,7 +693,7 @@
         <v>64.56005859375</v>
       </c>
       <c r="C14">
-        <v>62.25</v>
+        <v>66.25</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -704,7 +704,7 @@
         <v>59.25</v>
       </c>
       <c r="C15">
-        <v>37.8</v>
+        <v>53.11</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -715,7 +715,7 @@
         <v>60.159912109375</v>
       </c>
       <c r="C16">
-        <v>26.1</v>
+        <v>48.01</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -726,7 +726,7 @@
         <v>61.659912109375</v>
       </c>
       <c r="C17">
-        <v>28.65</v>
+        <v>35.15</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -737,7 +737,7 @@
         <v>66.85986328125</v>
       </c>
       <c r="C18">
-        <v>50.35</v>
+        <v>65.15000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -748,7 +748,7 @@
         <v>58.9599609375</v>
       </c>
       <c r="C19">
-        <v>38.8</v>
+        <v>56.91</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -759,7 +759,7 @@
         <v>68.06005859375</v>
       </c>
       <c r="C20">
-        <v>41.7</v>
+        <v>59.81</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -770,7 +770,7 @@
         <v>51.260009765625</v>
       </c>
       <c r="C21">
-        <v>71.65000000000001</v>
+        <v>74.75</v>
       </c>
     </row>
     <row r="22" spans="1:3">

--- a/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -561,7 +561,7 @@
         <v>73.759765625</v>
       </c>
       <c r="C2">
-        <v>58.2</v>
+        <v>81.26000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -572,7 +572,7 @@
         <v>61.56005859375</v>
       </c>
       <c r="C3">
-        <v>59.81</v>
+        <v>82.18000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -583,7 +583,7 @@
         <v>72.7001953125</v>
       </c>
       <c r="C4">
-        <v>39.71</v>
+        <v>64.58</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -594,7 +594,7 @@
         <v>53.659912109375</v>
       </c>
       <c r="C5">
-        <v>61.41</v>
+        <v>81.48</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -605,7 +605,7 @@
         <v>63.89990234375</v>
       </c>
       <c r="C6">
-        <v>75.16</v>
+        <v>92.78</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -616,7 +616,7 @@
         <v>57.449951171875</v>
       </c>
       <c r="C7">
-        <v>49.15</v>
+        <v>83.2</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -627,7 +627,7 @@
         <v>47.860107421875</v>
       </c>
       <c r="C8">
-        <v>61.91</v>
+        <v>72.18000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -638,7 +638,7 @@
         <v>62.56005859375</v>
       </c>
       <c r="C9">
-        <v>74.01000000000001</v>
+        <v>96.48</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -649,7 +649,7 @@
         <v>73.9599609375</v>
       </c>
       <c r="C10">
-        <v>69.7</v>
+        <v>92.76000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -660,7 +660,7 @@
         <v>84.259765625</v>
       </c>
       <c r="C11">
-        <v>77.52</v>
+        <v>82.61</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -671,7 +671,7 @@
         <v>64.56005859375</v>
       </c>
       <c r="C12">
-        <v>82.75</v>
+        <v>105.5</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -682,7 +682,7 @@
         <v>50.260009765625</v>
       </c>
       <c r="C13">
-        <v>48.25</v>
+        <v>57.55</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -693,7 +693,7 @@
         <v>64.56005859375</v>
       </c>
       <c r="C14">
-        <v>66.25</v>
+        <v>86.59999999999999</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -704,7 +704,7 @@
         <v>59.25</v>
       </c>
       <c r="C15">
-        <v>53.11</v>
+        <v>73.78</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -715,7 +715,7 @@
         <v>60.159912109375</v>
       </c>
       <c r="C16">
-        <v>48.01</v>
+        <v>64.58</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -726,7 +726,7 @@
         <v>61.659912109375</v>
       </c>
       <c r="C17">
-        <v>35.15</v>
+        <v>69.5</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -737,7 +737,7 @@
         <v>66.85986328125</v>
       </c>
       <c r="C18">
-        <v>65.15000000000001</v>
+        <v>92.7</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -748,7 +748,7 @@
         <v>58.9599609375</v>
       </c>
       <c r="C19">
-        <v>56.91</v>
+        <v>79.28</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -759,7 +759,7 @@
         <v>68.06005859375</v>
       </c>
       <c r="C20">
-        <v>59.81</v>
+        <v>82.18000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -770,7 +770,7 @@
         <v>51.260009765625</v>
       </c>
       <c r="C21">
-        <v>74.75</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="22" spans="1:3">

--- a/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -561,7 +561,7 @@
         <v>73.759765625</v>
       </c>
       <c r="C2">
-        <v>81.26000000000001</v>
+        <v>81.39990234375</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -572,7 +572,7 @@
         <v>61.56005859375</v>
       </c>
       <c r="C3">
-        <v>82.18000000000001</v>
+        <v>82.18017578125</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -583,7 +583,7 @@
         <v>72.7001953125</v>
       </c>
       <c r="C4">
-        <v>64.58</v>
+        <v>64.580078125</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -594,7 +594,7 @@
         <v>53.659912109375</v>
       </c>
       <c r="C5">
-        <v>81.48</v>
+        <v>81.47998046875</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -605,7 +605,7 @@
         <v>63.89990234375</v>
       </c>
       <c r="C6">
-        <v>92.78</v>
+        <v>92.77978515625</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -616,7 +616,7 @@
         <v>57.449951171875</v>
       </c>
       <c r="C7">
-        <v>83.2</v>
+        <v>83.2001953125</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -627,7 +627,7 @@
         <v>47.860107421875</v>
       </c>
       <c r="C8">
-        <v>72.18000000000001</v>
+        <v>72.18017578125</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -638,7 +638,7 @@
         <v>62.56005859375</v>
       </c>
       <c r="C9">
-        <v>96.48</v>
+        <v>96.47998046875</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -649,7 +649,7 @@
         <v>73.9599609375</v>
       </c>
       <c r="C10">
-        <v>92.76000000000001</v>
+        <v>92.89990234375</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -660,7 +660,7 @@
         <v>84.259765625</v>
       </c>
       <c r="C11">
-        <v>82.61</v>
+        <v>82.60986328125</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -682,7 +682,7 @@
         <v>50.260009765625</v>
       </c>
       <c r="C13">
-        <v>57.55</v>
+        <v>57.550048828125</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -693,7 +693,7 @@
         <v>64.56005859375</v>
       </c>
       <c r="C14">
-        <v>86.59999999999999</v>
+        <v>86.60009765625</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -704,7 +704,7 @@
         <v>59.25</v>
       </c>
       <c r="C15">
-        <v>73.78</v>
+        <v>73.77978515625</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -715,7 +715,7 @@
         <v>60.159912109375</v>
       </c>
       <c r="C16">
-        <v>64.58</v>
+        <v>64.580078125</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -737,7 +737,7 @@
         <v>66.85986328125</v>
       </c>
       <c r="C18">
-        <v>92.7</v>
+        <v>92.7001953125</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -748,7 +748,7 @@
         <v>58.9599609375</v>
       </c>
       <c r="C19">
-        <v>79.28</v>
+        <v>79.27978515625</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -759,7 +759,7 @@
         <v>68.06005859375</v>
       </c>
       <c r="C20">
-        <v>82.18000000000001</v>
+        <v>82.18017578125</v>
       </c>
     </row>
     <row r="21" spans="1:3">

--- a/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="40">
   <si>
     <t>Rodada 1</t>
   </si>
@@ -563,6 +563,9 @@
       <c r="C2">
         <v>81.39990234375</v>
       </c>
+      <c r="D2">
+        <v>40.57</v>
+      </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" s="1" t="s">
@@ -574,6 +577,9 @@
       <c r="C3">
         <v>82.18017578125</v>
       </c>
+      <c r="D3">
+        <v>45.17</v>
+      </c>
     </row>
     <row r="4" spans="1:20">
       <c r="A4" s="1" t="s">
@@ -585,6 +591,9 @@
       <c r="C4">
         <v>64.580078125</v>
       </c>
+      <c r="D4">
+        <v>58.4</v>
+      </c>
     </row>
     <row r="5" spans="1:20">
       <c r="A5" s="1" t="s">
@@ -596,6 +605,9 @@
       <c r="C5">
         <v>81.47998046875</v>
       </c>
+      <c r="D5">
+        <v>38.07</v>
+      </c>
     </row>
     <row r="6" spans="1:20">
       <c r="A6" s="1" t="s">
@@ -607,6 +619,9 @@
       <c r="C6">
         <v>92.77978515625</v>
       </c>
+      <c r="D6">
+        <v>40.6</v>
+      </c>
     </row>
     <row r="7" spans="1:20">
       <c r="A7" s="1" t="s">
@@ -618,6 +633,9 @@
       <c r="C7">
         <v>83.2001953125</v>
       </c>
+      <c r="D7">
+        <v>27.9</v>
+      </c>
     </row>
     <row r="8" spans="1:20">
       <c r="A8" s="1" t="s">
@@ -629,6 +647,9 @@
       <c r="C8">
         <v>72.18017578125</v>
       </c>
+      <c r="D8">
+        <v>62.8</v>
+      </c>
     </row>
     <row r="9" spans="1:20">
       <c r="A9" s="1" t="s">
@@ -640,6 +661,9 @@
       <c r="C9">
         <v>96.47998046875</v>
       </c>
+      <c r="D9">
+        <v>53.77</v>
+      </c>
     </row>
     <row r="10" spans="1:20">
       <c r="A10" s="1" t="s">
@@ -651,6 +675,9 @@
       <c r="C10">
         <v>92.89990234375</v>
       </c>
+      <c r="D10">
+        <v>47.57</v>
+      </c>
     </row>
     <row r="11" spans="1:20">
       <c r="A11" s="1" t="s">
@@ -662,6 +689,9 @@
       <c r="C11">
         <v>82.60986328125</v>
       </c>
+      <c r="D11">
+        <v>29.2</v>
+      </c>
     </row>
     <row r="12" spans="1:20">
       <c r="A12" s="1" t="s">
@@ -673,6 +703,9 @@
       <c r="C12">
         <v>105.5</v>
       </c>
+      <c r="D12">
+        <v>50.77</v>
+      </c>
     </row>
     <row r="13" spans="1:20">
       <c r="A13" s="1" t="s">
@@ -684,6 +717,9 @@
       <c r="C13">
         <v>57.550048828125</v>
       </c>
+      <c r="D13">
+        <v>28.49</v>
+      </c>
     </row>
     <row r="14" spans="1:20">
       <c r="A14" s="1" t="s">
@@ -695,6 +731,9 @@
       <c r="C14">
         <v>86.60009765625</v>
       </c>
+      <c r="D14">
+        <v>50.07</v>
+      </c>
     </row>
     <row r="15" spans="1:20">
       <c r="A15" s="1" t="s">
@@ -706,6 +745,9 @@
       <c r="C15">
         <v>73.77978515625</v>
       </c>
+      <c r="D15">
+        <v>54.27</v>
+      </c>
     </row>
     <row r="16" spans="1:20">
       <c r="A16" s="1" t="s">
@@ -717,8 +759,11 @@
       <c r="C16">
         <v>64.580078125</v>
       </c>
-    </row>
-    <row r="17" spans="1:3">
+      <c r="D16">
+        <v>57.47</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
       <c r="A17" s="1" t="s">
         <v>34</v>
       </c>
@@ -728,8 +773,11 @@
       <c r="C17">
         <v>69.5</v>
       </c>
-    </row>
-    <row r="18" spans="1:3">
+      <c r="D17">
+        <v>36.36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
       <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
@@ -739,8 +787,11 @@
       <c r="C18">
         <v>92.7001953125</v>
       </c>
-    </row>
-    <row r="19" spans="1:3">
+      <c r="D18">
+        <v>55.19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
       <c r="A19" s="1" t="s">
         <v>36</v>
       </c>
@@ -750,8 +801,11 @@
       <c r="C19">
         <v>79.27978515625</v>
       </c>
-    </row>
-    <row r="20" spans="1:3">
+      <c r="D19">
+        <v>45.77</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
       <c r="A20" s="1" t="s">
         <v>37</v>
       </c>
@@ -761,8 +815,11 @@
       <c r="C20">
         <v>82.18017578125</v>
       </c>
-    </row>
-    <row r="21" spans="1:3">
+      <c r="D20">
+        <v>45.17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
       <c r="A21" s="1" t="s">
         <v>38</v>
       </c>
@@ -772,8 +829,11 @@
       <c r="C21">
         <v>95.5</v>
       </c>
-    </row>
-    <row r="22" spans="1:3">
+      <c r="D21">
+        <v>57.27</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
       <c r="A22" s="1" t="s">
         <v>39</v>
       </c>
@@ -782,6 +842,9 @@
       </c>
       <c r="C22" t="s">
         <v>29</v>
+      </c>
+      <c r="D22" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -564,7 +564,7 @@
         <v>81.39990234375</v>
       </c>
       <c r="D2">
-        <v>40.57</v>
+        <v>80.56</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -578,7 +578,7 @@
         <v>82.18017578125</v>
       </c>
       <c r="D3">
-        <v>45.17</v>
+        <v>105.76</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -592,7 +592,7 @@
         <v>64.580078125</v>
       </c>
       <c r="D4">
-        <v>58.4</v>
+        <v>98.65000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -606,7 +606,7 @@
         <v>81.47998046875</v>
       </c>
       <c r="D5">
-        <v>38.07</v>
+        <v>78.45999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -620,7 +620,7 @@
         <v>92.77978515625</v>
       </c>
       <c r="D6">
-        <v>40.6</v>
+        <v>78.40000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -634,7 +634,7 @@
         <v>83.2001953125</v>
       </c>
       <c r="D7">
-        <v>27.9</v>
+        <v>70.8</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -648,7 +648,7 @@
         <v>72.18017578125</v>
       </c>
       <c r="D8">
-        <v>62.8</v>
+        <v>97.40000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -662,7 +662,7 @@
         <v>96.47998046875</v>
       </c>
       <c r="D9">
-        <v>53.77</v>
+        <v>87.45999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -676,7 +676,7 @@
         <v>92.89990234375</v>
       </c>
       <c r="D10">
-        <v>47.57</v>
+        <v>81.76000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -690,7 +690,7 @@
         <v>82.60986328125</v>
       </c>
       <c r="D11">
-        <v>29.2</v>
+        <v>81.25</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -704,7 +704,7 @@
         <v>105.5</v>
       </c>
       <c r="D12">
-        <v>50.77</v>
+        <v>80.36</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -718,7 +718,7 @@
         <v>57.550048828125</v>
       </c>
       <c r="D13">
-        <v>28.49</v>
+        <v>70.04000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -732,7 +732,7 @@
         <v>86.60009765625</v>
       </c>
       <c r="D14">
-        <v>50.07</v>
+        <v>69.66</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -746,7 +746,7 @@
         <v>73.77978515625</v>
       </c>
       <c r="D15">
-        <v>54.27</v>
+        <v>92.95999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -760,7 +760,7 @@
         <v>64.580078125</v>
       </c>
       <c r="D16">
-        <v>57.47</v>
+        <v>88.76000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -774,7 +774,7 @@
         <v>69.5</v>
       </c>
       <c r="D17">
-        <v>36.36</v>
+        <v>84.86</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -788,7 +788,7 @@
         <v>92.7001953125</v>
       </c>
       <c r="D18">
-        <v>55.19</v>
+        <v>73.23999999999999</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -802,7 +802,7 @@
         <v>79.27978515625</v>
       </c>
       <c r="D19">
-        <v>45.77</v>
+        <v>86.66</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -816,7 +816,7 @@
         <v>82.18017578125</v>
       </c>
       <c r="D20">
-        <v>45.17</v>
+        <v>105.76</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -830,7 +830,7 @@
         <v>95.5</v>
       </c>
       <c r="D21">
-        <v>57.27</v>
+        <v>60.36</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -844,7 +844,7 @@
         <v>29</v>
       </c>
       <c r="D22" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -564,7 +564,7 @@
         <v>81.39990234375</v>
       </c>
       <c r="D2">
-        <v>80.56</v>
+        <v>81.35986328125</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -578,7 +578,7 @@
         <v>82.18017578125</v>
       </c>
       <c r="D3">
-        <v>105.76</v>
+        <v>105.759765625</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -592,7 +592,7 @@
         <v>64.580078125</v>
       </c>
       <c r="D4">
-        <v>98.65000000000001</v>
+        <v>98.64990234375</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -606,7 +606,7 @@
         <v>81.47998046875</v>
       </c>
       <c r="D5">
-        <v>78.45999999999999</v>
+        <v>79.259765625</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -620,7 +620,7 @@
         <v>92.77978515625</v>
       </c>
       <c r="D6">
-        <v>78.40000000000001</v>
+        <v>78.39990234375</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -634,7 +634,7 @@
         <v>83.2001953125</v>
       </c>
       <c r="D7">
-        <v>70.8</v>
+        <v>70.7998046875</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -648,7 +648,7 @@
         <v>72.18017578125</v>
       </c>
       <c r="D8">
-        <v>97.40000000000001</v>
+        <v>97.39990234375</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -662,7 +662,7 @@
         <v>96.47998046875</v>
       </c>
       <c r="D9">
-        <v>87.45999999999999</v>
+        <v>87.4599609375</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -676,7 +676,7 @@
         <v>92.89990234375</v>
       </c>
       <c r="D10">
-        <v>81.76000000000001</v>
+        <v>81.759765625</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -704,7 +704,7 @@
         <v>105.5</v>
       </c>
       <c r="D12">
-        <v>80.36</v>
+        <v>81.16015625</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -718,7 +718,7 @@
         <v>57.550048828125</v>
       </c>
       <c r="D13">
-        <v>70.04000000000001</v>
+        <v>70.83984375</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -732,7 +732,7 @@
         <v>86.60009765625</v>
       </c>
       <c r="D14">
-        <v>69.66</v>
+        <v>70.35986328125</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -746,7 +746,7 @@
         <v>73.77978515625</v>
       </c>
       <c r="D15">
-        <v>92.95999999999999</v>
+        <v>93.759765625</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -760,7 +760,7 @@
         <v>64.580078125</v>
       </c>
       <c r="D16">
-        <v>88.76000000000001</v>
+        <v>88.759765625</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -774,7 +774,7 @@
         <v>69.5</v>
       </c>
       <c r="D17">
-        <v>84.86</v>
+        <v>83.64990234375</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -788,7 +788,7 @@
         <v>92.7001953125</v>
       </c>
       <c r="D18">
-        <v>73.23999999999999</v>
+        <v>72.740234375</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -802,7 +802,7 @@
         <v>79.27978515625</v>
       </c>
       <c r="D19">
-        <v>86.66</v>
+        <v>86.66015625</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -816,7 +816,7 @@
         <v>82.18017578125</v>
       </c>
       <c r="D20">
-        <v>105.76</v>
+        <v>105.759765625</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -830,7 +830,7 @@
         <v>95.5</v>
       </c>
       <c r="D21">
-        <v>60.36</v>
+        <v>61.159912109375</v>
       </c>
     </row>
     <row r="22" spans="1:4">

--- a/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="40">
   <si>
     <t>Rodada 1</t>
   </si>
@@ -566,6 +566,9 @@
       <c r="D2">
         <v>81.35986328125</v>
       </c>
+      <c r="E2">
+        <v>41.5</v>
+      </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" s="1" t="s">
@@ -580,6 +583,9 @@
       <c r="D3">
         <v>105.759765625</v>
       </c>
+      <c r="E3">
+        <v>43.8</v>
+      </c>
     </row>
     <row r="4" spans="1:20">
       <c r="A4" s="1" t="s">
@@ -594,6 +600,9 @@
       <c r="D4">
         <v>98.64990234375</v>
       </c>
+      <c r="E4">
+        <v>42.3</v>
+      </c>
     </row>
     <row r="5" spans="1:20">
       <c r="A5" s="1" t="s">
@@ -608,6 +617,9 @@
       <c r="D5">
         <v>79.259765625</v>
       </c>
+      <c r="E5">
+        <v>59.53</v>
+      </c>
     </row>
     <row r="6" spans="1:20">
       <c r="A6" s="1" t="s">
@@ -622,6 +634,9 @@
       <c r="D6">
         <v>78.39990234375</v>
       </c>
+      <c r="E6">
+        <v>51.7</v>
+      </c>
     </row>
     <row r="7" spans="1:20">
       <c r="A7" s="1" t="s">
@@ -636,6 +651,9 @@
       <c r="D7">
         <v>70.7998046875</v>
       </c>
+      <c r="E7">
+        <v>51.19</v>
+      </c>
     </row>
     <row r="8" spans="1:20">
       <c r="A8" s="1" t="s">
@@ -650,6 +668,9 @@
       <c r="D8">
         <v>97.39990234375</v>
       </c>
+      <c r="E8">
+        <v>65.55</v>
+      </c>
     </row>
     <row r="9" spans="1:20">
       <c r="A9" s="1" t="s">
@@ -664,6 +685,9 @@
       <c r="D9">
         <v>87.4599609375</v>
       </c>
+      <c r="E9">
+        <v>44.6</v>
+      </c>
     </row>
     <row r="10" spans="1:20">
       <c r="A10" s="1" t="s">
@@ -678,6 +702,9 @@
       <c r="D10">
         <v>81.759765625</v>
       </c>
+      <c r="E10">
+        <v>25.3</v>
+      </c>
     </row>
     <row r="11" spans="1:20">
       <c r="A11" s="1" t="s">
@@ -692,6 +719,9 @@
       <c r="D11">
         <v>81.25</v>
       </c>
+      <c r="E11">
+        <v>18.4</v>
+      </c>
     </row>
     <row r="12" spans="1:20">
       <c r="A12" s="1" t="s">
@@ -706,6 +736,9 @@
       <c r="D12">
         <v>81.16015625</v>
       </c>
+      <c r="E12">
+        <v>47.25</v>
+      </c>
     </row>
     <row r="13" spans="1:20">
       <c r="A13" s="1" t="s">
@@ -720,6 +753,9 @@
       <c r="D13">
         <v>70.83984375</v>
       </c>
+      <c r="E13">
+        <v>28.33</v>
+      </c>
     </row>
     <row r="14" spans="1:20">
       <c r="A14" s="1" t="s">
@@ -734,6 +770,9 @@
       <c r="D14">
         <v>70.35986328125</v>
       </c>
+      <c r="E14">
+        <v>32.3</v>
+      </c>
     </row>
     <row r="15" spans="1:20">
       <c r="A15" s="1" t="s">
@@ -748,6 +787,9 @@
       <c r="D15">
         <v>93.759765625</v>
       </c>
+      <c r="E15">
+        <v>44.07</v>
+      </c>
     </row>
     <row r="16" spans="1:20">
       <c r="A16" s="1" t="s">
@@ -762,8 +804,11 @@
       <c r="D16">
         <v>88.759765625</v>
       </c>
-    </row>
-    <row r="17" spans="1:4">
+      <c r="E16">
+        <v>58.2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" s="1" t="s">
         <v>34</v>
       </c>
@@ -776,8 +821,11 @@
       <c r="D17">
         <v>83.64990234375</v>
       </c>
-    </row>
-    <row r="18" spans="1:4">
+      <c r="E17">
+        <v>46.53</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
@@ -790,8 +838,11 @@
       <c r="D18">
         <v>72.740234375</v>
       </c>
-    </row>
-    <row r="19" spans="1:4">
+      <c r="E18">
+        <v>48.89</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19" s="1" t="s">
         <v>36</v>
       </c>
@@ -804,8 +855,11 @@
       <c r="D19">
         <v>86.66015625</v>
       </c>
-    </row>
-    <row r="20" spans="1:4">
+      <c r="E19">
+        <v>70.40000000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20" s="1" t="s">
         <v>37</v>
       </c>
@@ -818,8 +872,11 @@
       <c r="D20">
         <v>105.759765625</v>
       </c>
-    </row>
-    <row r="21" spans="1:4">
+      <c r="E20">
+        <v>43.8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21" s="1" t="s">
         <v>38</v>
       </c>
@@ -832,8 +889,11 @@
       <c r="D21">
         <v>61.159912109375</v>
       </c>
-    </row>
-    <row r="22" spans="1:4">
+      <c r="E21">
+        <v>43.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22" s="1" t="s">
         <v>39</v>
       </c>
@@ -845,6 +905,9 @@
       </c>
       <c r="D22" t="s">
         <v>20</v>
+      </c>
+      <c r="E22" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -567,7 +567,7 @@
         <v>81.35986328125</v>
       </c>
       <c r="E2">
-        <v>41.5</v>
+        <v>45.85</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -584,7 +584,7 @@
         <v>105.759765625</v>
       </c>
       <c r="E3">
-        <v>43.8</v>
+        <v>46.65</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -601,7 +601,7 @@
         <v>98.64990234375</v>
       </c>
       <c r="E4">
-        <v>42.3</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -618,7 +618,7 @@
         <v>79.259765625</v>
       </c>
       <c r="E5">
-        <v>59.53</v>
+        <v>68.73</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -635,7 +635,7 @@
         <v>78.39990234375</v>
       </c>
       <c r="E6">
-        <v>51.7</v>
+        <v>64.05</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -652,7 +652,7 @@
         <v>70.7998046875</v>
       </c>
       <c r="E7">
-        <v>51.19</v>
+        <v>67.26000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -669,7 +669,7 @@
         <v>97.39990234375</v>
       </c>
       <c r="E8">
-        <v>65.55</v>
+        <v>81.65000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -686,7 +686,7 @@
         <v>87.4599609375</v>
       </c>
       <c r="E9">
-        <v>44.6</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -703,7 +703,7 @@
         <v>81.759765625</v>
       </c>
       <c r="E10">
-        <v>25.3</v>
+        <v>31.15</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -720,7 +720,7 @@
         <v>81.25</v>
       </c>
       <c r="E11">
-        <v>18.4</v>
+        <v>22.15</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -737,7 +737,7 @@
         <v>81.16015625</v>
       </c>
       <c r="E12">
-        <v>47.25</v>
+        <v>47.55</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -754,7 +754,7 @@
         <v>70.83984375</v>
       </c>
       <c r="E13">
-        <v>28.33</v>
+        <v>27.43</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -771,7 +771,7 @@
         <v>70.35986328125</v>
       </c>
       <c r="E14">
-        <v>32.3</v>
+        <v>35.6</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -788,7 +788,7 @@
         <v>93.759765625</v>
       </c>
       <c r="E15">
-        <v>44.07</v>
+        <v>47.58</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -805,7 +805,7 @@
         <v>88.759765625</v>
       </c>
       <c r="E16">
-        <v>58.2</v>
+        <v>92.05</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -822,7 +822,7 @@
         <v>83.64990234375</v>
       </c>
       <c r="E17">
-        <v>46.53</v>
+        <v>51.73</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -839,7 +839,7 @@
         <v>72.740234375</v>
       </c>
       <c r="E18">
-        <v>48.89</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -856,7 +856,7 @@
         <v>86.66015625</v>
       </c>
       <c r="E19">
-        <v>70.40000000000001</v>
+        <v>78.66</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -873,7 +873,7 @@
         <v>105.759765625</v>
       </c>
       <c r="E20">
-        <v>43.8</v>
+        <v>46.65</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -890,7 +890,7 @@
         <v>61.159912109375</v>
       </c>
       <c r="E21">
-        <v>43.5</v>
+        <v>57.05</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -907,7 +907,7 @@
         <v>20</v>
       </c>
       <c r="E22" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -567,7 +567,7 @@
         <v>81.35986328125</v>
       </c>
       <c r="E2">
-        <v>45.85</v>
+        <v>65.05</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -584,7 +584,7 @@
         <v>105.759765625</v>
       </c>
       <c r="E3">
-        <v>46.65</v>
+        <v>65.15000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -601,7 +601,7 @@
         <v>98.64990234375</v>
       </c>
       <c r="E4">
-        <v>38.5</v>
+        <v>85.48</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -618,7 +618,7 @@
         <v>79.259765625</v>
       </c>
       <c r="E5">
-        <v>68.73</v>
+        <v>86.43000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -635,7 +635,7 @@
         <v>78.39990234375</v>
       </c>
       <c r="E6">
-        <v>64.05</v>
+        <v>87.65000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -652,7 +652,7 @@
         <v>70.7998046875</v>
       </c>
       <c r="E7">
-        <v>67.26000000000001</v>
+        <v>77.26000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -686,7 +686,7 @@
         <v>87.4599609375</v>
       </c>
       <c r="E9">
-        <v>58</v>
+        <v>81.43000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -703,7 +703,7 @@
         <v>81.759765625</v>
       </c>
       <c r="E10">
-        <v>31.15</v>
+        <v>53.25</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -720,7 +720,7 @@
         <v>81.25</v>
       </c>
       <c r="E11">
-        <v>22.15</v>
+        <v>45.65</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -737,7 +737,7 @@
         <v>81.16015625</v>
       </c>
       <c r="E12">
-        <v>47.55</v>
+        <v>66.75</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -771,7 +771,7 @@
         <v>70.35986328125</v>
       </c>
       <c r="E14">
-        <v>35.6</v>
+        <v>34.9</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -788,7 +788,7 @@
         <v>93.759765625</v>
       </c>
       <c r="E15">
-        <v>47.58</v>
+        <v>51.93</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -805,7 +805,7 @@
         <v>88.759765625</v>
       </c>
       <c r="E16">
-        <v>92.05</v>
+        <v>109.75</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -839,7 +839,7 @@
         <v>72.740234375</v>
       </c>
       <c r="E18">
-        <v>45.94</v>
+        <v>50.59</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -856,7 +856,7 @@
         <v>86.66015625</v>
       </c>
       <c r="E19">
-        <v>78.66</v>
+        <v>80.36</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -873,7 +873,7 @@
         <v>105.759765625</v>
       </c>
       <c r="E20">
-        <v>46.65</v>
+        <v>65.15000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -890,7 +890,7 @@
         <v>61.159912109375</v>
       </c>
       <c r="E21">
-        <v>57.05</v>
+        <v>67.75</v>
       </c>
     </row>
     <row r="22" spans="1:5">

--- a/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -567,7 +567,7 @@
         <v>81.35986328125</v>
       </c>
       <c r="E2">
-        <v>65.05</v>
+        <v>65.0498046875</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -584,7 +584,7 @@
         <v>105.759765625</v>
       </c>
       <c r="E3">
-        <v>65.15000000000001</v>
+        <v>65.14990234375</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -601,7 +601,7 @@
         <v>98.64990234375</v>
       </c>
       <c r="E4">
-        <v>85.48</v>
+        <v>85.47998046875</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -618,7 +618,7 @@
         <v>79.259765625</v>
       </c>
       <c r="E5">
-        <v>86.43000000000001</v>
+        <v>86.43017578125</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -635,7 +635,7 @@
         <v>78.39990234375</v>
       </c>
       <c r="E6">
-        <v>87.65000000000001</v>
+        <v>87.64990234375</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -652,7 +652,7 @@
         <v>70.7998046875</v>
       </c>
       <c r="E7">
-        <v>77.26000000000001</v>
+        <v>77.259765625</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -669,7 +669,7 @@
         <v>97.39990234375</v>
       </c>
       <c r="E8">
-        <v>81.65000000000001</v>
+        <v>81.64990234375</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -686,7 +686,7 @@
         <v>87.4599609375</v>
       </c>
       <c r="E9">
-        <v>81.43000000000001</v>
+        <v>81.43017578125</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -720,7 +720,7 @@
         <v>81.25</v>
       </c>
       <c r="E11">
-        <v>45.65</v>
+        <v>45.64990234375</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -754,7 +754,7 @@
         <v>70.83984375</v>
       </c>
       <c r="E13">
-        <v>27.43</v>
+        <v>27.4300537109375</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -771,7 +771,7 @@
         <v>70.35986328125</v>
       </c>
       <c r="E14">
-        <v>34.9</v>
+        <v>34.89990234375</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -788,7 +788,7 @@
         <v>93.759765625</v>
       </c>
       <c r="E15">
-        <v>51.93</v>
+        <v>51.929931640625</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -822,7 +822,7 @@
         <v>83.64990234375</v>
       </c>
       <c r="E17">
-        <v>51.73</v>
+        <v>51.72998046875</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -839,7 +839,7 @@
         <v>72.740234375</v>
       </c>
       <c r="E18">
-        <v>50.59</v>
+        <v>50.590087890625</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -856,7 +856,7 @@
         <v>86.66015625</v>
       </c>
       <c r="E19">
-        <v>80.36</v>
+        <v>80.35986328125</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -873,7 +873,7 @@
         <v>105.759765625</v>
       </c>
       <c r="E20">
-        <v>65.15000000000001</v>
+        <v>65.14990234375</v>
       </c>
     </row>
     <row r="21" spans="1:5">

--- a/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="40">
   <si>
     <t>Rodada 1</t>
   </si>
@@ -569,6 +569,9 @@
       <c r="E2">
         <v>65.0498046875</v>
       </c>
+      <c r="F2">
+        <v>10.5</v>
+      </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" s="1" t="s">
@@ -586,6 +589,9 @@
       <c r="E3">
         <v>65.14990234375</v>
       </c>
+      <c r="F3">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="4" spans="1:20">
       <c r="A4" s="1" t="s">
@@ -603,6 +609,9 @@
       <c r="E4">
         <v>85.47998046875</v>
       </c>
+      <c r="F4">
+        <v>13.9</v>
+      </c>
     </row>
     <row r="5" spans="1:20">
       <c r="A5" s="1" t="s">
@@ -620,6 +629,9 @@
       <c r="E5">
         <v>86.43017578125</v>
       </c>
+      <c r="F5">
+        <v>25.7</v>
+      </c>
     </row>
     <row r="6" spans="1:20">
       <c r="A6" s="1" t="s">
@@ -637,6 +649,9 @@
       <c r="E6">
         <v>87.64990234375</v>
       </c>
+      <c r="F6">
+        <v>10.5</v>
+      </c>
     </row>
     <row r="7" spans="1:20">
       <c r="A7" s="1" t="s">
@@ -654,6 +669,9 @@
       <c r="E7">
         <v>77.259765625</v>
       </c>
+      <c r="F7">
+        <v>20.17</v>
+      </c>
     </row>
     <row r="8" spans="1:20">
       <c r="A8" s="1" t="s">
@@ -671,6 +689,9 @@
       <c r="E8">
         <v>81.64990234375</v>
       </c>
+      <c r="F8">
+        <v>13.8</v>
+      </c>
     </row>
     <row r="9" spans="1:20">
       <c r="A9" s="1" t="s">
@@ -688,6 +709,9 @@
       <c r="E9">
         <v>81.43017578125</v>
       </c>
+      <c r="F9">
+        <v>11.7</v>
+      </c>
     </row>
     <row r="10" spans="1:20">
       <c r="A10" s="1" t="s">
@@ -705,6 +729,9 @@
       <c r="E10">
         <v>53.25</v>
       </c>
+      <c r="F10">
+        <v>20.9</v>
+      </c>
     </row>
     <row r="11" spans="1:20">
       <c r="A11" s="1" t="s">
@@ -722,6 +749,9 @@
       <c r="E11">
         <v>45.64990234375</v>
       </c>
+      <c r="F11">
+        <v>14.9</v>
+      </c>
     </row>
     <row r="12" spans="1:20">
       <c r="A12" s="1" t="s">
@@ -739,6 +769,9 @@
       <c r="E12">
         <v>66.75</v>
       </c>
+      <c r="F12">
+        <v>69.25</v>
+      </c>
     </row>
     <row r="13" spans="1:20">
       <c r="A13" s="1" t="s">
@@ -756,6 +789,9 @@
       <c r="E13">
         <v>27.4300537109375</v>
       </c>
+      <c r="F13">
+        <v>18.74</v>
+      </c>
     </row>
     <row r="14" spans="1:20">
       <c r="A14" s="1" t="s">
@@ -773,6 +809,9 @@
       <c r="E14">
         <v>34.89990234375</v>
       </c>
+      <c r="F14">
+        <v>6</v>
+      </c>
     </row>
     <row r="15" spans="1:20">
       <c r="A15" s="1" t="s">
@@ -790,6 +829,9 @@
       <c r="E15">
         <v>51.929931640625</v>
       </c>
+      <c r="F15">
+        <v>22.2</v>
+      </c>
     </row>
     <row r="16" spans="1:20">
       <c r="A16" s="1" t="s">
@@ -807,8 +849,11 @@
       <c r="E16">
         <v>109.75</v>
       </c>
-    </row>
-    <row r="17" spans="1:5">
+      <c r="F16">
+        <v>20.6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" s="1" t="s">
         <v>34</v>
       </c>
@@ -824,8 +869,11 @@
       <c r="E17">
         <v>51.72998046875</v>
       </c>
-    </row>
-    <row r="18" spans="1:5">
+      <c r="F17">
+        <v>3.57</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
@@ -841,8 +889,11 @@
       <c r="E18">
         <v>50.590087890625</v>
       </c>
-    </row>
-    <row r="19" spans="1:5">
+      <c r="F18">
+        <v>20.7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19" s="1" t="s">
         <v>36</v>
       </c>
@@ -858,8 +909,11 @@
       <c r="E19">
         <v>80.35986328125</v>
       </c>
-    </row>
-    <row r="20" spans="1:5">
+      <c r="F19">
+        <v>11.3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20" s="1" t="s">
         <v>37</v>
       </c>
@@ -875,8 +929,11 @@
       <c r="E20">
         <v>65.14990234375</v>
       </c>
-    </row>
-    <row r="21" spans="1:5">
+      <c r="F20">
+        <v>22.3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21" s="1" t="s">
         <v>38</v>
       </c>
@@ -892,8 +949,11 @@
       <c r="E21">
         <v>67.75</v>
       </c>
-    </row>
-    <row r="22" spans="1:5">
+      <c r="F21">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22" s="1" t="s">
         <v>39</v>
       </c>
@@ -908,6 +968,9 @@
       </c>
       <c r="E22" t="s">
         <v>33</v>
+      </c>
+      <c r="F22" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -570,7 +570,7 @@
         <v>65.0498046875</v>
       </c>
       <c r="F2">
-        <v>10.5</v>
+        <v>103.1201171875</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -590,7 +590,7 @@
         <v>65.14990234375</v>
       </c>
       <c r="F3">
-        <v>22.3</v>
+        <v>93.02001953125</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -610,7 +610,7 @@
         <v>85.47998046875</v>
       </c>
       <c r="F4">
-        <v>13.9</v>
+        <v>84.60986328125</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -630,7 +630,7 @@
         <v>86.43017578125</v>
       </c>
       <c r="F5">
-        <v>25.7</v>
+        <v>86.419921875</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -650,7 +650,7 @@
         <v>87.64990234375</v>
       </c>
       <c r="F6">
-        <v>10.5</v>
+        <v>89.02001953125</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -670,7 +670,7 @@
         <v>77.259765625</v>
       </c>
       <c r="F7">
-        <v>20.17</v>
+        <v>69.3701171875</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -690,7 +690,7 @@
         <v>81.64990234375</v>
       </c>
       <c r="F8">
-        <v>13.8</v>
+        <v>84.81982421875</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -710,7 +710,7 @@
         <v>81.43017578125</v>
       </c>
       <c r="F9">
-        <v>11.7</v>
+        <v>85.669921875</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -730,7 +730,7 @@
         <v>53.25</v>
       </c>
       <c r="F10">
-        <v>20.9</v>
+        <v>83.31982421875</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -750,7 +750,7 @@
         <v>45.64990234375</v>
       </c>
       <c r="F11">
-        <v>14.9</v>
+        <v>72.27001953125</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -770,7 +770,7 @@
         <v>66.75</v>
       </c>
       <c r="F12">
-        <v>69.25</v>
+        <v>107.56005859375</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -790,7 +790,7 @@
         <v>27.4300537109375</v>
       </c>
       <c r="F13">
-        <v>18.74</v>
+        <v>39.340087890625</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -810,7 +810,7 @@
         <v>34.89990234375</v>
       </c>
       <c r="F14">
-        <v>6</v>
+        <v>88.6201171875</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -830,7 +830,7 @@
         <v>51.929931640625</v>
       </c>
       <c r="F15">
-        <v>22.2</v>
+        <v>74.77001953125</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -850,7 +850,7 @@
         <v>109.75</v>
       </c>
       <c r="F16">
-        <v>20.6</v>
+        <v>81.47021484375</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -870,7 +870,7 @@
         <v>51.72998046875</v>
       </c>
       <c r="F17">
-        <v>3.57</v>
+        <v>82.1298828125</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -890,7 +890,7 @@
         <v>50.590087890625</v>
       </c>
       <c r="F18">
-        <v>20.7</v>
+        <v>81.169921875</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -910,7 +910,7 @@
         <v>80.35986328125</v>
       </c>
       <c r="F19">
-        <v>11.3</v>
+        <v>98.52001953125</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -930,7 +930,7 @@
         <v>65.14990234375</v>
       </c>
       <c r="F20">
-        <v>22.3</v>
+        <v>93.02001953125</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -950,7 +950,7 @@
         <v>67.75</v>
       </c>
       <c r="F21">
-        <v>6</v>
+        <v>75.419921875</v>
       </c>
     </row>
     <row r="22" spans="1:6">

--- a/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="40">
   <si>
     <t>Rodada 1</t>
   </si>
@@ -572,6 +572,9 @@
       <c r="F2">
         <v>103.1201171875</v>
       </c>
+      <c r="G2">
+        <v>69.42</v>
+      </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" s="1" t="s">
@@ -592,6 +595,9 @@
       <c r="F3">
         <v>93.02001953125</v>
       </c>
+      <c r="G3">
+        <v>83</v>
+      </c>
     </row>
     <row r="4" spans="1:20">
       <c r="A4" s="1" t="s">
@@ -612,6 +618,9 @@
       <c r="F4">
         <v>84.60986328125</v>
       </c>
+      <c r="G4">
+        <v>72.11</v>
+      </c>
     </row>
     <row r="5" spans="1:20">
       <c r="A5" s="1" t="s">
@@ -632,6 +641,9 @@
       <c r="F5">
         <v>86.419921875</v>
       </c>
+      <c r="G5">
+        <v>47.39</v>
+      </c>
     </row>
     <row r="6" spans="1:20">
       <c r="A6" s="1" t="s">
@@ -652,6 +664,9 @@
       <c r="F6">
         <v>89.02001953125</v>
       </c>
+      <c r="G6">
+        <v>62.81</v>
+      </c>
     </row>
     <row r="7" spans="1:20">
       <c r="A7" s="1" t="s">
@@ -672,6 +687,9 @@
       <c r="F7">
         <v>69.3701171875</v>
       </c>
+      <c r="G7">
+        <v>52.2</v>
+      </c>
     </row>
     <row r="8" spans="1:20">
       <c r="A8" s="1" t="s">
@@ -692,6 +710,9 @@
       <c r="F8">
         <v>84.81982421875</v>
       </c>
+      <c r="G8">
+        <v>62.01</v>
+      </c>
     </row>
     <row r="9" spans="1:20">
       <c r="A9" s="1" t="s">
@@ -712,6 +733,9 @@
       <c r="F9">
         <v>85.669921875</v>
       </c>
+      <c r="G9">
+        <v>58.61</v>
+      </c>
     </row>
     <row r="10" spans="1:20">
       <c r="A10" s="1" t="s">
@@ -732,6 +756,9 @@
       <c r="F10">
         <v>83.31982421875</v>
       </c>
+      <c r="G10">
+        <v>54.81</v>
+      </c>
     </row>
     <row r="11" spans="1:20">
       <c r="A11" s="1" t="s">
@@ -752,6 +779,9 @@
       <c r="F11">
         <v>72.27001953125</v>
       </c>
+      <c r="G11">
+        <v>53.46</v>
+      </c>
     </row>
     <row r="12" spans="1:20">
       <c r="A12" s="1" t="s">
@@ -772,6 +802,9 @@
       <c r="F12">
         <v>107.56005859375</v>
       </c>
+      <c r="G12">
+        <v>71.61</v>
+      </c>
     </row>
     <row r="13" spans="1:20">
       <c r="A13" s="1" t="s">
@@ -792,6 +825,9 @@
       <c r="F13">
         <v>39.340087890625</v>
       </c>
+      <c r="G13">
+        <v>71.66</v>
+      </c>
     </row>
     <row r="14" spans="1:20">
       <c r="A14" s="1" t="s">
@@ -812,6 +848,9 @@
       <c r="F14">
         <v>88.6201171875</v>
       </c>
+      <c r="G14">
+        <v>58.89</v>
+      </c>
     </row>
     <row r="15" spans="1:20">
       <c r="A15" s="1" t="s">
@@ -832,6 +871,9 @@
       <c r="F15">
         <v>74.77001953125</v>
       </c>
+      <c r="G15">
+        <v>66.51000000000001</v>
+      </c>
     </row>
     <row r="16" spans="1:20">
       <c r="A16" s="1" t="s">
@@ -852,8 +894,11 @@
       <c r="F16">
         <v>81.47021484375</v>
       </c>
-    </row>
-    <row r="17" spans="1:6">
+      <c r="G16">
+        <v>56.4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
       <c r="A17" s="1" t="s">
         <v>34</v>
       </c>
@@ -872,8 +917,11 @@
       <c r="F17">
         <v>82.1298828125</v>
       </c>
-    </row>
-    <row r="18" spans="1:6">
+      <c r="G17">
+        <v>76.69</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
@@ -892,8 +940,11 @@
       <c r="F18">
         <v>81.169921875</v>
       </c>
-    </row>
-    <row r="19" spans="1:6">
+      <c r="G18">
+        <v>62.92</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19" s="1" t="s">
         <v>36</v>
       </c>
@@ -912,8 +963,11 @@
       <c r="F19">
         <v>98.52001953125</v>
       </c>
-    </row>
-    <row r="20" spans="1:6">
+      <c r="G19">
+        <v>77.41</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="A20" s="1" t="s">
         <v>37</v>
       </c>
@@ -932,8 +986,11 @@
       <c r="F20">
         <v>93.02001953125</v>
       </c>
-    </row>
-    <row r="21" spans="1:6">
+      <c r="G20">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
       <c r="A21" s="1" t="s">
         <v>38</v>
       </c>
@@ -952,8 +1009,11 @@
       <c r="F21">
         <v>75.419921875</v>
       </c>
-    </row>
-    <row r="22" spans="1:6">
+      <c r="G21">
+        <v>54.21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
       <c r="A22" s="1" t="s">
         <v>39</v>
       </c>
@@ -971,6 +1031,9 @@
       </c>
       <c r="F22" t="s">
         <v>29</v>
+      </c>
+      <c r="G22" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -573,7 +573,7 @@
         <v>103.1201171875</v>
       </c>
       <c r="G2">
-        <v>69.42</v>
+        <v>69.419921875</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -619,7 +619,7 @@
         <v>84.60986328125</v>
       </c>
       <c r="G4">
-        <v>72.11</v>
+        <v>72.10986328125</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -642,7 +642,7 @@
         <v>86.419921875</v>
       </c>
       <c r="G5">
-        <v>47.39</v>
+        <v>47.389892578125</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -665,7 +665,7 @@
         <v>89.02001953125</v>
       </c>
       <c r="G6">
-        <v>62.81</v>
+        <v>62.81005859375</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -688,7 +688,7 @@
         <v>69.3701171875</v>
       </c>
       <c r="G7">
-        <v>52.2</v>
+        <v>52.199951171875</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -711,7 +711,7 @@
         <v>84.81982421875</v>
       </c>
       <c r="G8">
-        <v>62.01</v>
+        <v>62.010009765625</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -734,7 +734,7 @@
         <v>85.669921875</v>
       </c>
       <c r="G9">
-        <v>58.61</v>
+        <v>58.610107421875</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -757,7 +757,7 @@
         <v>83.31982421875</v>
       </c>
       <c r="G10">
-        <v>54.81</v>
+        <v>54.81005859375</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -780,7 +780,7 @@
         <v>72.27001953125</v>
       </c>
       <c r="G11">
-        <v>53.46</v>
+        <v>53.4599609375</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -803,7 +803,7 @@
         <v>107.56005859375</v>
       </c>
       <c r="G12">
-        <v>71.61</v>
+        <v>71.60986328125</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -826,7 +826,7 @@
         <v>39.340087890625</v>
       </c>
       <c r="G13">
-        <v>71.66</v>
+        <v>71.66015625</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -849,7 +849,7 @@
         <v>88.6201171875</v>
       </c>
       <c r="G14">
-        <v>58.89</v>
+        <v>58.889892578125</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -872,7 +872,7 @@
         <v>74.77001953125</v>
       </c>
       <c r="G15">
-        <v>66.51000000000001</v>
+        <v>66.509765625</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -895,7 +895,7 @@
         <v>81.47021484375</v>
       </c>
       <c r="G16">
-        <v>56.4</v>
+        <v>56.39990234375</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -918,7 +918,7 @@
         <v>82.1298828125</v>
       </c>
       <c r="G17">
-        <v>76.69</v>
+        <v>76.68994140625</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -941,7 +941,7 @@
         <v>81.169921875</v>
       </c>
       <c r="G18">
-        <v>62.92</v>
+        <v>62.919921875</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -964,7 +964,7 @@
         <v>98.52001953125</v>
       </c>
       <c r="G19">
-        <v>77.41</v>
+        <v>77.41015625</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1010,7 +1010,7 @@
         <v>75.419921875</v>
       </c>
       <c r="G21">
-        <v>54.21</v>
+        <v>54.2099609375</v>
       </c>
     </row>
     <row r="22" spans="1:7">

--- a/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="40">
   <si>
     <t>Rodada 1</t>
   </si>
@@ -575,6 +575,9 @@
       <c r="G2">
         <v>69.419921875</v>
       </c>
+      <c r="H2">
+        <v>40.67</v>
+      </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" s="1" t="s">
@@ -598,6 +601,9 @@
       <c r="G3">
         <v>83</v>
       </c>
+      <c r="H3">
+        <v>43.17</v>
+      </c>
     </row>
     <row r="4" spans="1:20">
       <c r="A4" s="1" t="s">
@@ -621,6 +627,9 @@
       <c r="G4">
         <v>72.10986328125</v>
       </c>
+      <c r="H4">
+        <v>45.87</v>
+      </c>
     </row>
     <row r="5" spans="1:20">
       <c r="A5" s="1" t="s">
@@ -644,6 +653,9 @@
       <c r="G5">
         <v>47.389892578125</v>
       </c>
+      <c r="H5">
+        <v>38.87</v>
+      </c>
     </row>
     <row r="6" spans="1:20">
       <c r="A6" s="1" t="s">
@@ -667,6 +679,9 @@
       <c r="G6">
         <v>62.81005859375</v>
       </c>
+      <c r="H6">
+        <v>69.97</v>
+      </c>
     </row>
     <row r="7" spans="1:20">
       <c r="A7" s="1" t="s">
@@ -690,6 +705,9 @@
       <c r="G7">
         <v>52.199951171875</v>
       </c>
+      <c r="H7">
+        <v>22.97</v>
+      </c>
     </row>
     <row r="8" spans="1:20">
       <c r="A8" s="1" t="s">
@@ -713,6 +731,9 @@
       <c r="G8">
         <v>62.010009765625</v>
       </c>
+      <c r="H8">
+        <v>30.77</v>
+      </c>
     </row>
     <row r="9" spans="1:20">
       <c r="A9" s="1" t="s">
@@ -736,6 +757,9 @@
       <c r="G9">
         <v>58.610107421875</v>
       </c>
+      <c r="H9">
+        <v>45.37</v>
+      </c>
     </row>
     <row r="10" spans="1:20">
       <c r="A10" s="1" t="s">
@@ -759,6 +783,9 @@
       <c r="G10">
         <v>54.81005859375</v>
       </c>
+      <c r="H10">
+        <v>23.67</v>
+      </c>
     </row>
     <row r="11" spans="1:20">
       <c r="A11" s="1" t="s">
@@ -782,6 +809,9 @@
       <c r="G11">
         <v>53.4599609375</v>
       </c>
+      <c r="H11">
+        <v>32.1</v>
+      </c>
     </row>
     <row r="12" spans="1:20">
       <c r="A12" s="1" t="s">
@@ -805,6 +835,9 @@
       <c r="G12">
         <v>71.60986328125</v>
       </c>
+      <c r="H12">
+        <v>33.27</v>
+      </c>
     </row>
     <row r="13" spans="1:20">
       <c r="A13" s="1" t="s">
@@ -828,6 +861,9 @@
       <c r="G13">
         <v>71.66015625</v>
       </c>
+      <c r="H13">
+        <v>28.77</v>
+      </c>
     </row>
     <row r="14" spans="1:20">
       <c r="A14" s="1" t="s">
@@ -851,6 +887,9 @@
       <c r="G14">
         <v>58.889892578125</v>
       </c>
+      <c r="H14">
+        <v>36.17</v>
+      </c>
     </row>
     <row r="15" spans="1:20">
       <c r="A15" s="1" t="s">
@@ -874,6 +913,9 @@
       <c r="G15">
         <v>66.509765625</v>
       </c>
+      <c r="H15">
+        <v>70.17</v>
+      </c>
     </row>
     <row r="16" spans="1:20">
       <c r="A16" s="1" t="s">
@@ -897,8 +939,11 @@
       <c r="G16">
         <v>56.39990234375</v>
       </c>
-    </row>
-    <row r="17" spans="1:7">
+      <c r="H16">
+        <v>36.3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" s="1" t="s">
         <v>34</v>
       </c>
@@ -920,8 +965,11 @@
       <c r="G17">
         <v>76.68994140625</v>
       </c>
-    </row>
-    <row r="18" spans="1:7">
+      <c r="H17">
+        <v>26.77</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
@@ -943,8 +991,11 @@
       <c r="G18">
         <v>62.919921875</v>
       </c>
-    </row>
-    <row r="19" spans="1:7">
+      <c r="H18">
+        <v>35.8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" s="1" t="s">
         <v>36</v>
       </c>
@@ -966,8 +1017,11 @@
       <c r="G19">
         <v>77.41015625</v>
       </c>
-    </row>
-    <row r="20" spans="1:7">
+      <c r="H19">
+        <v>37.57</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" s="1" t="s">
         <v>37</v>
       </c>
@@ -989,8 +1043,11 @@
       <c r="G20">
         <v>83</v>
       </c>
-    </row>
-    <row r="21" spans="1:7">
+      <c r="H20">
+        <v>43.17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" s="1" t="s">
         <v>38</v>
       </c>
@@ -1012,8 +1069,11 @@
       <c r="G21">
         <v>54.2099609375</v>
       </c>
-    </row>
-    <row r="22" spans="1:7">
+      <c r="H21">
+        <v>29.77</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" s="1" t="s">
         <v>39</v>
       </c>
@@ -1034,6 +1094,9 @@
       </c>
       <c r="G22" t="s">
         <v>20</v>
+      </c>
+      <c r="H22" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -576,7 +576,7 @@
         <v>69.419921875</v>
       </c>
       <c r="H2">
-        <v>40.67</v>
+        <v>70.47021484375</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -602,7 +602,7 @@
         <v>83</v>
       </c>
       <c r="H3">
-        <v>43.17</v>
+        <v>85.97021484375</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -628,7 +628,7 @@
         <v>72.10986328125</v>
       </c>
       <c r="H4">
-        <v>45.87</v>
+        <v>87.1201171875</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -654,7 +654,7 @@
         <v>47.389892578125</v>
       </c>
       <c r="H5">
-        <v>38.87</v>
+        <v>67.27001953125</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -680,7 +680,7 @@
         <v>62.81005859375</v>
       </c>
       <c r="H6">
-        <v>69.97</v>
+        <v>105.8701171875</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -706,7 +706,7 @@
         <v>52.199951171875</v>
       </c>
       <c r="H7">
-        <v>22.97</v>
+        <v>39.969970703125</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -732,7 +732,7 @@
         <v>62.010009765625</v>
       </c>
       <c r="H8">
-        <v>30.77</v>
+        <v>77.06982421875</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -758,7 +758,7 @@
         <v>58.610107421875</v>
       </c>
       <c r="H9">
-        <v>45.37</v>
+        <v>81.56982421875</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -784,7 +784,7 @@
         <v>54.81005859375</v>
       </c>
       <c r="H10">
-        <v>23.67</v>
+        <v>79.919921875</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -810,7 +810,7 @@
         <v>53.4599609375</v>
       </c>
       <c r="H11">
-        <v>32.1</v>
+        <v>58.669921875</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -836,7 +836,7 @@
         <v>71.60986328125</v>
       </c>
       <c r="H12">
-        <v>33.27</v>
+        <v>94.8701171875</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -862,7 +862,7 @@
         <v>71.66015625</v>
       </c>
       <c r="H13">
-        <v>28.77</v>
+        <v>34.469970703125</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -888,7 +888,7 @@
         <v>58.889892578125</v>
       </c>
       <c r="H14">
-        <v>36.17</v>
+        <v>60.070068359375</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -914,7 +914,7 @@
         <v>66.509765625</v>
       </c>
       <c r="H15">
-        <v>70.17</v>
+        <v>82.56982421875</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -940,7 +940,7 @@
         <v>56.39990234375</v>
       </c>
       <c r="H16">
-        <v>36.3</v>
+        <v>59.56005859375</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -966,7 +966,7 @@
         <v>76.68994140625</v>
       </c>
       <c r="H17">
-        <v>26.77</v>
+        <v>50.969970703125</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -992,7 +992,7 @@
         <v>62.919921875</v>
       </c>
       <c r="H18">
-        <v>35.8</v>
+        <v>87.009765625</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1018,7 +1018,7 @@
         <v>77.41015625</v>
       </c>
       <c r="H19">
-        <v>37.57</v>
+        <v>71.3701171875</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1044,7 +1044,7 @@
         <v>83</v>
       </c>
       <c r="H20">
-        <v>43.17</v>
+        <v>76.97021484375</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1070,7 +1070,7 @@
         <v>54.2099609375</v>
       </c>
       <c r="H21">
-        <v>29.77</v>
+        <v>56.669921875</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1096,7 +1096,7 @@
         <v>20</v>
       </c>
       <c r="H22" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="40">
   <si>
     <t>Rodada 1</t>
   </si>
@@ -578,6 +578,9 @@
       <c r="H2">
         <v>70.47021484375</v>
       </c>
+      <c r="I2">
+        <v>74.9501953125</v>
+      </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" s="1" t="s">
@@ -604,6 +607,9 @@
       <c r="H3">
         <v>85.97021484375</v>
       </c>
+      <c r="I3">
+        <v>76.4501953125</v>
+      </c>
     </row>
     <row r="4" spans="1:20">
       <c r="A4" s="1" t="s">
@@ -630,6 +636,9 @@
       <c r="H4">
         <v>87.1201171875</v>
       </c>
+      <c r="I4">
+        <v>55.0400390625</v>
+      </c>
     </row>
     <row r="5" spans="1:20">
       <c r="A5" s="1" t="s">
@@ -656,6 +665,9 @@
       <c r="H5">
         <v>67.27001953125</v>
       </c>
+      <c r="I5">
+        <v>75.75</v>
+      </c>
     </row>
     <row r="6" spans="1:20">
       <c r="A6" s="1" t="s">
@@ -682,6 +694,9 @@
       <c r="H6">
         <v>105.8701171875</v>
       </c>
+      <c r="I6">
+        <v>76.89990234375</v>
+      </c>
     </row>
     <row r="7" spans="1:20">
       <c r="A7" s="1" t="s">
@@ -708,6 +723,9 @@
       <c r="H7">
         <v>39.969970703125</v>
       </c>
+      <c r="I7">
+        <v>60.5</v>
+      </c>
     </row>
     <row r="8" spans="1:20">
       <c r="A8" s="1" t="s">
@@ -734,6 +752,9 @@
       <c r="H8">
         <v>77.06982421875</v>
       </c>
+      <c r="I8">
+        <v>80.0498046875</v>
+      </c>
     </row>
     <row r="9" spans="1:20">
       <c r="A9" s="1" t="s">
@@ -760,6 +781,9 @@
       <c r="H9">
         <v>81.56982421875</v>
       </c>
+      <c r="I9">
+        <v>73.35009765625</v>
+      </c>
     </row>
     <row r="10" spans="1:20">
       <c r="A10" s="1" t="s">
@@ -786,6 +810,9 @@
       <c r="H10">
         <v>79.919921875</v>
       </c>
+      <c r="I10">
+        <v>72.25</v>
+      </c>
     </row>
     <row r="11" spans="1:20">
       <c r="A11" s="1" t="s">
@@ -812,6 +839,9 @@
       <c r="H11">
         <v>58.669921875</v>
       </c>
+      <c r="I11">
+        <v>45.699951171875</v>
+      </c>
     </row>
     <row r="12" spans="1:20">
       <c r="A12" s="1" t="s">
@@ -838,6 +868,9 @@
       <c r="H12">
         <v>94.8701171875</v>
       </c>
+      <c r="I12">
+        <v>74.0498046875</v>
+      </c>
     </row>
     <row r="13" spans="1:20">
       <c r="A13" s="1" t="s">
@@ -864,6 +897,9 @@
       <c r="H13">
         <v>34.469970703125</v>
       </c>
+      <c r="I13">
+        <v>40.280029296875</v>
+      </c>
     </row>
     <row r="14" spans="1:20">
       <c r="A14" s="1" t="s">
@@ -890,6 +926,9 @@
       <c r="H14">
         <v>60.070068359375</v>
       </c>
+      <c r="I14">
+        <v>79.85009765625</v>
+      </c>
     </row>
     <row r="15" spans="1:20">
       <c r="A15" s="1" t="s">
@@ -916,6 +955,9 @@
       <c r="H15">
         <v>82.56982421875</v>
       </c>
+      <c r="I15">
+        <v>76.25</v>
+      </c>
     </row>
     <row r="16" spans="1:20">
       <c r="A16" s="1" t="s">
@@ -942,8 +984,11 @@
       <c r="H16">
         <v>59.56005859375</v>
       </c>
-    </row>
-    <row r="17" spans="1:8">
+      <c r="I16">
+        <v>75.0498046875</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" s="1" t="s">
         <v>34</v>
       </c>
@@ -968,8 +1013,11 @@
       <c r="H17">
         <v>50.969970703125</v>
       </c>
-    </row>
-    <row r="18" spans="1:8">
+      <c r="I17">
+        <v>74.85009765625</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
@@ -994,8 +1042,11 @@
       <c r="H18">
         <v>87.009765625</v>
       </c>
-    </row>
-    <row r="19" spans="1:8">
+      <c r="I18">
+        <v>69.89990234375</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19" s="1" t="s">
         <v>36</v>
       </c>
@@ -1020,8 +1071,11 @@
       <c r="H19">
         <v>71.3701171875</v>
       </c>
-    </row>
-    <row r="20" spans="1:8">
+      <c r="I19">
+        <v>80.75</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20" s="1" t="s">
         <v>37</v>
       </c>
@@ -1046,8 +1100,11 @@
       <c r="H20">
         <v>76.97021484375</v>
       </c>
-    </row>
-    <row r="21" spans="1:8">
+      <c r="I20">
+        <v>76.4501953125</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21" s="1" t="s">
         <v>38</v>
       </c>
@@ -1072,8 +1129,11 @@
       <c r="H21">
         <v>56.669921875</v>
       </c>
-    </row>
-    <row r="22" spans="1:8">
+      <c r="I21">
+        <v>56.669921875</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
       <c r="A22" s="1" t="s">
         <v>39</v>
       </c>
@@ -1097,6 +1157,9 @@
       </c>
       <c r="H22" t="s">
         <v>23</v>
+      </c>
+      <c r="I22" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -1130,7 +1130,7 @@
         <v>56.669921875</v>
       </c>
       <c r="I21">
-        <v>56.669921875</v>
+        <v>67.64990234375</v>
       </c>
     </row>
     <row r="22" spans="1:9">

--- a/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="40">
   <si>
     <t>Rodada 1</t>
   </si>
@@ -581,6 +581,9 @@
       <c r="I2">
         <v>74.9501953125</v>
       </c>
+      <c r="J2">
+        <v>90.38</v>
+      </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" s="1" t="s">
@@ -610,6 +613,9 @@
       <c r="I3">
         <v>76.4501953125</v>
       </c>
+      <c r="J3">
+        <v>86.45</v>
+      </c>
     </row>
     <row r="4" spans="1:20">
       <c r="A4" s="1" t="s">
@@ -639,6 +645,9 @@
       <c r="I4">
         <v>55.0400390625</v>
       </c>
+      <c r="J4">
+        <v>93.88</v>
+      </c>
     </row>
     <row r="5" spans="1:20">
       <c r="A5" s="1" t="s">
@@ -668,6 +677,9 @@
       <c r="I5">
         <v>75.75</v>
       </c>
+      <c r="J5">
+        <v>85.95999999999999</v>
+      </c>
     </row>
     <row r="6" spans="1:20">
       <c r="A6" s="1" t="s">
@@ -697,6 +709,9 @@
       <c r="I6">
         <v>76.89990234375</v>
       </c>
+      <c r="J6">
+        <v>81.44</v>
+      </c>
     </row>
     <row r="7" spans="1:20">
       <c r="A7" s="1" t="s">
@@ -726,6 +741,9 @@
       <c r="I7">
         <v>60.5</v>
       </c>
+      <c r="J7">
+        <v>65.90000000000001</v>
+      </c>
     </row>
     <row r="8" spans="1:20">
       <c r="A8" s="1" t="s">
@@ -755,6 +773,9 @@
       <c r="I8">
         <v>80.0498046875</v>
       </c>
+      <c r="J8">
+        <v>61.01</v>
+      </c>
     </row>
     <row r="9" spans="1:20">
       <c r="A9" s="1" t="s">
@@ -784,6 +805,9 @@
       <c r="I9">
         <v>73.35009765625</v>
       </c>
+      <c r="J9">
+        <v>104.68</v>
+      </c>
     </row>
     <row r="10" spans="1:20">
       <c r="A10" s="1" t="s">
@@ -813,6 +837,9 @@
       <c r="I10">
         <v>72.25</v>
       </c>
+      <c r="J10">
+        <v>59.38</v>
+      </c>
     </row>
     <row r="11" spans="1:20">
       <c r="A11" s="1" t="s">
@@ -842,6 +869,9 @@
       <c r="I11">
         <v>45.699951171875</v>
       </c>
+      <c r="J11">
+        <v>69.34</v>
+      </c>
     </row>
     <row r="12" spans="1:20">
       <c r="A12" s="1" t="s">
@@ -871,6 +901,9 @@
       <c r="I12">
         <v>74.0498046875</v>
       </c>
+      <c r="J12">
+        <v>90.88</v>
+      </c>
     </row>
     <row r="13" spans="1:20">
       <c r="A13" s="1" t="s">
@@ -900,6 +933,9 @@
       <c r="I13">
         <v>40.280029296875</v>
       </c>
+      <c r="J13">
+        <v>46.66</v>
+      </c>
     </row>
     <row r="14" spans="1:20">
       <c r="A14" s="1" t="s">
@@ -929,6 +965,9 @@
       <c r="I14">
         <v>79.85009765625</v>
       </c>
+      <c r="J14">
+        <v>101.96</v>
+      </c>
     </row>
     <row r="15" spans="1:20">
       <c r="A15" s="1" t="s">
@@ -958,6 +997,9 @@
       <c r="I15">
         <v>76.25</v>
       </c>
+      <c r="J15">
+        <v>56.89</v>
+      </c>
     </row>
     <row r="16" spans="1:20">
       <c r="A16" s="1" t="s">
@@ -987,8 +1029,11 @@
       <c r="I16">
         <v>75.0498046875</v>
       </c>
-    </row>
-    <row r="17" spans="1:9">
+      <c r="J16">
+        <v>97.78</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17" s="1" t="s">
         <v>34</v>
       </c>
@@ -1016,8 +1061,11 @@
       <c r="I17">
         <v>74.85009765625</v>
       </c>
-    </row>
-    <row r="18" spans="1:9">
+      <c r="J17">
+        <v>90.04000000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
@@ -1045,8 +1093,11 @@
       <c r="I18">
         <v>69.89990234375</v>
       </c>
-    </row>
-    <row r="19" spans="1:9">
+      <c r="J18">
+        <v>92.14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19" s="1" t="s">
         <v>36</v>
       </c>
@@ -1074,8 +1125,11 @@
       <c r="I19">
         <v>80.75</v>
       </c>
-    </row>
-    <row r="20" spans="1:9">
+      <c r="J19">
+        <v>84.44</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20" s="1" t="s">
         <v>37</v>
       </c>
@@ -1103,8 +1157,11 @@
       <c r="I20">
         <v>76.4501953125</v>
       </c>
-    </row>
-    <row r="21" spans="1:9">
+      <c r="J20">
+        <v>86.45</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" s="1" t="s">
         <v>38</v>
       </c>
@@ -1132,8 +1189,11 @@
       <c r="I21">
         <v>67.64990234375</v>
       </c>
-    </row>
-    <row r="22" spans="1:9">
+      <c r="J21">
+        <v>109.44</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22" s="1" t="s">
         <v>39</v>
       </c>
@@ -1160,6 +1220,9 @@
       </c>
       <c r="I22" t="s">
         <v>36</v>
+      </c>
+      <c r="J22" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -582,7 +582,7 @@
         <v>74.9501953125</v>
       </c>
       <c r="J2">
-        <v>90.38</v>
+        <v>90.3798828125</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -614,7 +614,7 @@
         <v>76.4501953125</v>
       </c>
       <c r="J3">
-        <v>86.45</v>
+        <v>85.85009765625</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -646,7 +646,7 @@
         <v>55.0400390625</v>
       </c>
       <c r="J4">
-        <v>93.88</v>
+        <v>93.8798828125</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -678,7 +678,7 @@
         <v>75.75</v>
       </c>
       <c r="J5">
-        <v>85.95999999999999</v>
+        <v>85.9599609375</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -710,7 +710,7 @@
         <v>76.89990234375</v>
       </c>
       <c r="J6">
-        <v>81.44</v>
+        <v>79.93994140625</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -742,7 +742,7 @@
         <v>60.5</v>
       </c>
       <c r="J7">
-        <v>65.90000000000001</v>
+        <v>65.2998046875</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -774,7 +774,7 @@
         <v>80.0498046875</v>
       </c>
       <c r="J8">
-        <v>61.01</v>
+        <v>59.010009765625</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -806,7 +806,7 @@
         <v>73.35009765625</v>
       </c>
       <c r="J9">
-        <v>104.68</v>
+        <v>104.68017578125</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -838,7 +838,7 @@
         <v>72.25</v>
       </c>
       <c r="J10">
-        <v>59.38</v>
+        <v>59.3798828125</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -870,7 +870,7 @@
         <v>45.699951171875</v>
       </c>
       <c r="J11">
-        <v>69.34</v>
+        <v>69.33984375</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -902,7 +902,7 @@
         <v>74.0498046875</v>
       </c>
       <c r="J12">
-        <v>90.88</v>
+        <v>90.8798828125</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -934,7 +934,7 @@
         <v>40.280029296875</v>
       </c>
       <c r="J13">
-        <v>46.66</v>
+        <v>43.659912109375</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -966,7 +966,7 @@
         <v>79.85009765625</v>
       </c>
       <c r="J14">
-        <v>101.96</v>
+        <v>101.9599609375</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -998,7 +998,7 @@
         <v>76.25</v>
       </c>
       <c r="J15">
-        <v>56.89</v>
+        <v>56.090087890625</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -1030,7 +1030,7 @@
         <v>75.0498046875</v>
       </c>
       <c r="J16">
-        <v>97.78</v>
+        <v>96.27978515625</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -1062,7 +1062,7 @@
         <v>74.85009765625</v>
       </c>
       <c r="J17">
-        <v>90.04000000000001</v>
+        <v>90.0400390625</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -1094,7 +1094,7 @@
         <v>69.89990234375</v>
       </c>
       <c r="J18">
-        <v>92.14</v>
+        <v>91.14013671875</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -1126,7 +1126,7 @@
         <v>80.75</v>
       </c>
       <c r="J19">
-        <v>84.44</v>
+        <v>84.43994140625</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -1158,7 +1158,7 @@
         <v>76.4501953125</v>
       </c>
       <c r="J20">
-        <v>86.45</v>
+        <v>85.85009765625</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -1190,7 +1190,7 @@
         <v>67.64990234375</v>
       </c>
       <c r="J21">
-        <v>109.44</v>
+        <v>109.43994140625</v>
       </c>
     </row>
     <row r="22" spans="1:10">

--- a/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="40">
   <si>
     <t>Rodada 1</t>
   </si>
@@ -584,6 +584,9 @@
       <c r="J2">
         <v>90.3798828125</v>
       </c>
+      <c r="K2">
+        <v>58.39</v>
+      </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" s="1" t="s">
@@ -616,6 +619,9 @@
       <c r="J3">
         <v>85.85009765625</v>
       </c>
+      <c r="K3">
+        <v>59.29</v>
+      </c>
     </row>
     <row r="4" spans="1:20">
       <c r="A4" s="1" t="s">
@@ -648,6 +654,9 @@
       <c r="J4">
         <v>93.8798828125</v>
       </c>
+      <c r="K4">
+        <v>51.97</v>
+      </c>
     </row>
     <row r="5" spans="1:20">
       <c r="A5" s="1" t="s">
@@ -680,6 +689,9 @@
       <c r="J5">
         <v>85.9599609375</v>
       </c>
+      <c r="K5">
+        <v>39.87</v>
+      </c>
     </row>
     <row r="6" spans="1:20">
       <c r="A6" s="1" t="s">
@@ -712,6 +724,9 @@
       <c r="J6">
         <v>79.93994140625</v>
       </c>
+      <c r="K6">
+        <v>55.19</v>
+      </c>
     </row>
     <row r="7" spans="1:20">
       <c r="A7" s="1" t="s">
@@ -744,6 +759,9 @@
       <c r="J7">
         <v>65.2998046875</v>
       </c>
+      <c r="K7">
+        <v>50.79</v>
+      </c>
     </row>
     <row r="8" spans="1:20">
       <c r="A8" s="1" t="s">
@@ -776,6 +794,9 @@
       <c r="J8">
         <v>59.010009765625</v>
       </c>
+      <c r="K8">
+        <v>60.57</v>
+      </c>
     </row>
     <row r="9" spans="1:20">
       <c r="A9" s="1" t="s">
@@ -808,6 +829,9 @@
       <c r="J9">
         <v>104.68017578125</v>
       </c>
+      <c r="K9">
+        <v>67.29000000000001</v>
+      </c>
     </row>
     <row r="10" spans="1:20">
       <c r="A10" s="1" t="s">
@@ -840,6 +864,9 @@
       <c r="J10">
         <v>59.3798828125</v>
       </c>
+      <c r="K10">
+        <v>66.67</v>
+      </c>
     </row>
     <row r="11" spans="1:20">
       <c r="A11" s="1" t="s">
@@ -872,6 +899,9 @@
       <c r="J11">
         <v>69.33984375</v>
       </c>
+      <c r="K11">
+        <v>84.47</v>
+      </c>
     </row>
     <row r="12" spans="1:20">
       <c r="A12" s="1" t="s">
@@ -904,6 +934,9 @@
       <c r="J12">
         <v>90.8798828125</v>
       </c>
+      <c r="K12">
+        <v>48.77</v>
+      </c>
     </row>
     <row r="13" spans="1:20">
       <c r="A13" s="1" t="s">
@@ -936,6 +969,9 @@
       <c r="J13">
         <v>43.659912109375</v>
       </c>
+      <c r="K13">
+        <v>55.12</v>
+      </c>
     </row>
     <row r="14" spans="1:20">
       <c r="A14" s="1" t="s">
@@ -968,6 +1004,9 @@
       <c r="J14">
         <v>101.9599609375</v>
       </c>
+      <c r="K14">
+        <v>82.17</v>
+      </c>
     </row>
     <row r="15" spans="1:20">
       <c r="A15" s="1" t="s">
@@ -1000,6 +1039,9 @@
       <c r="J15">
         <v>56.090087890625</v>
       </c>
+      <c r="K15">
+        <v>42.07</v>
+      </c>
     </row>
     <row r="16" spans="1:20">
       <c r="A16" s="1" t="s">
@@ -1032,8 +1074,11 @@
       <c r="J16">
         <v>96.27978515625</v>
       </c>
-    </row>
-    <row r="17" spans="1:10">
+      <c r="K16">
+        <v>78.89</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
       <c r="A17" s="1" t="s">
         <v>34</v>
       </c>
@@ -1064,8 +1109,11 @@
       <c r="J17">
         <v>90.0400390625</v>
       </c>
-    </row>
-    <row r="18" spans="1:10">
+      <c r="K17">
+        <v>39.57</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
       <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
@@ -1096,8 +1144,11 @@
       <c r="J18">
         <v>91.14013671875</v>
       </c>
-    </row>
-    <row r="19" spans="1:10">
+      <c r="K18">
+        <v>48.27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
       <c r="A19" s="1" t="s">
         <v>36</v>
       </c>
@@ -1128,8 +1179,11 @@
       <c r="J19">
         <v>84.43994140625</v>
       </c>
-    </row>
-    <row r="20" spans="1:10">
+      <c r="K19">
+        <v>68.47</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
       <c r="A20" s="1" t="s">
         <v>37</v>
       </c>
@@ -1160,8 +1214,11 @@
       <c r="J20">
         <v>85.85009765625</v>
       </c>
-    </row>
-    <row r="21" spans="1:10">
+      <c r="K20">
+        <v>59.29</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
       <c r="A21" s="1" t="s">
         <v>38</v>
       </c>
@@ -1192,8 +1249,11 @@
       <c r="J21">
         <v>109.43994140625</v>
       </c>
-    </row>
-    <row r="22" spans="1:10">
+      <c r="K21">
+        <v>63.97</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
       <c r="A22" s="1" t="s">
         <v>39</v>
       </c>
@@ -1223,6 +1283,9 @@
       </c>
       <c r="J22" t="s">
         <v>38</v>
+      </c>
+      <c r="K22" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -585,7 +585,7 @@
         <v>90.3798828125</v>
       </c>
       <c r="K2">
-        <v>58.39</v>
+        <v>57.18994140625</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -620,7 +620,7 @@
         <v>85.85009765625</v>
       </c>
       <c r="K3">
-        <v>59.29</v>
+        <v>58.090087890625</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -655,7 +655,7 @@
         <v>93.8798828125</v>
       </c>
       <c r="K4">
-        <v>51.97</v>
+        <v>51.570068359375</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -690,7 +690,7 @@
         <v>85.9599609375</v>
       </c>
       <c r="K5">
-        <v>39.87</v>
+        <v>39.469970703125</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -725,7 +725,7 @@
         <v>79.93994140625</v>
       </c>
       <c r="K6">
-        <v>55.19</v>
+        <v>54.389892578125</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -760,7 +760,7 @@
         <v>65.2998046875</v>
       </c>
       <c r="K7">
-        <v>50.79</v>
+        <v>50.7900390625</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -795,7 +795,7 @@
         <v>59.010009765625</v>
       </c>
       <c r="K8">
-        <v>60.57</v>
+        <v>60.169921875</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -830,7 +830,7 @@
         <v>104.68017578125</v>
       </c>
       <c r="K9">
-        <v>67.29000000000001</v>
+        <v>66.89013671875</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -865,7 +865,7 @@
         <v>59.3798828125</v>
       </c>
       <c r="K10">
-        <v>66.67</v>
+        <v>66.27001953125</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -900,7 +900,7 @@
         <v>69.33984375</v>
       </c>
       <c r="K11">
-        <v>84.47</v>
+        <v>84.06982421875</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -935,7 +935,7 @@
         <v>90.8798828125</v>
       </c>
       <c r="K12">
-        <v>48.77</v>
+        <v>47.570068359375</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -970,7 +970,7 @@
         <v>43.659912109375</v>
       </c>
       <c r="K13">
-        <v>55.12</v>
+        <v>55.1201171875</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -1005,7 +1005,7 @@
         <v>101.9599609375</v>
       </c>
       <c r="K14">
-        <v>82.17</v>
+        <v>82.169921875</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -1040,7 +1040,7 @@
         <v>56.090087890625</v>
       </c>
       <c r="K15">
-        <v>42.07</v>
+        <v>40.8701171875</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -1075,7 +1075,7 @@
         <v>96.27978515625</v>
       </c>
       <c r="K16">
-        <v>78.89</v>
+        <v>78.89013671875</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1110,7 +1110,7 @@
         <v>90.0400390625</v>
       </c>
       <c r="K17">
-        <v>39.57</v>
+        <v>38.3701171875</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1145,7 +1145,7 @@
         <v>91.14013671875</v>
       </c>
       <c r="K18">
-        <v>48.27</v>
+        <v>47.8701171875</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1180,7 +1180,7 @@
         <v>84.43994140625</v>
       </c>
       <c r="K19">
-        <v>68.47</v>
+        <v>67.27001953125</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1215,7 +1215,7 @@
         <v>85.85009765625</v>
       </c>
       <c r="K20">
-        <v>59.29</v>
+        <v>58.090087890625</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -1250,7 +1250,7 @@
         <v>109.43994140625</v>
       </c>
       <c r="K21">
-        <v>63.97</v>
+        <v>63.570068359375</v>
       </c>
     </row>
     <row r="22" spans="1:11">

--- a/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="40">
   <si>
     <t>Rodada 1</t>
   </si>
@@ -587,6 +587,9 @@
       <c r="K2">
         <v>57.18994140625</v>
       </c>
+      <c r="L2">
+        <v>86.259765625</v>
+      </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" s="1" t="s">
@@ -622,6 +625,9 @@
       <c r="K3">
         <v>58.090087890625</v>
       </c>
+      <c r="L3">
+        <v>79.66015625</v>
+      </c>
     </row>
     <row r="4" spans="1:20">
       <c r="A4" s="1" t="s">
@@ -657,6 +663,9 @@
       <c r="K4">
         <v>51.570068359375</v>
       </c>
+      <c r="L4">
+        <v>79.580078125</v>
+      </c>
     </row>
     <row r="5" spans="1:20">
       <c r="A5" s="1" t="s">
@@ -692,6 +701,9 @@
       <c r="K5">
         <v>39.469970703125</v>
       </c>
+      <c r="L5">
+        <v>85.16015625</v>
+      </c>
     </row>
     <row r="6" spans="1:20">
       <c r="A6" s="1" t="s">
@@ -727,6 +739,9 @@
       <c r="K6">
         <v>54.389892578125</v>
       </c>
+      <c r="L6">
+        <v>91.27978515625</v>
+      </c>
     </row>
     <row r="7" spans="1:20">
       <c r="A7" s="1" t="s">
@@ -762,6 +777,9 @@
       <c r="K7">
         <v>50.7900390625</v>
       </c>
+      <c r="L7">
+        <v>71.35986328125</v>
+      </c>
     </row>
     <row r="8" spans="1:20">
       <c r="A8" s="1" t="s">
@@ -797,6 +815,9 @@
       <c r="K8">
         <v>60.169921875</v>
       </c>
+      <c r="L8">
+        <v>82.81005859375</v>
+      </c>
     </row>
     <row r="9" spans="1:20">
       <c r="A9" s="1" t="s">
@@ -832,6 +853,9 @@
       <c r="K9">
         <v>66.89013671875</v>
       </c>
+      <c r="L9">
+        <v>90.4599609375</v>
+      </c>
     </row>
     <row r="10" spans="1:20">
       <c r="A10" s="1" t="s">
@@ -867,6 +891,9 @@
       <c r="K10">
         <v>66.27001953125</v>
       </c>
+      <c r="L10">
+        <v>105.9599609375</v>
+      </c>
     </row>
     <row r="11" spans="1:20">
       <c r="A11" s="1" t="s">
@@ -902,6 +929,9 @@
       <c r="K11">
         <v>84.06982421875</v>
       </c>
+      <c r="L11">
+        <v>53.030029296875</v>
+      </c>
     </row>
     <row r="12" spans="1:20">
       <c r="A12" s="1" t="s">
@@ -937,6 +967,9 @@
       <c r="K12">
         <v>47.570068359375</v>
       </c>
+      <c r="L12">
+        <v>69.25</v>
+      </c>
     </row>
     <row r="13" spans="1:20">
       <c r="A13" s="1" t="s">
@@ -972,6 +1005,9 @@
       <c r="K13">
         <v>55.1201171875</v>
       </c>
+      <c r="L13">
+        <v>59.659912109375</v>
+      </c>
     </row>
     <row r="14" spans="1:20">
       <c r="A14" s="1" t="s">
@@ -1007,6 +1043,9 @@
       <c r="K14">
         <v>82.169921875</v>
       </c>
+      <c r="L14">
+        <v>101.35986328125</v>
+      </c>
     </row>
     <row r="15" spans="1:20">
       <c r="A15" s="1" t="s">
@@ -1042,6 +1081,9 @@
       <c r="K15">
         <v>40.8701171875</v>
       </c>
+      <c r="L15">
+        <v>82.4599609375</v>
+      </c>
     </row>
     <row r="16" spans="1:20">
       <c r="A16" s="1" t="s">
@@ -1077,8 +1119,11 @@
       <c r="K16">
         <v>78.89013671875</v>
       </c>
-    </row>
-    <row r="17" spans="1:11">
+      <c r="L16">
+        <v>86.66015625</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
       <c r="A17" s="1" t="s">
         <v>34</v>
       </c>
@@ -1112,8 +1157,11 @@
       <c r="K17">
         <v>38.3701171875</v>
       </c>
-    </row>
-    <row r="18" spans="1:11">
+      <c r="L17">
+        <v>70.35986328125</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
       <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
@@ -1147,8 +1195,11 @@
       <c r="K18">
         <v>47.8701171875</v>
       </c>
-    </row>
-    <row r="19" spans="1:11">
+      <c r="L18">
+        <v>83.47998046875</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
       <c r="A19" s="1" t="s">
         <v>36</v>
       </c>
@@ -1182,8 +1233,11 @@
       <c r="K19">
         <v>67.27001953125</v>
       </c>
-    </row>
-    <row r="20" spans="1:11">
+      <c r="L19">
+        <v>94.06005859375</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
       <c r="A20" s="1" t="s">
         <v>37</v>
       </c>
@@ -1217,8 +1271,11 @@
       <c r="K20">
         <v>58.090087890625</v>
       </c>
-    </row>
-    <row r="21" spans="1:11">
+      <c r="L20">
+        <v>88.759765625</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
       <c r="A21" s="1" t="s">
         <v>38</v>
       </c>
@@ -1252,8 +1309,11 @@
       <c r="K21">
         <v>63.570068359375</v>
       </c>
-    </row>
-    <row r="22" spans="1:11">
+      <c r="L21">
+        <v>101.41015625</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
       <c r="A22" s="1" t="s">
         <v>39</v>
       </c>
@@ -1286,6 +1346,9 @@
       </c>
       <c r="K22" t="s">
         <v>28</v>
+      </c>
+      <c r="L22" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="40">
   <si>
     <t>Rodada 1</t>
   </si>
@@ -590,6 +590,9 @@
       <c r="L2">
         <v>86.259765625</v>
       </c>
+      <c r="M2">
+        <v>82.90000000000001</v>
+      </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" s="1" t="s">
@@ -628,6 +631,9 @@
       <c r="L3">
         <v>79.66015625</v>
       </c>
+      <c r="M3">
+        <v>84.40000000000001</v>
+      </c>
     </row>
     <row r="4" spans="1:20">
       <c r="A4" s="1" t="s">
@@ -666,6 +672,9 @@
       <c r="L4">
         <v>79.580078125</v>
       </c>
+      <c r="M4">
+        <v>77.95</v>
+      </c>
     </row>
     <row r="5" spans="1:20">
       <c r="A5" s="1" t="s">
@@ -704,6 +713,9 @@
       <c r="L5">
         <v>85.16015625</v>
       </c>
+      <c r="M5">
+        <v>81.45</v>
+      </c>
     </row>
     <row r="6" spans="1:20">
       <c r="A6" s="1" t="s">
@@ -742,6 +754,9 @@
       <c r="L6">
         <v>91.27978515625</v>
       </c>
+      <c r="M6">
+        <v>81.09999999999999</v>
+      </c>
     </row>
     <row r="7" spans="1:20">
       <c r="A7" s="1" t="s">
@@ -780,6 +795,9 @@
       <c r="L7">
         <v>71.35986328125</v>
       </c>
+      <c r="M7">
+        <v>75.91</v>
+      </c>
     </row>
     <row r="8" spans="1:20">
       <c r="A8" s="1" t="s">
@@ -818,6 +836,9 @@
       <c r="L8">
         <v>82.81005859375</v>
       </c>
+      <c r="M8">
+        <v>77.34999999999999</v>
+      </c>
     </row>
     <row r="9" spans="1:20">
       <c r="A9" s="1" t="s">
@@ -856,6 +877,9 @@
       <c r="L9">
         <v>90.4599609375</v>
       </c>
+      <c r="M9">
+        <v>84.40000000000001</v>
+      </c>
     </row>
     <row r="10" spans="1:20">
       <c r="A10" s="1" t="s">
@@ -894,6 +918,9 @@
       <c r="L10">
         <v>105.9599609375</v>
       </c>
+      <c r="M10">
+        <v>77.25</v>
+      </c>
     </row>
     <row r="11" spans="1:20">
       <c r="A11" s="1" t="s">
@@ -932,6 +959,9 @@
       <c r="L11">
         <v>53.030029296875</v>
       </c>
+      <c r="M11">
+        <v>83.7</v>
+      </c>
     </row>
     <row r="12" spans="1:20">
       <c r="A12" s="1" t="s">
@@ -970,6 +1000,9 @@
       <c r="L12">
         <v>69.25</v>
       </c>
+      <c r="M12">
+        <v>84</v>
+      </c>
     </row>
     <row r="13" spans="1:20">
       <c r="A13" s="1" t="s">
@@ -1008,6 +1041,9 @@
       <c r="L13">
         <v>59.659912109375</v>
       </c>
+      <c r="M13">
+        <v>69.31999999999999</v>
+      </c>
     </row>
     <row r="14" spans="1:20">
       <c r="A14" s="1" t="s">
@@ -1046,6 +1082,9 @@
       <c r="L14">
         <v>101.35986328125</v>
       </c>
+      <c r="M14">
+        <v>64.2</v>
+      </c>
     </row>
     <row r="15" spans="1:20">
       <c r="A15" s="1" t="s">
@@ -1084,6 +1123,9 @@
       <c r="L15">
         <v>82.4599609375</v>
       </c>
+      <c r="M15">
+        <v>92.34999999999999</v>
+      </c>
     </row>
     <row r="16" spans="1:20">
       <c r="A16" s="1" t="s">
@@ -1122,8 +1164,11 @@
       <c r="L16">
         <v>86.66015625</v>
       </c>
-    </row>
-    <row r="17" spans="1:12">
+      <c r="M16">
+        <v>80.7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17" s="1" t="s">
         <v>34</v>
       </c>
@@ -1160,8 +1205,11 @@
       <c r="L17">
         <v>70.35986328125</v>
       </c>
-    </row>
-    <row r="18" spans="1:12">
+      <c r="M17">
+        <v>71.59999999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
@@ -1198,8 +1246,11 @@
       <c r="L18">
         <v>83.47998046875</v>
       </c>
-    </row>
-    <row r="19" spans="1:12">
+      <c r="M18">
+        <v>63.8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
       <c r="A19" s="1" t="s">
         <v>36</v>
       </c>
@@ -1236,8 +1287,11 @@
       <c r="L19">
         <v>94.06005859375</v>
       </c>
-    </row>
-    <row r="20" spans="1:12">
+      <c r="M19">
+        <v>84.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
       <c r="A20" s="1" t="s">
         <v>37</v>
       </c>
@@ -1274,8 +1328,11 @@
       <c r="L20">
         <v>88.759765625</v>
       </c>
-    </row>
-    <row r="21" spans="1:12">
+      <c r="M20">
+        <v>86.66</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
       <c r="A21" s="1" t="s">
         <v>38</v>
       </c>
@@ -1312,8 +1369,11 @@
       <c r="L21">
         <v>101.41015625</v>
       </c>
-    </row>
-    <row r="22" spans="1:12">
+      <c r="M21">
+        <v>70.3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
       <c r="A22" s="1" t="s">
         <v>39</v>
       </c>
@@ -1349,6 +1409,9 @@
       </c>
       <c r="L22" t="s">
         <v>27</v>
+      </c>
+      <c r="M22" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -591,7 +591,7 @@
         <v>86.259765625</v>
       </c>
       <c r="M2">
-        <v>82.90000000000001</v>
+        <v>82.89990234375</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -632,7 +632,7 @@
         <v>79.66015625</v>
       </c>
       <c r="M3">
-        <v>84.40000000000001</v>
+        <v>84.39990234375</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -673,7 +673,7 @@
         <v>79.580078125</v>
       </c>
       <c r="M4">
-        <v>77.95</v>
+        <v>77.9501953125</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -714,7 +714,7 @@
         <v>85.16015625</v>
       </c>
       <c r="M5">
-        <v>81.45</v>
+        <v>81.4501953125</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -755,7 +755,7 @@
         <v>91.27978515625</v>
       </c>
       <c r="M6">
-        <v>81.09999999999999</v>
+        <v>81.10009765625</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -796,7 +796,7 @@
         <v>71.35986328125</v>
       </c>
       <c r="M7">
-        <v>75.91</v>
+        <v>75.91015625</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -837,7 +837,7 @@
         <v>82.81005859375</v>
       </c>
       <c r="M8">
-        <v>77.34999999999999</v>
+        <v>77.35009765625</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -878,7 +878,7 @@
         <v>90.4599609375</v>
       </c>
       <c r="M9">
-        <v>84.40000000000001</v>
+        <v>84.39990234375</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -960,7 +960,7 @@
         <v>53.030029296875</v>
       </c>
       <c r="M11">
-        <v>83.7</v>
+        <v>83.7001953125</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -1042,7 +1042,7 @@
         <v>59.659912109375</v>
       </c>
       <c r="M13">
-        <v>69.31999999999999</v>
+        <v>69.31982421875</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -1083,7 +1083,7 @@
         <v>101.35986328125</v>
       </c>
       <c r="M14">
-        <v>64.2</v>
+        <v>64.2001953125</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -1124,7 +1124,7 @@
         <v>82.4599609375</v>
       </c>
       <c r="M15">
-        <v>92.34999999999999</v>
+        <v>92.35009765625</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -1165,7 +1165,7 @@
         <v>86.66015625</v>
       </c>
       <c r="M16">
-        <v>80.7</v>
+        <v>80.7001953125</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -1206,7 +1206,7 @@
         <v>70.35986328125</v>
       </c>
       <c r="M17">
-        <v>71.59999999999999</v>
+        <v>71.60009765625</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -1247,7 +1247,7 @@
         <v>83.47998046875</v>
       </c>
       <c r="M18">
-        <v>63.8</v>
+        <v>63.800048828125</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -1329,7 +1329,7 @@
         <v>88.759765625</v>
       </c>
       <c r="M20">
-        <v>86.66</v>
+        <v>86.66015625</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -1370,7 +1370,7 @@
         <v>101.41015625</v>
       </c>
       <c r="M21">
-        <v>70.3</v>
+        <v>70.2998046875</v>
       </c>
     </row>
     <row r="22" spans="1:13">

--- a/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="40">
   <si>
     <t>Rodada 1</t>
   </si>
@@ -593,6 +593,9 @@
       <c r="M2">
         <v>82.89990234375</v>
       </c>
+      <c r="N2">
+        <v>95.02</v>
+      </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" s="1" t="s">
@@ -634,6 +637,9 @@
       <c r="M3">
         <v>84.39990234375</v>
       </c>
+      <c r="N3">
+        <v>97.62</v>
+      </c>
     </row>
     <row r="4" spans="1:20">
       <c r="A4" s="1" t="s">
@@ -675,6 +681,9 @@
       <c r="M4">
         <v>77.9501953125</v>
       </c>
+      <c r="N4">
+        <v>111.22</v>
+      </c>
     </row>
     <row r="5" spans="1:20">
       <c r="A5" s="1" t="s">
@@ -716,6 +725,9 @@
       <c r="M5">
         <v>81.4501953125</v>
       </c>
+      <c r="N5">
+        <v>113.22</v>
+      </c>
     </row>
     <row r="6" spans="1:20">
       <c r="A6" s="1" t="s">
@@ -757,6 +769,9 @@
       <c r="M6">
         <v>81.10009765625</v>
       </c>
+      <c r="N6">
+        <v>136.52</v>
+      </c>
     </row>
     <row r="7" spans="1:20">
       <c r="A7" s="1" t="s">
@@ -798,6 +813,9 @@
       <c r="M7">
         <v>75.91015625</v>
       </c>
+      <c r="N7">
+        <v>80.12</v>
+      </c>
     </row>
     <row r="8" spans="1:20">
       <c r="A8" s="1" t="s">
@@ -839,6 +857,9 @@
       <c r="M8">
         <v>77.35009765625</v>
       </c>
+      <c r="N8">
+        <v>91.87</v>
+      </c>
     </row>
     <row r="9" spans="1:20">
       <c r="A9" s="1" t="s">
@@ -880,6 +901,9 @@
       <c r="M9">
         <v>84.39990234375</v>
       </c>
+      <c r="N9">
+        <v>108.52</v>
+      </c>
     </row>
     <row r="10" spans="1:20">
       <c r="A10" s="1" t="s">
@@ -921,6 +945,9 @@
       <c r="M10">
         <v>77.25</v>
       </c>
+      <c r="N10">
+        <v>98.37</v>
+      </c>
     </row>
     <row r="11" spans="1:20">
       <c r="A11" s="1" t="s">
@@ -962,6 +989,9 @@
       <c r="M11">
         <v>83.7001953125</v>
       </c>
+      <c r="N11">
+        <v>71.95</v>
+      </c>
     </row>
     <row r="12" spans="1:20">
       <c r="A12" s="1" t="s">
@@ -1003,6 +1033,9 @@
       <c r="M12">
         <v>84</v>
       </c>
+      <c r="N12">
+        <v>93.92</v>
+      </c>
     </row>
     <row r="13" spans="1:20">
       <c r="A13" s="1" t="s">
@@ -1044,6 +1077,9 @@
       <c r="M13">
         <v>69.31982421875</v>
       </c>
+      <c r="N13">
+        <v>57.96</v>
+      </c>
     </row>
     <row r="14" spans="1:20">
       <c r="A14" s="1" t="s">
@@ -1085,6 +1121,9 @@
       <c r="M14">
         <v>64.2001953125</v>
       </c>
+      <c r="N14">
+        <v>113.02</v>
+      </c>
     </row>
     <row r="15" spans="1:20">
       <c r="A15" s="1" t="s">
@@ -1126,6 +1165,9 @@
       <c r="M15">
         <v>92.35009765625</v>
       </c>
+      <c r="N15">
+        <v>98.12</v>
+      </c>
     </row>
     <row r="16" spans="1:20">
       <c r="A16" s="1" t="s">
@@ -1167,8 +1209,11 @@
       <c r="M16">
         <v>80.7001953125</v>
       </c>
-    </row>
-    <row r="17" spans="1:13">
+      <c r="N16">
+        <v>108.52</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" s="1" t="s">
         <v>34</v>
       </c>
@@ -1208,8 +1253,11 @@
       <c r="M17">
         <v>71.60009765625</v>
       </c>
-    </row>
-    <row r="18" spans="1:13">
+      <c r="N17">
+        <v>92.58</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
@@ -1249,8 +1297,11 @@
       <c r="M18">
         <v>63.800048828125</v>
       </c>
-    </row>
-    <row r="19" spans="1:13">
+      <c r="N18">
+        <v>110.35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19" s="1" t="s">
         <v>36</v>
       </c>
@@ -1290,8 +1341,11 @@
       <c r="M19">
         <v>84.5</v>
       </c>
-    </row>
-    <row r="20" spans="1:13">
+      <c r="N19">
+        <v>87.92</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20" s="1" t="s">
         <v>37</v>
       </c>
@@ -1331,8 +1385,11 @@
       <c r="M20">
         <v>86.66015625</v>
       </c>
-    </row>
-    <row r="21" spans="1:13">
+      <c r="N20">
+        <v>97.62</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21" s="1" t="s">
         <v>38</v>
       </c>
@@ -1372,8 +1429,11 @@
       <c r="M21">
         <v>70.2998046875</v>
       </c>
-    </row>
-    <row r="22" spans="1:13">
+      <c r="N21">
+        <v>101.86</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
       <c r="A22" s="1" t="s">
         <v>39</v>
       </c>
@@ -1412,6 +1472,9 @@
       </c>
       <c r="M22" t="s">
         <v>32</v>
+      </c>
+      <c r="N22" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -594,7 +594,7 @@
         <v>82.89990234375</v>
       </c>
       <c r="N2">
-        <v>95.02</v>
+        <v>104.29</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -638,7 +638,7 @@
         <v>84.39990234375</v>
       </c>
       <c r="N3">
-        <v>97.62</v>
+        <v>106.39</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -682,7 +682,7 @@
         <v>77.9501953125</v>
       </c>
       <c r="N4">
-        <v>111.22</v>
+        <v>111.29</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -726,7 +726,7 @@
         <v>81.4501953125</v>
       </c>
       <c r="N5">
-        <v>113.22</v>
+        <v>113.29</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -770,7 +770,7 @@
         <v>81.10009765625</v>
       </c>
       <c r="N6">
-        <v>136.52</v>
+        <v>136.59</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -814,7 +814,7 @@
         <v>75.91015625</v>
       </c>
       <c r="N7">
-        <v>80.12</v>
+        <v>80.19</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -858,7 +858,7 @@
         <v>77.35009765625</v>
       </c>
       <c r="N8">
-        <v>91.87</v>
+        <v>115.44</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -902,7 +902,7 @@
         <v>84.39990234375</v>
       </c>
       <c r="N9">
-        <v>108.52</v>
+        <v>108.59</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -946,7 +946,7 @@
         <v>77.25</v>
       </c>
       <c r="N10">
-        <v>98.37</v>
+        <v>122.49</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -990,7 +990,7 @@
         <v>83.7001953125</v>
       </c>
       <c r="N11">
-        <v>71.95</v>
+        <v>90.15000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -1034,7 +1034,7 @@
         <v>84</v>
       </c>
       <c r="N12">
-        <v>93.92</v>
+        <v>101.99</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -1122,7 +1122,7 @@
         <v>64.2001953125</v>
       </c>
       <c r="N14">
-        <v>113.02</v>
+        <v>121.09</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -1166,7 +1166,7 @@
         <v>92.35009765625</v>
       </c>
       <c r="N15">
-        <v>98.12</v>
+        <v>97.69</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -1210,7 +1210,7 @@
         <v>80.7001953125</v>
       </c>
       <c r="N16">
-        <v>108.52</v>
+        <v>108.59</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -1342,7 +1342,7 @@
         <v>84.5</v>
       </c>
       <c r="N19">
-        <v>87.92</v>
+        <v>97.79000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1386,7 +1386,7 @@
         <v>86.66015625</v>
       </c>
       <c r="N20">
-        <v>97.62</v>
+        <v>106.39</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1430,7 +1430,7 @@
         <v>70.2998046875</v>
       </c>
       <c r="N21">
-        <v>101.86</v>
+        <v>129.16</v>
       </c>
     </row>
     <row r="22" spans="1:14">

--- a/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -594,7 +594,7 @@
         <v>82.89990234375</v>
       </c>
       <c r="N2">
-        <v>104.29</v>
+        <v>104.2900390625</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -638,7 +638,7 @@
         <v>84.39990234375</v>
       </c>
       <c r="N3">
-        <v>106.39</v>
+        <v>106.39013671875</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -682,7 +682,7 @@
         <v>77.9501953125</v>
       </c>
       <c r="N4">
-        <v>111.29</v>
+        <v>111.2900390625</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -726,7 +726,7 @@
         <v>81.4501953125</v>
       </c>
       <c r="N5">
-        <v>113.29</v>
+        <v>113.2900390625</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -770,7 +770,7 @@
         <v>81.10009765625</v>
       </c>
       <c r="N6">
-        <v>136.59</v>
+        <v>136.58984375</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -814,7 +814,7 @@
         <v>75.91015625</v>
       </c>
       <c r="N7">
-        <v>80.19</v>
+        <v>80.18994140625</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -858,7 +858,7 @@
         <v>77.35009765625</v>
       </c>
       <c r="N8">
-        <v>115.44</v>
+        <v>115.43994140625</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -902,7 +902,7 @@
         <v>84.39990234375</v>
       </c>
       <c r="N9">
-        <v>108.59</v>
+        <v>108.58984375</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -946,7 +946,7 @@
         <v>77.25</v>
       </c>
       <c r="N10">
-        <v>122.49</v>
+        <v>122.490234375</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -990,7 +990,7 @@
         <v>83.7001953125</v>
       </c>
       <c r="N11">
-        <v>90.15000000000001</v>
+        <v>90.14990234375</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -1034,7 +1034,7 @@
         <v>84</v>
       </c>
       <c r="N12">
-        <v>101.99</v>
+        <v>101.990234375</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -1078,7 +1078,7 @@
         <v>69.31982421875</v>
       </c>
       <c r="N13">
-        <v>57.96</v>
+        <v>57.9599609375</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -1122,7 +1122,7 @@
         <v>64.2001953125</v>
       </c>
       <c r="N14">
-        <v>121.09</v>
+        <v>121.08984375</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -1166,7 +1166,7 @@
         <v>92.35009765625</v>
       </c>
       <c r="N15">
-        <v>97.69</v>
+        <v>97.68994140625</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -1210,7 +1210,7 @@
         <v>80.7001953125</v>
       </c>
       <c r="N16">
-        <v>108.59</v>
+        <v>108.58984375</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -1254,7 +1254,7 @@
         <v>71.60009765625</v>
       </c>
       <c r="N17">
-        <v>92.58</v>
+        <v>92.490234375</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1298,7 +1298,7 @@
         <v>63.800048828125</v>
       </c>
       <c r="N18">
-        <v>110.35</v>
+        <v>110.35009765625</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1342,7 +1342,7 @@
         <v>84.5</v>
       </c>
       <c r="N19">
-        <v>97.79000000000001</v>
+        <v>97.7900390625</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1386,7 +1386,7 @@
         <v>86.66015625</v>
       </c>
       <c r="N20">
-        <v>106.39</v>
+        <v>106.39013671875</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1430,7 +1430,7 @@
         <v>70.2998046875</v>
       </c>
       <c r="N21">
-        <v>129.16</v>
+        <v>129.16015625</v>
       </c>
     </row>
     <row r="22" spans="1:14">

--- a/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="40">
   <si>
     <t>Rodada 1</t>
   </si>
@@ -596,6 +596,9 @@
       <c r="N2">
         <v>104.2900390625</v>
       </c>
+      <c r="O2">
+        <v>48.080078125</v>
+      </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" s="1" t="s">
@@ -640,6 +643,9 @@
       <c r="N3">
         <v>106.39013671875</v>
       </c>
+      <c r="O3">
+        <v>51.8798828125</v>
+      </c>
     </row>
     <row r="4" spans="1:20">
       <c r="A4" s="1" t="s">
@@ -684,6 +690,9 @@
       <c r="N4">
         <v>111.2900390625</v>
       </c>
+      <c r="O4">
+        <v>47.050048828125</v>
+      </c>
     </row>
     <row r="5" spans="1:20">
       <c r="A5" s="1" t="s">
@@ -728,6 +737,9 @@
       <c r="N5">
         <v>113.2900390625</v>
       </c>
+      <c r="O5">
+        <v>61.949951171875</v>
+      </c>
     </row>
     <row r="6" spans="1:20">
       <c r="A6" s="1" t="s">
@@ -772,6 +784,9 @@
       <c r="N6">
         <v>136.58984375</v>
       </c>
+      <c r="O6">
+        <v>46.050048828125</v>
+      </c>
     </row>
     <row r="7" spans="1:20">
       <c r="A7" s="1" t="s">
@@ -816,6 +831,9 @@
       <c r="N7">
         <v>80.18994140625</v>
       </c>
+      <c r="O7">
+        <v>50.72998046875</v>
+      </c>
     </row>
     <row r="8" spans="1:20">
       <c r="A8" s="1" t="s">
@@ -860,6 +878,9 @@
       <c r="N8">
         <v>115.43994140625</v>
       </c>
+      <c r="O8">
+        <v>57.72998046875</v>
+      </c>
     </row>
     <row r="9" spans="1:20">
       <c r="A9" s="1" t="s">
@@ -904,6 +925,9 @@
       <c r="N9">
         <v>108.58984375</v>
       </c>
+      <c r="O9">
+        <v>49.280029296875</v>
+      </c>
     </row>
     <row r="10" spans="1:20">
       <c r="A10" s="1" t="s">
@@ -948,6 +972,9 @@
       <c r="N10">
         <v>122.490234375</v>
       </c>
+      <c r="O10">
+        <v>53.47998046875</v>
+      </c>
     </row>
     <row r="11" spans="1:20">
       <c r="A11" s="1" t="s">
@@ -992,6 +1019,9 @@
       <c r="N11">
         <v>90.14990234375</v>
       </c>
+      <c r="O11">
+        <v>49.43994140625</v>
+      </c>
     </row>
     <row r="12" spans="1:20">
       <c r="A12" s="1" t="s">
@@ -1036,6 +1066,9 @@
       <c r="N12">
         <v>101.990234375</v>
       </c>
+      <c r="O12">
+        <v>55.97998046875</v>
+      </c>
     </row>
     <row r="13" spans="1:20">
       <c r="A13" s="1" t="s">
@@ -1080,6 +1113,9 @@
       <c r="N13">
         <v>57.9599609375</v>
       </c>
+      <c r="O13">
+        <v>44.330078125</v>
+      </c>
     </row>
     <row r="14" spans="1:20">
       <c r="A14" s="1" t="s">
@@ -1124,6 +1160,9 @@
       <c r="N14">
         <v>121.08984375</v>
       </c>
+      <c r="O14">
+        <v>78.35009765625</v>
+      </c>
     </row>
     <row r="15" spans="1:20">
       <c r="A15" s="1" t="s">
@@ -1168,6 +1207,9 @@
       <c r="N15">
         <v>97.68994140625</v>
       </c>
+      <c r="O15">
+        <v>57.239990234375</v>
+      </c>
     </row>
     <row r="16" spans="1:20">
       <c r="A16" s="1" t="s">
@@ -1212,8 +1254,11 @@
       <c r="N16">
         <v>108.58984375</v>
       </c>
-    </row>
-    <row r="17" spans="1:14">
+      <c r="O16">
+        <v>61.679931640625</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15">
       <c r="A17" s="1" t="s">
         <v>34</v>
       </c>
@@ -1256,8 +1301,11 @@
       <c r="N17">
         <v>92.490234375</v>
       </c>
-    </row>
-    <row r="18" spans="1:14">
+      <c r="O17">
+        <v>49.9599609375</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15">
       <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
@@ -1300,8 +1348,11 @@
       <c r="N18">
         <v>110.35009765625</v>
       </c>
-    </row>
-    <row r="19" spans="1:14">
+      <c r="O18">
+        <v>51.080078125</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15">
       <c r="A19" s="1" t="s">
         <v>36</v>
       </c>
@@ -1344,8 +1395,11 @@
       <c r="N19">
         <v>97.7900390625</v>
       </c>
-    </row>
-    <row r="20" spans="1:14">
+      <c r="O19">
+        <v>62.050048828125</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15">
       <c r="A20" s="1" t="s">
         <v>37</v>
       </c>
@@ -1388,8 +1442,11 @@
       <c r="N20">
         <v>106.39013671875</v>
       </c>
-    </row>
-    <row r="21" spans="1:14">
+      <c r="O20">
+        <v>53.780029296875</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15">
       <c r="A21" s="1" t="s">
         <v>38</v>
       </c>
@@ -1432,8 +1489,11 @@
       <c r="N21">
         <v>129.16015625</v>
       </c>
-    </row>
-    <row r="22" spans="1:14">
+      <c r="O21">
+        <v>77.14990234375</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15">
       <c r="A22" s="1" t="s">
         <v>39</v>
       </c>
@@ -1475,6 +1535,9 @@
       </c>
       <c r="N22" t="s">
         <v>23</v>
+      </c>
+      <c r="O22" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="40">
   <si>
     <t>Rodada 1</t>
   </si>
@@ -599,6 +599,9 @@
       <c r="O2">
         <v>48.080078125</v>
       </c>
+      <c r="P2">
+        <v>64.92</v>
+      </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" s="1" t="s">
@@ -646,6 +649,9 @@
       <c r="O3">
         <v>51.8798828125</v>
       </c>
+      <c r="P3">
+        <v>63.75</v>
+      </c>
     </row>
     <row r="4" spans="1:20">
       <c r="A4" s="1" t="s">
@@ -693,6 +699,9 @@
       <c r="O4">
         <v>47.050048828125</v>
       </c>
+      <c r="P4">
+        <v>51.92</v>
+      </c>
     </row>
     <row r="5" spans="1:20">
       <c r="A5" s="1" t="s">
@@ -740,6 +749,9 @@
       <c r="O5">
         <v>61.949951171875</v>
       </c>
+      <c r="P5">
+        <v>60.17</v>
+      </c>
     </row>
     <row r="6" spans="1:20">
       <c r="A6" s="1" t="s">
@@ -787,6 +799,9 @@
       <c r="O6">
         <v>46.050048828125</v>
       </c>
+      <c r="P6">
+        <v>48.27</v>
+      </c>
     </row>
     <row r="7" spans="1:20">
       <c r="A7" s="1" t="s">
@@ -834,6 +849,9 @@
       <c r="O7">
         <v>50.72998046875</v>
       </c>
+      <c r="P7">
+        <v>51.93</v>
+      </c>
     </row>
     <row r="8" spans="1:20">
       <c r="A8" s="1" t="s">
@@ -881,6 +899,9 @@
       <c r="O8">
         <v>57.72998046875</v>
       </c>
+      <c r="P8">
+        <v>55.9</v>
+      </c>
     </row>
     <row r="9" spans="1:20">
       <c r="A9" s="1" t="s">
@@ -928,6 +949,9 @@
       <c r="O9">
         <v>49.280029296875</v>
       </c>
+      <c r="P9">
+        <v>54.58</v>
+      </c>
     </row>
     <row r="10" spans="1:20">
       <c r="A10" s="1" t="s">
@@ -975,6 +999,9 @@
       <c r="O10">
         <v>53.47998046875</v>
       </c>
+      <c r="P10">
+        <v>68.34999999999999</v>
+      </c>
     </row>
     <row r="11" spans="1:20">
       <c r="A11" s="1" t="s">
@@ -1022,6 +1049,9 @@
       <c r="O11">
         <v>49.43994140625</v>
       </c>
+      <c r="P11">
+        <v>53.5</v>
+      </c>
     </row>
     <row r="12" spans="1:20">
       <c r="A12" s="1" t="s">
@@ -1069,6 +1099,9 @@
       <c r="O12">
         <v>55.97998046875</v>
       </c>
+      <c r="P12">
+        <v>57.3</v>
+      </c>
     </row>
     <row r="13" spans="1:20">
       <c r="A13" s="1" t="s">
@@ -1116,6 +1149,9 @@
       <c r="O13">
         <v>44.330078125</v>
       </c>
+      <c r="P13">
+        <v>31.44</v>
+      </c>
     </row>
     <row r="14" spans="1:20">
       <c r="A14" s="1" t="s">
@@ -1163,6 +1199,9 @@
       <c r="O14">
         <v>78.35009765625</v>
       </c>
+      <c r="P14">
+        <v>50.63</v>
+      </c>
     </row>
     <row r="15" spans="1:20">
       <c r="A15" s="1" t="s">
@@ -1210,6 +1249,9 @@
       <c r="O15">
         <v>57.239990234375</v>
       </c>
+      <c r="P15">
+        <v>65.34</v>
+      </c>
     </row>
     <row r="16" spans="1:20">
       <c r="A16" s="1" t="s">
@@ -1257,8 +1299,11 @@
       <c r="O16">
         <v>61.679931640625</v>
       </c>
-    </row>
-    <row r="17" spans="1:15">
+      <c r="P16">
+        <v>49.02</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
       <c r="A17" s="1" t="s">
         <v>34</v>
       </c>
@@ -1304,8 +1349,11 @@
       <c r="O17">
         <v>49.9599609375</v>
       </c>
-    </row>
-    <row r="18" spans="1:15">
+      <c r="P17">
+        <v>44.88</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
       <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
@@ -1351,8 +1399,11 @@
       <c r="O18">
         <v>51.080078125</v>
       </c>
-    </row>
-    <row r="19" spans="1:15">
+      <c r="P18">
+        <v>65.59999999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
       <c r="A19" s="1" t="s">
         <v>36</v>
       </c>
@@ -1398,8 +1449,11 @@
       <c r="O19">
         <v>62.050048828125</v>
       </c>
-    </row>
-    <row r="20" spans="1:15">
+      <c r="P19">
+        <v>58.27</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
       <c r="A20" s="1" t="s">
         <v>37</v>
       </c>
@@ -1445,8 +1499,11 @@
       <c r="O20">
         <v>53.780029296875</v>
       </c>
-    </row>
-    <row r="21" spans="1:15">
+      <c r="P20">
+        <v>63.75</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
       <c r="A21" s="1" t="s">
         <v>38</v>
       </c>
@@ -1492,8 +1549,11 @@
       <c r="O21">
         <v>77.14990234375</v>
       </c>
-    </row>
-    <row r="22" spans="1:15">
+      <c r="P21">
+        <v>53.65</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16">
       <c r="A22" s="1" t="s">
         <v>39</v>
       </c>
@@ -1538,6 +1598,9 @@
       </c>
       <c r="O22" t="s">
         <v>31</v>
+      </c>
+      <c r="P22" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -600,7 +600,7 @@
         <v>48.080078125</v>
       </c>
       <c r="P2">
-        <v>64.92</v>
+        <v>64.919921875</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -700,7 +700,7 @@
         <v>47.050048828125</v>
       </c>
       <c r="P4">
-        <v>51.92</v>
+        <v>51.919921875</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -750,7 +750,7 @@
         <v>61.949951171875</v>
       </c>
       <c r="P5">
-        <v>60.17</v>
+        <v>60.169921875</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -800,7 +800,7 @@
         <v>46.050048828125</v>
       </c>
       <c r="P6">
-        <v>48.27</v>
+        <v>48.27001953125</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -850,7 +850,7 @@
         <v>50.72998046875</v>
       </c>
       <c r="P7">
-        <v>51.93</v>
+        <v>51.929931640625</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -900,7 +900,7 @@
         <v>57.72998046875</v>
       </c>
       <c r="P8">
-        <v>55.9</v>
+        <v>55.89990234375</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -950,7 +950,7 @@
         <v>49.280029296875</v>
       </c>
       <c r="P9">
-        <v>54.58</v>
+        <v>54.580078125</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -1000,7 +1000,7 @@
         <v>53.47998046875</v>
       </c>
       <c r="P10">
-        <v>68.34999999999999</v>
+        <v>68.35009765625</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -1100,7 +1100,7 @@
         <v>55.97998046875</v>
       </c>
       <c r="P12">
-        <v>57.3</v>
+        <v>57.300048828125</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -1150,7 +1150,7 @@
         <v>44.330078125</v>
       </c>
       <c r="P13">
-        <v>31.44</v>
+        <v>31.43994140625</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -1200,7 +1200,7 @@
         <v>78.35009765625</v>
       </c>
       <c r="P14">
-        <v>50.63</v>
+        <v>50.6298828125</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -1250,7 +1250,7 @@
         <v>57.239990234375</v>
       </c>
       <c r="P15">
-        <v>65.34</v>
+        <v>65.33984375</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -1300,7 +1300,7 @@
         <v>61.679931640625</v>
       </c>
       <c r="P16">
-        <v>49.02</v>
+        <v>49.02001953125</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -1350,7 +1350,7 @@
         <v>49.9599609375</v>
       </c>
       <c r="P17">
-        <v>44.88</v>
+        <v>44.8798828125</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -1400,7 +1400,7 @@
         <v>51.080078125</v>
       </c>
       <c r="P18">
-        <v>65.59999999999999</v>
+        <v>65.60009765625</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -1450,7 +1450,7 @@
         <v>62.050048828125</v>
       </c>
       <c r="P19">
-        <v>58.27</v>
+        <v>58.27001953125</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -1550,7 +1550,7 @@
         <v>77.14990234375</v>
       </c>
       <c r="P21">
-        <v>53.65</v>
+        <v>53.64990234375</v>
       </c>
     </row>
     <row r="22" spans="1:16">

--- a/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="40">
   <si>
     <t>Rodada 1</t>
   </si>
@@ -602,6 +602,9 @@
       <c r="P2">
         <v>64.919921875</v>
       </c>
+      <c r="Q2">
+        <v>71.78</v>
+      </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" s="1" t="s">
@@ -652,6 +655,9 @@
       <c r="P3">
         <v>63.75</v>
       </c>
+      <c r="Q3">
+        <v>73.08</v>
+      </c>
     </row>
     <row r="4" spans="1:20">
       <c r="A4" s="1" t="s">
@@ -702,6 +708,9 @@
       <c r="P4">
         <v>51.919921875</v>
       </c>
+      <c r="Q4">
+        <v>64.38</v>
+      </c>
     </row>
     <row r="5" spans="1:20">
       <c r="A5" s="1" t="s">
@@ -752,6 +761,9 @@
       <c r="P5">
         <v>60.169921875</v>
       </c>
+      <c r="Q5">
+        <v>72.28</v>
+      </c>
     </row>
     <row r="6" spans="1:20">
       <c r="A6" s="1" t="s">
@@ -802,6 +814,9 @@
       <c r="P6">
         <v>48.27001953125</v>
       </c>
+      <c r="Q6">
+        <v>87.88</v>
+      </c>
     </row>
     <row r="7" spans="1:20">
       <c r="A7" s="1" t="s">
@@ -852,6 +867,9 @@
       <c r="P7">
         <v>51.929931640625</v>
       </c>
+      <c r="Q7">
+        <v>67.09999999999999</v>
+      </c>
     </row>
     <row r="8" spans="1:20">
       <c r="A8" s="1" t="s">
@@ -902,6 +920,9 @@
       <c r="P8">
         <v>55.89990234375</v>
       </c>
+      <c r="Q8">
+        <v>103.39</v>
+      </c>
     </row>
     <row r="9" spans="1:20">
       <c r="A9" s="1" t="s">
@@ -952,6 +973,9 @@
       <c r="P9">
         <v>54.580078125</v>
       </c>
+      <c r="Q9">
+        <v>68.58</v>
+      </c>
     </row>
     <row r="10" spans="1:20">
       <c r="A10" s="1" t="s">
@@ -1002,6 +1026,9 @@
       <c r="P10">
         <v>68.35009765625</v>
       </c>
+      <c r="Q10">
+        <v>74.28</v>
+      </c>
     </row>
     <row r="11" spans="1:20">
       <c r="A11" s="1" t="s">
@@ -1052,6 +1079,9 @@
       <c r="P11">
         <v>53.5</v>
       </c>
+      <c r="Q11">
+        <v>80.04000000000001</v>
+      </c>
     </row>
     <row r="12" spans="1:20">
       <c r="A12" s="1" t="s">
@@ -1102,6 +1132,9 @@
       <c r="P12">
         <v>57.300048828125</v>
       </c>
+      <c r="Q12">
+        <v>72.48</v>
+      </c>
     </row>
     <row r="13" spans="1:20">
       <c r="A13" s="1" t="s">
@@ -1152,6 +1185,9 @@
       <c r="P13">
         <v>31.43994140625</v>
       </c>
+      <c r="Q13">
+        <v>68.69</v>
+      </c>
     </row>
     <row r="14" spans="1:20">
       <c r="A14" s="1" t="s">
@@ -1202,6 +1238,9 @@
       <c r="P14">
         <v>50.6298828125</v>
       </c>
+      <c r="Q14">
+        <v>74.58</v>
+      </c>
     </row>
     <row r="15" spans="1:20">
       <c r="A15" s="1" t="s">
@@ -1252,6 +1291,9 @@
       <c r="P15">
         <v>65.33984375</v>
       </c>
+      <c r="Q15">
+        <v>72.09999999999999</v>
+      </c>
     </row>
     <row r="16" spans="1:20">
       <c r="A16" s="1" t="s">
@@ -1302,8 +1344,11 @@
       <c r="P16">
         <v>49.02001953125</v>
       </c>
-    </row>
-    <row r="17" spans="1:16">
+      <c r="Q16">
+        <v>69.78</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17">
       <c r="A17" s="1" t="s">
         <v>34</v>
       </c>
@@ -1352,8 +1397,11 @@
       <c r="P17">
         <v>44.8798828125</v>
       </c>
-    </row>
-    <row r="18" spans="1:16">
+      <c r="Q17">
+        <v>76.69</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17">
       <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
@@ -1402,8 +1450,11 @@
       <c r="P18">
         <v>65.60009765625</v>
       </c>
-    </row>
-    <row r="19" spans="1:16">
+      <c r="Q18">
+        <v>57.68</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17">
       <c r="A19" s="1" t="s">
         <v>36</v>
       </c>
@@ -1452,8 +1503,11 @@
       <c r="P19">
         <v>58.27001953125</v>
       </c>
-    </row>
-    <row r="20" spans="1:16">
+      <c r="Q19">
+        <v>83.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17">
       <c r="A20" s="1" t="s">
         <v>37</v>
       </c>
@@ -1502,8 +1556,11 @@
       <c r="P20">
         <v>63.75</v>
       </c>
-    </row>
-    <row r="21" spans="1:16">
+      <c r="Q20">
+        <v>73.08</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17">
       <c r="A21" s="1" t="s">
         <v>38</v>
       </c>
@@ -1552,8 +1609,11 @@
       <c r="P21">
         <v>53.64990234375</v>
       </c>
-    </row>
-    <row r="22" spans="1:16">
+      <c r="Q21">
+        <v>61.8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17">
       <c r="A22" s="1" t="s">
         <v>39</v>
       </c>
@@ -1601,6 +1661,9 @@
       </c>
       <c r="P22" t="s">
         <v>27</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -603,7 +603,7 @@
         <v>64.919921875</v>
       </c>
       <c r="Q2">
-        <v>71.78</v>
+        <v>71.77978515625</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -656,7 +656,7 @@
         <v>63.75</v>
       </c>
       <c r="Q3">
-        <v>73.08</v>
+        <v>73.080078125</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -709,7 +709,7 @@
         <v>51.919921875</v>
       </c>
       <c r="Q4">
-        <v>64.38</v>
+        <v>64.3798828125</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -762,7 +762,7 @@
         <v>60.169921875</v>
       </c>
       <c r="Q5">
-        <v>72.28</v>
+        <v>72.27978515625</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -815,7 +815,7 @@
         <v>48.27001953125</v>
       </c>
       <c r="Q6">
-        <v>87.88</v>
+        <v>87.8798828125</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -868,7 +868,7 @@
         <v>51.929931640625</v>
       </c>
       <c r="Q7">
-        <v>67.09999999999999</v>
+        <v>67.10009765625</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -921,7 +921,7 @@
         <v>55.89990234375</v>
       </c>
       <c r="Q8">
-        <v>103.39</v>
+        <v>103.39013671875</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -974,7 +974,7 @@
         <v>54.580078125</v>
       </c>
       <c r="Q9">
-        <v>68.58</v>
+        <v>68.580078125</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -1027,7 +1027,7 @@
         <v>68.35009765625</v>
       </c>
       <c r="Q10">
-        <v>74.28</v>
+        <v>74.27978515625</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -1080,7 +1080,7 @@
         <v>53.5</v>
       </c>
       <c r="Q11">
-        <v>80.04000000000001</v>
+        <v>80.0400390625</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -1133,7 +1133,7 @@
         <v>57.300048828125</v>
       </c>
       <c r="Q12">
-        <v>72.48</v>
+        <v>72.47998046875</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -1186,7 +1186,7 @@
         <v>31.43994140625</v>
       </c>
       <c r="Q13">
-        <v>68.69</v>
+        <v>68.68994140625</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -1239,7 +1239,7 @@
         <v>50.6298828125</v>
       </c>
       <c r="Q14">
-        <v>74.58</v>
+        <v>74.580078125</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -1292,7 +1292,7 @@
         <v>65.33984375</v>
       </c>
       <c r="Q15">
-        <v>72.09999999999999</v>
+        <v>72.10009765625</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -1345,7 +1345,7 @@
         <v>49.02001953125</v>
       </c>
       <c r="Q16">
-        <v>69.78</v>
+        <v>69.77978515625</v>
       </c>
     </row>
     <row r="17" spans="1:17">
@@ -1398,7 +1398,7 @@
         <v>44.8798828125</v>
       </c>
       <c r="Q17">
-        <v>76.69</v>
+        <v>76.68994140625</v>
       </c>
     </row>
     <row r="18" spans="1:17">
@@ -1451,7 +1451,7 @@
         <v>65.60009765625</v>
       </c>
       <c r="Q18">
-        <v>57.68</v>
+        <v>57.679931640625</v>
       </c>
     </row>
     <row r="19" spans="1:17">
@@ -1557,7 +1557,7 @@
         <v>63.75</v>
       </c>
       <c r="Q20">
-        <v>73.08</v>
+        <v>73.080078125</v>
       </c>
     </row>
     <row r="21" spans="1:17">
@@ -1610,7 +1610,7 @@
         <v>53.64990234375</v>
       </c>
       <c r="Q21">
-        <v>61.8</v>
+        <v>61.800048828125</v>
       </c>
     </row>
     <row r="22" spans="1:17">

--- a/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="40">
   <si>
     <t>Rodada 1</t>
   </si>
@@ -82,55 +82,55 @@
     <t>Dom Camillo68</t>
   </si>
   <si>
+    <t>Fedato Futebol Clube</t>
+  </si>
+  <si>
+    <t>Gremiomaniasm</t>
+  </si>
+  <si>
+    <t>lsauer fc</t>
+  </si>
+  <si>
+    <t>Paulo Virgili FC</t>
+  </si>
+  <si>
+    <t>Pity10</t>
+  </si>
+  <si>
+    <t>pura bucha/internacional</t>
+  </si>
+  <si>
+    <t>PUXE FC</t>
+  </si>
+  <si>
+    <t>seralex</t>
+  </si>
+  <si>
+    <t>Tatols Beants F.C</t>
+  </si>
+  <si>
+    <t>TEAM LOPES 99</t>
+  </si>
+  <si>
+    <t>Texas Club 2026</t>
+  </si>
+  <si>
+    <t>TIGRE LEON</t>
+  </si>
+  <si>
     <t>FBC Colorado</t>
   </si>
   <si>
-    <t>Fedato Futebol Clube</t>
-  </si>
-  <si>
-    <t>Gremiomaniasm</t>
-  </si>
-  <si>
     <t>JV5 Tricolor Gaúcho</t>
   </si>
   <si>
-    <t>lsauer fc</t>
-  </si>
-  <si>
     <t>Mau Humor F.C.</t>
   </si>
   <si>
-    <t>Paulo Virgili FC</t>
-  </si>
-  <si>
-    <t>Pity10</t>
-  </si>
-  <si>
-    <t>pura bucha/internacional</t>
-  </si>
-  <si>
-    <t>PUXE FC</t>
-  </si>
-  <si>
     <t>Rolo Compressor ZN</t>
   </si>
   <si>
-    <t>seralex</t>
-  </si>
-  <si>
     <t>Sport Clube PAIM</t>
-  </si>
-  <si>
-    <t>Tatols Beants F.C</t>
-  </si>
-  <si>
-    <t>TEAM LOPES 99</t>
-  </si>
-  <si>
-    <t>Texas Club 2026</t>
-  </si>
-  <si>
-    <t>TIGRE LEON</t>
   </si>
   <si>
     <t>Lider_Rodada</t>
@@ -605,6 +605,9 @@
       <c r="Q2">
         <v>71.77978515625</v>
       </c>
+      <c r="R2">
+        <v>59.1201171875</v>
+      </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" s="1" t="s">
@@ -658,6 +661,9 @@
       <c r="Q3">
         <v>73.080078125</v>
       </c>
+      <c r="R3">
+        <v>65.6201171875</v>
+      </c>
     </row>
     <row r="4" spans="1:20">
       <c r="A4" s="1" t="s">
@@ -711,58 +717,64 @@
       <c r="Q4">
         <v>64.3798828125</v>
       </c>
+      <c r="R4">
+        <v>68.52001953125</v>
+      </c>
     </row>
     <row r="5" spans="1:20">
       <c r="A5" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B5">
-        <v>53.659912109375</v>
+        <v>63.89990234375</v>
       </c>
       <c r="C5">
-        <v>81.47998046875</v>
+        <v>92.77978515625</v>
       </c>
       <c r="D5">
-        <v>79.259765625</v>
+        <v>78.39990234375</v>
       </c>
       <c r="E5">
-        <v>86.43017578125</v>
+        <v>87.64990234375</v>
       </c>
       <c r="F5">
-        <v>86.419921875</v>
+        <v>89.02001953125</v>
       </c>
       <c r="G5">
-        <v>47.389892578125</v>
+        <v>62.81005859375</v>
       </c>
       <c r="H5">
-        <v>67.27001953125</v>
+        <v>105.8701171875</v>
       </c>
       <c r="I5">
-        <v>75.75</v>
+        <v>76.89990234375</v>
       </c>
       <c r="J5">
-        <v>85.9599609375</v>
+        <v>79.93994140625</v>
       </c>
       <c r="K5">
-        <v>39.469970703125</v>
+        <v>54.389892578125</v>
       </c>
       <c r="L5">
-        <v>85.16015625</v>
+        <v>91.27978515625</v>
       </c>
       <c r="M5">
-        <v>81.4501953125</v>
+        <v>81.10009765625</v>
       </c>
       <c r="N5">
-        <v>113.2900390625</v>
+        <v>136.58984375</v>
       </c>
       <c r="O5">
-        <v>61.949951171875</v>
+        <v>46.050048828125</v>
       </c>
       <c r="P5">
-        <v>60.169921875</v>
+        <v>48.27001953125</v>
       </c>
       <c r="Q5">
-        <v>72.27978515625</v>
+        <v>87.8798828125</v>
+      </c>
+      <c r="R5">
+        <v>65.919921875</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -770,52 +782,55 @@
         <v>23</v>
       </c>
       <c r="B6">
-        <v>63.89990234375</v>
+        <v>57.449951171875</v>
       </c>
       <c r="C6">
-        <v>92.77978515625</v>
+        <v>83.2001953125</v>
       </c>
       <c r="D6">
-        <v>78.39990234375</v>
+        <v>70.7998046875</v>
       </c>
       <c r="E6">
-        <v>87.64990234375</v>
+        <v>77.259765625</v>
       </c>
       <c r="F6">
-        <v>89.02001953125</v>
+        <v>69.3701171875</v>
       </c>
       <c r="G6">
-        <v>62.81005859375</v>
+        <v>52.199951171875</v>
       </c>
       <c r="H6">
-        <v>105.8701171875</v>
+        <v>39.969970703125</v>
       </c>
       <c r="I6">
-        <v>76.89990234375</v>
+        <v>60.5</v>
       </c>
       <c r="J6">
-        <v>79.93994140625</v>
+        <v>65.2998046875</v>
       </c>
       <c r="K6">
-        <v>54.389892578125</v>
+        <v>50.7900390625</v>
       </c>
       <c r="L6">
-        <v>91.27978515625</v>
+        <v>71.35986328125</v>
       </c>
       <c r="M6">
-        <v>81.10009765625</v>
+        <v>75.91015625</v>
       </c>
       <c r="N6">
-        <v>136.58984375</v>
+        <v>80.18994140625</v>
       </c>
       <c r="O6">
-        <v>46.050048828125</v>
+        <v>50.72998046875</v>
       </c>
       <c r="P6">
-        <v>48.27001953125</v>
+        <v>51.929931640625</v>
       </c>
       <c r="Q6">
-        <v>87.8798828125</v>
+        <v>67.10009765625</v>
+      </c>
+      <c r="R6">
+        <v>66.81982421875</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -823,52 +838,55 @@
         <v>24</v>
       </c>
       <c r="B7">
-        <v>57.449951171875</v>
+        <v>62.56005859375</v>
       </c>
       <c r="C7">
-        <v>83.2001953125</v>
+        <v>96.47998046875</v>
       </c>
       <c r="D7">
-        <v>70.7998046875</v>
+        <v>87.4599609375</v>
       </c>
       <c r="E7">
-        <v>77.259765625</v>
+        <v>81.43017578125</v>
       </c>
       <c r="F7">
-        <v>69.3701171875</v>
+        <v>85.669921875</v>
       </c>
       <c r="G7">
-        <v>52.199951171875</v>
+        <v>58.610107421875</v>
       </c>
       <c r="H7">
-        <v>39.969970703125</v>
+        <v>81.56982421875</v>
       </c>
       <c r="I7">
-        <v>60.5</v>
+        <v>73.35009765625</v>
       </c>
       <c r="J7">
-        <v>65.2998046875</v>
+        <v>104.68017578125</v>
       </c>
       <c r="K7">
-        <v>50.7900390625</v>
+        <v>66.89013671875</v>
       </c>
       <c r="L7">
-        <v>71.35986328125</v>
+        <v>90.4599609375</v>
       </c>
       <c r="M7">
-        <v>75.91015625</v>
+        <v>84.39990234375</v>
       </c>
       <c r="N7">
-        <v>80.18994140625</v>
+        <v>108.58984375</v>
       </c>
       <c r="O7">
-        <v>50.72998046875</v>
+        <v>49.280029296875</v>
       </c>
       <c r="P7">
-        <v>51.929931640625</v>
+        <v>54.580078125</v>
       </c>
       <c r="Q7">
-        <v>67.10009765625</v>
+        <v>68.580078125</v>
+      </c>
+      <c r="R7">
+        <v>70.81982421875</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -876,52 +894,55 @@
         <v>25</v>
       </c>
       <c r="B8">
-        <v>47.860107421875</v>
+        <v>84.259765625</v>
       </c>
       <c r="C8">
-        <v>72.18017578125</v>
+        <v>82.60986328125</v>
       </c>
       <c r="D8">
-        <v>97.39990234375</v>
+        <v>81.25</v>
       </c>
       <c r="E8">
-        <v>81.64990234375</v>
+        <v>45.64990234375</v>
       </c>
       <c r="F8">
-        <v>84.81982421875</v>
+        <v>72.27001953125</v>
       </c>
       <c r="G8">
-        <v>62.010009765625</v>
+        <v>53.4599609375</v>
       </c>
       <c r="H8">
-        <v>77.06982421875</v>
+        <v>58.669921875</v>
       </c>
       <c r="I8">
-        <v>80.0498046875</v>
+        <v>45.699951171875</v>
       </c>
       <c r="J8">
-        <v>59.010009765625</v>
+        <v>69.33984375</v>
       </c>
       <c r="K8">
-        <v>60.169921875</v>
+        <v>84.06982421875</v>
       </c>
       <c r="L8">
-        <v>82.81005859375</v>
+        <v>53.030029296875</v>
       </c>
       <c r="M8">
-        <v>77.35009765625</v>
+        <v>83.7001953125</v>
       </c>
       <c r="N8">
-        <v>115.43994140625</v>
+        <v>90.14990234375</v>
       </c>
       <c r="O8">
-        <v>57.72998046875</v>
+        <v>49.43994140625</v>
       </c>
       <c r="P8">
-        <v>55.89990234375</v>
+        <v>53.5</v>
       </c>
       <c r="Q8">
-        <v>103.39013671875</v>
+        <v>80.0400390625</v>
+      </c>
+      <c r="R8">
+        <v>61.449951171875</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -929,52 +950,55 @@
         <v>26</v>
       </c>
       <c r="B9">
-        <v>62.56005859375</v>
+        <v>64.56005859375</v>
       </c>
       <c r="C9">
-        <v>96.47998046875</v>
+        <v>105.5</v>
       </c>
       <c r="D9">
-        <v>87.4599609375</v>
+        <v>81.16015625</v>
       </c>
       <c r="E9">
-        <v>81.43017578125</v>
+        <v>66.75</v>
       </c>
       <c r="F9">
-        <v>85.669921875</v>
+        <v>107.56005859375</v>
       </c>
       <c r="G9">
-        <v>58.610107421875</v>
+        <v>71.60986328125</v>
       </c>
       <c r="H9">
-        <v>81.56982421875</v>
+        <v>94.8701171875</v>
       </c>
       <c r="I9">
-        <v>73.35009765625</v>
+        <v>74.0498046875</v>
       </c>
       <c r="J9">
-        <v>104.68017578125</v>
+        <v>90.8798828125</v>
       </c>
       <c r="K9">
-        <v>66.89013671875</v>
+        <v>47.570068359375</v>
       </c>
       <c r="L9">
-        <v>90.4599609375</v>
+        <v>69.25</v>
       </c>
       <c r="M9">
-        <v>84.39990234375</v>
+        <v>84</v>
       </c>
       <c r="N9">
-        <v>108.58984375</v>
+        <v>101.990234375</v>
       </c>
       <c r="O9">
-        <v>49.280029296875</v>
+        <v>55.97998046875</v>
       </c>
       <c r="P9">
-        <v>54.580078125</v>
+        <v>57.300048828125</v>
       </c>
       <c r="Q9">
-        <v>68.580078125</v>
+        <v>72.47998046875</v>
+      </c>
+      <c r="R9">
+        <v>75.72021484375</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -982,52 +1006,55 @@
         <v>27</v>
       </c>
       <c r="B10">
-        <v>73.9599609375</v>
+        <v>50.260009765625</v>
       </c>
       <c r="C10">
-        <v>92.89990234375</v>
+        <v>57.550048828125</v>
       </c>
       <c r="D10">
-        <v>81.759765625</v>
+        <v>70.83984375</v>
       </c>
       <c r="E10">
-        <v>53.25</v>
+        <v>27.4300537109375</v>
       </c>
       <c r="F10">
-        <v>83.31982421875</v>
+        <v>39.340087890625</v>
       </c>
       <c r="G10">
-        <v>54.81005859375</v>
+        <v>71.66015625</v>
       </c>
       <c r="H10">
-        <v>79.919921875</v>
+        <v>34.469970703125</v>
       </c>
       <c r="I10">
-        <v>72.25</v>
+        <v>40.280029296875</v>
       </c>
       <c r="J10">
-        <v>59.3798828125</v>
+        <v>43.659912109375</v>
       </c>
       <c r="K10">
-        <v>66.27001953125</v>
+        <v>55.1201171875</v>
       </c>
       <c r="L10">
-        <v>105.9599609375</v>
+        <v>59.659912109375</v>
       </c>
       <c r="M10">
-        <v>77.25</v>
+        <v>69.31982421875</v>
       </c>
       <c r="N10">
-        <v>122.490234375</v>
+        <v>57.9599609375</v>
       </c>
       <c r="O10">
-        <v>53.47998046875</v>
+        <v>44.330078125</v>
       </c>
       <c r="P10">
-        <v>68.35009765625</v>
+        <v>31.43994140625</v>
       </c>
       <c r="Q10">
-        <v>74.27978515625</v>
+        <v>68.68994140625</v>
+      </c>
+      <c r="R10">
+        <v>33.85009765625</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -1035,52 +1062,55 @@
         <v>28</v>
       </c>
       <c r="B11">
-        <v>84.259765625</v>
+        <v>64.56005859375</v>
       </c>
       <c r="C11">
-        <v>82.60986328125</v>
+        <v>86.60009765625</v>
       </c>
       <c r="D11">
-        <v>81.25</v>
+        <v>70.35986328125</v>
       </c>
       <c r="E11">
-        <v>45.64990234375</v>
+        <v>34.89990234375</v>
       </c>
       <c r="F11">
-        <v>72.27001953125</v>
+        <v>88.6201171875</v>
       </c>
       <c r="G11">
-        <v>53.4599609375</v>
+        <v>58.889892578125</v>
       </c>
       <c r="H11">
-        <v>58.669921875</v>
+        <v>60.070068359375</v>
       </c>
       <c r="I11">
-        <v>45.699951171875</v>
+        <v>79.85009765625</v>
       </c>
       <c r="J11">
-        <v>69.33984375</v>
+        <v>101.9599609375</v>
       </c>
       <c r="K11">
-        <v>84.06982421875</v>
+        <v>82.169921875</v>
       </c>
       <c r="L11">
-        <v>53.030029296875</v>
+        <v>101.35986328125</v>
       </c>
       <c r="M11">
-        <v>83.7001953125</v>
+        <v>64.2001953125</v>
       </c>
       <c r="N11">
-        <v>90.14990234375</v>
+        <v>121.08984375</v>
       </c>
       <c r="O11">
-        <v>49.43994140625</v>
+        <v>78.35009765625</v>
       </c>
       <c r="P11">
-        <v>53.5</v>
+        <v>50.6298828125</v>
       </c>
       <c r="Q11">
-        <v>80.0400390625</v>
+        <v>74.580078125</v>
+      </c>
+      <c r="R11">
+        <v>84.919921875</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -1088,52 +1118,55 @@
         <v>29</v>
       </c>
       <c r="B12">
-        <v>64.56005859375</v>
+        <v>60.159912109375</v>
       </c>
       <c r="C12">
-        <v>105.5</v>
+        <v>64.580078125</v>
       </c>
       <c r="D12">
-        <v>81.16015625</v>
+        <v>88.759765625</v>
       </c>
       <c r="E12">
-        <v>66.75</v>
+        <v>109.75</v>
       </c>
       <c r="F12">
-        <v>107.56005859375</v>
+        <v>81.47021484375</v>
       </c>
       <c r="G12">
-        <v>71.60986328125</v>
+        <v>56.39990234375</v>
       </c>
       <c r="H12">
-        <v>94.8701171875</v>
+        <v>59.56005859375</v>
       </c>
       <c r="I12">
-        <v>74.0498046875</v>
+        <v>75.0498046875</v>
       </c>
       <c r="J12">
-        <v>90.8798828125</v>
+        <v>96.27978515625</v>
       </c>
       <c r="K12">
-        <v>47.570068359375</v>
+        <v>78.89013671875</v>
       </c>
       <c r="L12">
-        <v>69.25</v>
+        <v>86.66015625</v>
       </c>
       <c r="M12">
-        <v>84</v>
+        <v>80.7001953125</v>
       </c>
       <c r="N12">
-        <v>101.990234375</v>
+        <v>108.58984375</v>
       </c>
       <c r="O12">
-        <v>55.97998046875</v>
+        <v>61.679931640625</v>
       </c>
       <c r="P12">
-        <v>57.300048828125</v>
+        <v>49.02001953125</v>
       </c>
       <c r="Q12">
-        <v>72.47998046875</v>
+        <v>69.77978515625</v>
+      </c>
+      <c r="R12">
+        <v>93.22021484375</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -1141,52 +1174,55 @@
         <v>30</v>
       </c>
       <c r="B13">
-        <v>50.260009765625</v>
+        <v>66.85986328125</v>
       </c>
       <c r="C13">
-        <v>57.550048828125</v>
+        <v>92.7001953125</v>
       </c>
       <c r="D13">
-        <v>70.83984375</v>
+        <v>72.740234375</v>
       </c>
       <c r="E13">
-        <v>27.4300537109375</v>
+        <v>50.590087890625</v>
       </c>
       <c r="F13">
-        <v>39.340087890625</v>
+        <v>81.169921875</v>
       </c>
       <c r="G13">
-        <v>71.66015625</v>
+        <v>62.919921875</v>
       </c>
       <c r="H13">
-        <v>34.469970703125</v>
+        <v>87.009765625</v>
       </c>
       <c r="I13">
-        <v>40.280029296875</v>
+        <v>69.89990234375</v>
       </c>
       <c r="J13">
-        <v>43.659912109375</v>
+        <v>91.14013671875</v>
       </c>
       <c r="K13">
-        <v>55.1201171875</v>
+        <v>47.8701171875</v>
       </c>
       <c r="L13">
-        <v>59.659912109375</v>
+        <v>83.47998046875</v>
       </c>
       <c r="M13">
-        <v>69.31982421875</v>
+        <v>63.800048828125</v>
       </c>
       <c r="N13">
-        <v>57.9599609375</v>
+        <v>110.35009765625</v>
       </c>
       <c r="O13">
-        <v>44.330078125</v>
+        <v>51.080078125</v>
       </c>
       <c r="P13">
-        <v>31.43994140625</v>
+        <v>65.60009765625</v>
       </c>
       <c r="Q13">
-        <v>68.68994140625</v>
+        <v>57.679931640625</v>
+      </c>
+      <c r="R13">
+        <v>78.02001953125</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -1194,52 +1230,55 @@
         <v>31</v>
       </c>
       <c r="B14">
-        <v>64.56005859375</v>
+        <v>58.9599609375</v>
       </c>
       <c r="C14">
-        <v>86.60009765625</v>
+        <v>79.27978515625</v>
       </c>
       <c r="D14">
-        <v>70.35986328125</v>
+        <v>86.66015625</v>
       </c>
       <c r="E14">
-        <v>34.89990234375</v>
+        <v>80.35986328125</v>
       </c>
       <c r="F14">
-        <v>88.6201171875</v>
+        <v>98.52001953125</v>
       </c>
       <c r="G14">
-        <v>58.889892578125</v>
+        <v>77.41015625</v>
       </c>
       <c r="H14">
-        <v>60.070068359375</v>
+        <v>71.3701171875</v>
       </c>
       <c r="I14">
-        <v>79.85009765625</v>
+        <v>80.75</v>
       </c>
       <c r="J14">
-        <v>101.9599609375</v>
+        <v>84.43994140625</v>
       </c>
       <c r="K14">
-        <v>82.169921875</v>
+        <v>67.27001953125</v>
       </c>
       <c r="L14">
-        <v>101.35986328125</v>
+        <v>94.06005859375</v>
       </c>
       <c r="M14">
-        <v>64.2001953125</v>
+        <v>84.5</v>
       </c>
       <c r="N14">
-        <v>121.08984375</v>
+        <v>97.7900390625</v>
       </c>
       <c r="O14">
-        <v>78.35009765625</v>
+        <v>62.050048828125</v>
       </c>
       <c r="P14">
-        <v>50.6298828125</v>
+        <v>58.27001953125</v>
       </c>
       <c r="Q14">
-        <v>74.580078125</v>
+        <v>83.5</v>
+      </c>
+      <c r="R14">
+        <v>62.6201171875</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -1247,52 +1286,55 @@
         <v>32</v>
       </c>
       <c r="B15">
-        <v>59.25</v>
+        <v>68.06005859375</v>
       </c>
       <c r="C15">
-        <v>73.77978515625</v>
+        <v>82.18017578125</v>
       </c>
       <c r="D15">
-        <v>93.759765625</v>
+        <v>105.759765625</v>
       </c>
       <c r="E15">
-        <v>51.929931640625</v>
+        <v>65.14990234375</v>
       </c>
       <c r="F15">
-        <v>74.77001953125</v>
+        <v>93.02001953125</v>
       </c>
       <c r="G15">
-        <v>66.509765625</v>
+        <v>83</v>
       </c>
       <c r="H15">
-        <v>82.56982421875</v>
+        <v>76.97021484375</v>
       </c>
       <c r="I15">
-        <v>76.25</v>
+        <v>76.4501953125</v>
       </c>
       <c r="J15">
-        <v>56.090087890625</v>
+        <v>85.85009765625</v>
       </c>
       <c r="K15">
-        <v>40.8701171875</v>
+        <v>58.090087890625</v>
       </c>
       <c r="L15">
-        <v>82.4599609375</v>
+        <v>88.759765625</v>
       </c>
       <c r="M15">
-        <v>92.35009765625</v>
+        <v>86.66015625</v>
       </c>
       <c r="N15">
-        <v>97.68994140625</v>
+        <v>106.39013671875</v>
       </c>
       <c r="O15">
-        <v>57.239990234375</v>
+        <v>53.780029296875</v>
       </c>
       <c r="P15">
-        <v>65.33984375</v>
+        <v>63.75</v>
       </c>
       <c r="Q15">
-        <v>72.10009765625</v>
+        <v>73.080078125</v>
+      </c>
+      <c r="R15">
+        <v>65.6201171875</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -1300,370 +1342,391 @@
         <v>33</v>
       </c>
       <c r="B16">
-        <v>60.159912109375</v>
+        <v>51.260009765625</v>
       </c>
       <c r="C16">
-        <v>64.580078125</v>
+        <v>95.5</v>
       </c>
       <c r="D16">
-        <v>88.759765625</v>
+        <v>61.159912109375</v>
       </c>
       <c r="E16">
-        <v>109.75</v>
+        <v>67.75</v>
       </c>
       <c r="F16">
-        <v>81.47021484375</v>
+        <v>75.419921875</v>
       </c>
       <c r="G16">
-        <v>56.39990234375</v>
+        <v>54.2099609375</v>
       </c>
       <c r="H16">
-        <v>59.56005859375</v>
+        <v>56.669921875</v>
       </c>
       <c r="I16">
-        <v>75.0498046875</v>
+        <v>67.64990234375</v>
       </c>
       <c r="J16">
-        <v>96.27978515625</v>
+        <v>109.43994140625</v>
       </c>
       <c r="K16">
-        <v>78.89013671875</v>
+        <v>63.570068359375</v>
       </c>
       <c r="L16">
-        <v>86.66015625</v>
+        <v>101.41015625</v>
       </c>
       <c r="M16">
-        <v>80.7001953125</v>
+        <v>70.2998046875</v>
       </c>
       <c r="N16">
-        <v>108.58984375</v>
+        <v>129.16015625</v>
       </c>
       <c r="O16">
-        <v>61.679931640625</v>
+        <v>77.14990234375</v>
       </c>
       <c r="P16">
-        <v>49.02001953125</v>
+        <v>53.64990234375</v>
       </c>
       <c r="Q16">
-        <v>69.77978515625</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17">
+        <v>61.800048828125</v>
+      </c>
+      <c r="R16">
+        <v>45.610107421875</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18">
       <c r="A17" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B17">
-        <v>61.659912109375</v>
+        <v>53.659912109375</v>
       </c>
       <c r="C17">
-        <v>69.5</v>
+        <v>81.47998046875</v>
       </c>
       <c r="D17">
-        <v>83.64990234375</v>
+        <v>79.259765625</v>
       </c>
       <c r="E17">
-        <v>51.72998046875</v>
+        <v>86.43017578125</v>
       </c>
       <c r="F17">
-        <v>82.1298828125</v>
+        <v>86.419921875</v>
       </c>
       <c r="G17">
-        <v>76.68994140625</v>
+        <v>47.389892578125</v>
       </c>
       <c r="H17">
-        <v>50.969970703125</v>
+        <v>67.27001953125</v>
       </c>
       <c r="I17">
-        <v>74.85009765625</v>
+        <v>75.75</v>
       </c>
       <c r="J17">
-        <v>90.0400390625</v>
+        <v>85.9599609375</v>
       </c>
       <c r="K17">
-        <v>38.3701171875</v>
+        <v>39.469970703125</v>
       </c>
       <c r="L17">
-        <v>70.35986328125</v>
+        <v>85.16015625</v>
       </c>
       <c r="M17">
-        <v>71.60009765625</v>
+        <v>81.4501953125</v>
       </c>
       <c r="N17">
-        <v>92.490234375</v>
+        <v>113.2900390625</v>
       </c>
       <c r="O17">
-        <v>49.9599609375</v>
+        <v>61.949951171875</v>
       </c>
       <c r="P17">
-        <v>44.8798828125</v>
+        <v>60.169921875</v>
       </c>
       <c r="Q17">
-        <v>76.68994140625</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17">
+        <v>72.27978515625</v>
+      </c>
+      <c r="R17">
+        <v>65.31982421875</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18">
       <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B18">
-        <v>66.85986328125</v>
+        <v>47.860107421875</v>
       </c>
       <c r="C18">
-        <v>92.7001953125</v>
+        <v>72.18017578125</v>
       </c>
       <c r="D18">
-        <v>72.740234375</v>
+        <v>97.39990234375</v>
       </c>
       <c r="E18">
-        <v>50.590087890625</v>
+        <v>81.64990234375</v>
       </c>
       <c r="F18">
-        <v>81.169921875</v>
+        <v>84.81982421875</v>
       </c>
       <c r="G18">
-        <v>62.919921875</v>
+        <v>62.010009765625</v>
       </c>
       <c r="H18">
-        <v>87.009765625</v>
+        <v>77.06982421875</v>
       </c>
       <c r="I18">
-        <v>69.89990234375</v>
+        <v>80.0498046875</v>
       </c>
       <c r="J18">
-        <v>91.14013671875</v>
+        <v>59.010009765625</v>
       </c>
       <c r="K18">
-        <v>47.8701171875</v>
+        <v>60.169921875</v>
       </c>
       <c r="L18">
-        <v>83.47998046875</v>
+        <v>82.81005859375</v>
       </c>
       <c r="M18">
-        <v>63.800048828125</v>
+        <v>77.35009765625</v>
       </c>
       <c r="N18">
-        <v>110.35009765625</v>
+        <v>115.43994140625</v>
       </c>
       <c r="O18">
-        <v>51.080078125</v>
+        <v>57.72998046875</v>
       </c>
       <c r="P18">
-        <v>65.60009765625</v>
+        <v>55.89990234375</v>
       </c>
       <c r="Q18">
-        <v>57.679931640625</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17">
+        <v>103.39013671875</v>
+      </c>
+      <c r="R18">
+        <v>60.1201171875</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18">
       <c r="A19" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B19">
-        <v>58.9599609375</v>
+        <v>73.9599609375</v>
       </c>
       <c r="C19">
-        <v>79.27978515625</v>
+        <v>92.89990234375</v>
       </c>
       <c r="D19">
-        <v>86.66015625</v>
+        <v>81.759765625</v>
       </c>
       <c r="E19">
-        <v>80.35986328125</v>
+        <v>53.25</v>
       </c>
       <c r="F19">
-        <v>98.52001953125</v>
+        <v>83.31982421875</v>
       </c>
       <c r="G19">
-        <v>77.41015625</v>
+        <v>54.81005859375</v>
       </c>
       <c r="H19">
-        <v>71.3701171875</v>
+        <v>79.919921875</v>
       </c>
       <c r="I19">
-        <v>80.75</v>
+        <v>72.25</v>
       </c>
       <c r="J19">
-        <v>84.43994140625</v>
+        <v>59.3798828125</v>
       </c>
       <c r="K19">
-        <v>67.27001953125</v>
+        <v>66.27001953125</v>
       </c>
       <c r="L19">
-        <v>94.06005859375</v>
+        <v>105.9599609375</v>
       </c>
       <c r="M19">
-        <v>84.5</v>
+        <v>77.25</v>
       </c>
       <c r="N19">
-        <v>97.7900390625</v>
+        <v>122.490234375</v>
       </c>
       <c r="O19">
-        <v>62.050048828125</v>
+        <v>53.47998046875</v>
       </c>
       <c r="P19">
-        <v>58.27001953125</v>
+        <v>68.35009765625</v>
       </c>
       <c r="Q19">
-        <v>83.5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17">
+        <v>74.27978515625</v>
+      </c>
+      <c r="R19">
+        <v>71.6201171875</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18">
       <c r="A20" s="1" t="s">
         <v>37</v>
       </c>
       <c r="B20">
-        <v>68.06005859375</v>
+        <v>59.25</v>
       </c>
       <c r="C20">
-        <v>82.18017578125</v>
+        <v>73.77978515625</v>
       </c>
       <c r="D20">
-        <v>105.759765625</v>
+        <v>93.759765625</v>
       </c>
       <c r="E20">
-        <v>65.14990234375</v>
+        <v>51.929931640625</v>
       </c>
       <c r="F20">
-        <v>93.02001953125</v>
+        <v>74.77001953125</v>
       </c>
       <c r="G20">
-        <v>83</v>
+        <v>66.509765625</v>
       </c>
       <c r="H20">
-        <v>76.97021484375</v>
+        <v>82.56982421875</v>
       </c>
       <c r="I20">
-        <v>76.4501953125</v>
+        <v>76.25</v>
       </c>
       <c r="J20">
-        <v>85.85009765625</v>
+        <v>56.090087890625</v>
       </c>
       <c r="K20">
-        <v>58.090087890625</v>
+        <v>40.8701171875</v>
       </c>
       <c r="L20">
-        <v>88.759765625</v>
+        <v>82.4599609375</v>
       </c>
       <c r="M20">
-        <v>86.66015625</v>
+        <v>92.35009765625</v>
       </c>
       <c r="N20">
-        <v>106.39013671875</v>
+        <v>97.68994140625</v>
       </c>
       <c r="O20">
-        <v>53.780029296875</v>
+        <v>57.239990234375</v>
       </c>
       <c r="P20">
-        <v>63.75</v>
+        <v>65.33984375</v>
       </c>
       <c r="Q20">
-        <v>73.080078125</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17">
+        <v>72.10009765625</v>
+      </c>
+      <c r="R20">
+        <v>74.1201171875</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18">
       <c r="A21" s="1" t="s">
         <v>38</v>
       </c>
       <c r="B21">
-        <v>51.260009765625</v>
+        <v>61.659912109375</v>
       </c>
       <c r="C21">
-        <v>95.5</v>
+        <v>69.5</v>
       </c>
       <c r="D21">
-        <v>61.159912109375</v>
+        <v>83.64990234375</v>
       </c>
       <c r="E21">
-        <v>67.75</v>
+        <v>51.72998046875</v>
       </c>
       <c r="F21">
-        <v>75.419921875</v>
+        <v>82.1298828125</v>
       </c>
       <c r="G21">
-        <v>54.2099609375</v>
+        <v>76.68994140625</v>
       </c>
       <c r="H21">
-        <v>56.669921875</v>
+        <v>50.969970703125</v>
       </c>
       <c r="I21">
-        <v>67.64990234375</v>
+        <v>74.85009765625</v>
       </c>
       <c r="J21">
-        <v>109.43994140625</v>
+        <v>90.0400390625</v>
       </c>
       <c r="K21">
-        <v>63.570068359375</v>
+        <v>38.3701171875</v>
       </c>
       <c r="L21">
-        <v>101.41015625</v>
+        <v>70.35986328125</v>
       </c>
       <c r="M21">
-        <v>70.2998046875</v>
+        <v>71.60009765625</v>
       </c>
       <c r="N21">
-        <v>129.16015625</v>
+        <v>92.490234375</v>
       </c>
       <c r="O21">
-        <v>77.14990234375</v>
+        <v>49.9599609375</v>
       </c>
       <c r="P21">
-        <v>53.64990234375</v>
+        <v>44.8798828125</v>
       </c>
       <c r="Q21">
-        <v>61.800048828125</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17">
+        <v>76.68994140625</v>
+      </c>
+      <c r="R21">
+        <v>58.64990234375</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18">
       <c r="A22" s="1" t="s">
         <v>39</v>
       </c>
       <c r="B22" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C22" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D22" t="s">
         <v>20</v>
       </c>
       <c r="E22" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F22" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="G22" t="s">
         <v>20</v>
       </c>
       <c r="H22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I22" t="s">
+        <v>31</v>
+      </c>
+      <c r="J22" t="s">
+        <v>33</v>
+      </c>
+      <c r="K22" t="s">
+        <v>25</v>
+      </c>
+      <c r="L22" t="s">
         <v>36</v>
       </c>
-      <c r="J22" t="s">
-        <v>38</v>
-      </c>
-      <c r="K22" t="s">
+      <c r="M22" t="s">
+        <v>37</v>
+      </c>
+      <c r="N22" t="s">
+        <v>22</v>
+      </c>
+      <c r="O22" t="s">
         <v>28</v>
       </c>
-      <c r="L22" t="s">
-        <v>27</v>
-      </c>
-      <c r="M22" t="s">
-        <v>32</v>
-      </c>
-      <c r="N22" t="s">
-        <v>23</v>
-      </c>
-      <c r="O22" t="s">
-        <v>31</v>
-      </c>
       <c r="P22" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="Q22" t="s">
-        <v>25</v>
+        <v>35</v>
+      </c>
+      <c r="R22" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/liga_serie_B/datasets_liga_serie_B/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="40">
   <si>
     <t>Rodada 1</t>
   </si>
@@ -82,15 +82,24 @@
     <t>Dom Camillo68</t>
   </si>
   <si>
+    <t>FBC Colorado</t>
+  </si>
+  <si>
     <t>Fedato Futebol Clube</t>
   </si>
   <si>
     <t>Gremiomaniasm</t>
   </si>
   <si>
+    <t>JV5 Tricolor Gaúcho</t>
+  </si>
+  <si>
     <t>lsauer fc</t>
   </si>
   <si>
+    <t>Mau Humor F.C.</t>
+  </si>
+  <si>
     <t>Paulo Virgili FC</t>
   </si>
   <si>
@@ -103,9 +112,15 @@
     <t>PUXE FC</t>
   </si>
   <si>
+    <t>Rolo Compressor ZN</t>
+  </si>
+  <si>
     <t>seralex</t>
   </si>
   <si>
+    <t>Sport Clube PAIM</t>
+  </si>
+  <si>
     <t>Tatols Beants F.C</t>
   </si>
   <si>
@@ -116,21 +131,6 @@
   </si>
   <si>
     <t>TIGRE LEON</t>
-  </si>
-  <si>
-    <t>FBC Colorado</t>
-  </si>
-  <si>
-    <t>JV5 Tricolor Gaúcho</t>
-  </si>
-  <si>
-    <t>Mau Humor F.C.</t>
-  </si>
-  <si>
-    <t>Rolo Compressor ZN</t>
-  </si>
-  <si>
-    <t>Sport Clube PAIM</t>
   </si>
   <si>
     <t>Lider_Rodada</t>
@@ -608,6 +608,9 @@
       <c r="R2">
         <v>59.1201171875</v>
       </c>
+      <c r="S2">
+        <v>113.0498046875</v>
+      </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" s="1" t="s">
@@ -664,6 +667,9 @@
       <c r="R3">
         <v>65.6201171875</v>
       </c>
+      <c r="S3">
+        <v>109.5</v>
+      </c>
     </row>
     <row r="4" spans="1:20">
       <c r="A4" s="1" t="s">
@@ -720,61 +726,67 @@
       <c r="R4">
         <v>68.52001953125</v>
       </c>
+      <c r="S4">
+        <v>121.7998046875</v>
+      </c>
     </row>
     <row r="5" spans="1:20">
       <c r="A5" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B5">
-        <v>63.89990234375</v>
+        <v>53.659912109375</v>
       </c>
       <c r="C5">
-        <v>92.77978515625</v>
+        <v>81.47998046875</v>
       </c>
       <c r="D5">
-        <v>78.39990234375</v>
+        <v>79.259765625</v>
       </c>
       <c r="E5">
-        <v>87.64990234375</v>
+        <v>86.43017578125</v>
       </c>
       <c r="F5">
-        <v>89.02001953125</v>
+        <v>86.419921875</v>
       </c>
       <c r="G5">
-        <v>62.81005859375</v>
+        <v>47.389892578125</v>
       </c>
       <c r="H5">
-        <v>105.8701171875</v>
+        <v>67.27001953125</v>
       </c>
       <c r="I5">
-        <v>76.89990234375</v>
+        <v>75.75</v>
       </c>
       <c r="J5">
-        <v>79.93994140625</v>
+        <v>85.9599609375</v>
       </c>
       <c r="K5">
-        <v>54.389892578125</v>
+        <v>39.469970703125</v>
       </c>
       <c r="L5">
-        <v>91.27978515625</v>
+        <v>85.16015625</v>
       </c>
       <c r="M5">
-        <v>81.10009765625</v>
+        <v>81.4501953125</v>
       </c>
       <c r="N5">
-        <v>136.58984375</v>
+        <v>113.2900390625</v>
       </c>
       <c r="O5">
-        <v>46.050048828125</v>
+        <v>61.949951171875</v>
       </c>
       <c r="P5">
-        <v>48.27001953125</v>
+        <v>60.169921875</v>
       </c>
       <c r="Q5">
-        <v>87.8798828125</v>
+        <v>72.27978515625</v>
       </c>
       <c r="R5">
-        <v>65.919921875</v>
+        <v>65.31982421875</v>
+      </c>
+      <c r="S5">
+        <v>106.64990234375</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -782,55 +794,58 @@
         <v>23</v>
       </c>
       <c r="B6">
-        <v>57.449951171875</v>
+        <v>63.89990234375</v>
       </c>
       <c r="C6">
-        <v>83.2001953125</v>
+        <v>92.77978515625</v>
       </c>
       <c r="D6">
-        <v>70.7998046875</v>
+        <v>78.39990234375</v>
       </c>
       <c r="E6">
-        <v>77.259765625</v>
+        <v>87.64990234375</v>
       </c>
       <c r="F6">
-        <v>69.3701171875</v>
+        <v>89.02001953125</v>
       </c>
       <c r="G6">
-        <v>52.199951171875</v>
+        <v>62.81005859375</v>
       </c>
       <c r="H6">
-        <v>39.969970703125</v>
+        <v>105.8701171875</v>
       </c>
       <c r="I6">
-        <v>60.5</v>
+        <v>76.89990234375</v>
       </c>
       <c r="J6">
-        <v>65.2998046875</v>
+        <v>79.93994140625</v>
       </c>
       <c r="K6">
-        <v>50.7900390625</v>
+        <v>54.389892578125</v>
       </c>
       <c r="L6">
-        <v>71.35986328125</v>
+        <v>91.27978515625</v>
       </c>
       <c r="M6">
-        <v>75.91015625</v>
+        <v>81.10009765625</v>
       </c>
       <c r="N6">
-        <v>80.18994140625</v>
+        <v>136.58984375</v>
       </c>
       <c r="O6">
-        <v>50.72998046875</v>
+        <v>46.050048828125</v>
       </c>
       <c r="P6">
-        <v>51.929931640625</v>
+        <v>48.27001953125</v>
       </c>
       <c r="Q6">
-        <v>67.10009765625</v>
+        <v>87.8798828125</v>
       </c>
       <c r="R6">
-        <v>66.81982421875</v>
+        <v>65.919921875</v>
+      </c>
+      <c r="S6">
+        <v>116.10009765625</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -838,55 +853,58 @@
         <v>24</v>
       </c>
       <c r="B7">
-        <v>62.56005859375</v>
+        <v>57.449951171875</v>
       </c>
       <c r="C7">
-        <v>96.47998046875</v>
+        <v>83.2001953125</v>
       </c>
       <c r="D7">
-        <v>87.4599609375</v>
+        <v>70.7998046875</v>
       </c>
       <c r="E7">
-        <v>81.43017578125</v>
+        <v>77.259765625</v>
       </c>
       <c r="F7">
-        <v>85.669921875</v>
+        <v>69.3701171875</v>
       </c>
       <c r="G7">
-        <v>58.610107421875</v>
+        <v>52.199951171875</v>
       </c>
       <c r="H7">
-        <v>81.56982421875</v>
+        <v>39.969970703125</v>
       </c>
       <c r="I7">
-        <v>73.35009765625</v>
+        <v>60.5</v>
       </c>
       <c r="J7">
-        <v>104.68017578125</v>
+        <v>65.2998046875</v>
       </c>
       <c r="K7">
-        <v>66.89013671875</v>
+        <v>50.7900390625</v>
       </c>
       <c r="L7">
-        <v>90.4599609375</v>
+        <v>71.35986328125</v>
       </c>
       <c r="M7">
-        <v>84.39990234375</v>
+        <v>75.91015625</v>
       </c>
       <c r="N7">
-        <v>108.58984375</v>
+        <v>80.18994140625</v>
       </c>
       <c r="O7">
-        <v>49.280029296875</v>
+        <v>50.72998046875</v>
       </c>
       <c r="P7">
-        <v>54.580078125</v>
+        <v>51.929931640625</v>
       </c>
       <c r="Q7">
-        <v>68.580078125</v>
+        <v>67.10009765625</v>
       </c>
       <c r="R7">
-        <v>70.81982421875</v>
+        <v>66.81982421875</v>
+      </c>
+      <c r="S7">
+        <v>115.60009765625</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -894,55 +912,58 @@
         <v>25</v>
       </c>
       <c r="B8">
-        <v>84.259765625</v>
+        <v>47.860107421875</v>
       </c>
       <c r="C8">
-        <v>82.60986328125</v>
+        <v>72.18017578125</v>
       </c>
       <c r="D8">
-        <v>81.25</v>
+        <v>97.39990234375</v>
       </c>
       <c r="E8">
-        <v>45.64990234375</v>
+        <v>81.64990234375</v>
       </c>
       <c r="F8">
-        <v>72.27001953125</v>
+        <v>84.81982421875</v>
       </c>
       <c r="G8">
-        <v>53.4599609375</v>
+        <v>62.010009765625</v>
       </c>
       <c r="H8">
-        <v>58.669921875</v>
+        <v>77.06982421875</v>
       </c>
       <c r="I8">
-        <v>45.699951171875</v>
+        <v>80.0498046875</v>
       </c>
       <c r="J8">
-        <v>69.33984375</v>
+        <v>59.010009765625</v>
       </c>
       <c r="K8">
-        <v>84.06982421875</v>
+        <v>60.169921875</v>
       </c>
       <c r="L8">
-        <v>53.030029296875</v>
+        <v>82.81005859375</v>
       </c>
       <c r="M8">
-        <v>83.7001953125</v>
+        <v>77.35009765625</v>
       </c>
       <c r="N8">
-        <v>90.14990234375</v>
+        <v>115.43994140625</v>
       </c>
       <c r="O8">
-        <v>49.43994140625</v>
+        <v>57.72998046875</v>
       </c>
       <c r="P8">
-        <v>53.5</v>
+        <v>55.89990234375</v>
       </c>
       <c r="Q8">
-        <v>80.0400390625</v>
+        <v>103.39013671875</v>
       </c>
       <c r="R8">
-        <v>61.449951171875</v>
+        <v>60.1201171875</v>
+      </c>
+      <c r="S8">
+        <v>132.9501953125</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -950,55 +971,58 @@
         <v>26</v>
       </c>
       <c r="B9">
-        <v>64.56005859375</v>
+        <v>62.56005859375</v>
       </c>
       <c r="C9">
-        <v>105.5</v>
+        <v>96.47998046875</v>
       </c>
       <c r="D9">
-        <v>81.16015625</v>
+        <v>87.4599609375</v>
       </c>
       <c r="E9">
-        <v>66.75</v>
+        <v>81.43017578125</v>
       </c>
       <c r="F9">
-        <v>107.56005859375</v>
+        <v>85.669921875</v>
       </c>
       <c r="G9">
-        <v>71.60986328125</v>
+        <v>58.610107421875</v>
       </c>
       <c r="H9">
-        <v>94.8701171875</v>
+        <v>81.56982421875</v>
       </c>
       <c r="I9">
-        <v>74.0498046875</v>
+        <v>73.35009765625</v>
       </c>
       <c r="J9">
-        <v>90.8798828125</v>
+        <v>104.68017578125</v>
       </c>
       <c r="K9">
-        <v>47.570068359375</v>
+        <v>66.89013671875</v>
       </c>
       <c r="L9">
-        <v>69.25</v>
+        <v>90.4599609375</v>
       </c>
       <c r="M9">
-        <v>84</v>
+        <v>84.39990234375</v>
       </c>
       <c r="N9">
-        <v>101.990234375</v>
+        <v>108.58984375</v>
       </c>
       <c r="O9">
-        <v>55.97998046875</v>
+        <v>49.280029296875</v>
       </c>
       <c r="P9">
-        <v>57.300048828125</v>
+        <v>54.580078125</v>
       </c>
       <c r="Q9">
-        <v>72.47998046875</v>
+        <v>68.580078125</v>
       </c>
       <c r="R9">
-        <v>75.72021484375</v>
+        <v>70.81982421875</v>
+      </c>
+      <c r="S9">
+        <v>106.10009765625</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -1006,55 +1030,58 @@
         <v>27</v>
       </c>
       <c r="B10">
-        <v>50.260009765625</v>
+        <v>73.9599609375</v>
       </c>
       <c r="C10">
-        <v>57.550048828125</v>
+        <v>92.89990234375</v>
       </c>
       <c r="D10">
-        <v>70.83984375</v>
+        <v>81.759765625</v>
       </c>
       <c r="E10">
-        <v>27.4300537109375</v>
+        <v>53.25</v>
       </c>
       <c r="F10">
-        <v>39.340087890625</v>
+        <v>83.31982421875</v>
       </c>
       <c r="G10">
-        <v>71.66015625</v>
+        <v>54.81005859375</v>
       </c>
       <c r="H10">
-        <v>34.469970703125</v>
+        <v>79.919921875</v>
       </c>
       <c r="I10">
-        <v>40.280029296875</v>
+        <v>72.25</v>
       </c>
       <c r="J10">
-        <v>43.659912109375</v>
+        <v>59.3798828125</v>
       </c>
       <c r="K10">
-        <v>55.1201171875</v>
+        <v>66.27001953125</v>
       </c>
       <c r="L10">
-        <v>59.659912109375</v>
+        <v>105.9599609375</v>
       </c>
       <c r="M10">
-        <v>69.31982421875</v>
+        <v>77.25</v>
       </c>
       <c r="N10">
-        <v>57.9599609375</v>
+        <v>122.490234375</v>
       </c>
       <c r="O10">
-        <v>44.330078125</v>
+        <v>53.47998046875</v>
       </c>
       <c r="P10">
-        <v>31.43994140625</v>
+        <v>68.35009765625</v>
       </c>
       <c r="Q10">
-        <v>68.68994140625</v>
+        <v>74.27978515625</v>
       </c>
       <c r="R10">
-        <v>33.85009765625</v>
+        <v>71.6201171875</v>
+      </c>
+      <c r="S10">
+        <v>109.25</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -1062,55 +1089,58 @@
         <v>28</v>
       </c>
       <c r="B11">
-        <v>64.56005859375</v>
+        <v>84.259765625</v>
       </c>
       <c r="C11">
-        <v>86.60009765625</v>
+        <v>82.60986328125</v>
       </c>
       <c r="D11">
-        <v>70.35986328125</v>
+        <v>81.25</v>
       </c>
       <c r="E11">
-        <v>34.89990234375</v>
+        <v>45.64990234375</v>
       </c>
       <c r="F11">
-        <v>88.6201171875</v>
+        <v>72.27001953125</v>
       </c>
       <c r="G11">
-        <v>58.889892578125</v>
+        <v>53.4599609375</v>
       </c>
       <c r="H11">
-        <v>60.070068359375</v>
+        <v>58.669921875</v>
       </c>
       <c r="I11">
-        <v>79.85009765625</v>
+        <v>45.699951171875</v>
       </c>
       <c r="J11">
-        <v>101.9599609375</v>
+        <v>69.33984375</v>
       </c>
       <c r="K11">
-        <v>82.169921875</v>
+        <v>84.06982421875</v>
       </c>
       <c r="L11">
-        <v>101.35986328125</v>
+        <v>53.030029296875</v>
       </c>
       <c r="M11">
-        <v>64.2001953125</v>
+        <v>83.7001953125</v>
       </c>
       <c r="N11">
-        <v>121.08984375</v>
+        <v>90.14990234375</v>
       </c>
       <c r="O11">
-        <v>78.35009765625</v>
+        <v>49.43994140625</v>
       </c>
       <c r="P11">
-        <v>50.6298828125</v>
+        <v>53.5</v>
       </c>
       <c r="Q11">
-        <v>74.580078125</v>
+        <v>80.0400390625</v>
       </c>
       <c r="R11">
-        <v>84.919921875</v>
+        <v>61.449951171875</v>
+      </c>
+      <c r="S11">
+        <v>85.97998046875</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -1118,55 +1148,58 @@
         <v>29</v>
       </c>
       <c r="B12">
-        <v>60.159912109375</v>
+        <v>64.56005859375</v>
       </c>
       <c r="C12">
-        <v>64.580078125</v>
+        <v>105.5</v>
       </c>
       <c r="D12">
-        <v>88.759765625</v>
+        <v>81.16015625</v>
       </c>
       <c r="E12">
-        <v>109.75</v>
+        <v>66.75</v>
       </c>
       <c r="F12">
-        <v>81.47021484375</v>
+        <v>107.56005859375</v>
       </c>
       <c r="G12">
-        <v>56.39990234375</v>
+        <v>71.60986328125</v>
       </c>
       <c r="H12">
-        <v>59.56005859375</v>
+        <v>94.8701171875</v>
       </c>
       <c r="I12">
-        <v>75.0498046875</v>
+        <v>74.0498046875</v>
       </c>
       <c r="J12">
-        <v>96.27978515625</v>
+        <v>90.8798828125</v>
       </c>
       <c r="K12">
-        <v>78.89013671875</v>
+        <v>47.570068359375</v>
       </c>
       <c r="L12">
-        <v>86.66015625</v>
+        <v>69.25</v>
       </c>
       <c r="M12">
-        <v>80.7001953125</v>
+        <v>84</v>
       </c>
       <c r="N12">
-        <v>108.58984375</v>
+        <v>101.990234375</v>
       </c>
       <c r="O12">
-        <v>61.679931640625</v>
+        <v>55.97998046875</v>
       </c>
       <c r="P12">
-        <v>49.02001953125</v>
+        <v>57.300048828125</v>
       </c>
       <c r="Q12">
-        <v>69.77978515625</v>
+        <v>72.47998046875</v>
       </c>
       <c r="R12">
-        <v>93.22021484375</v>
+        <v>75.72021484375</v>
+      </c>
+      <c r="S12">
+        <v>54.93994140625</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -1174,55 +1207,58 @@
         <v>30</v>
       </c>
       <c r="B13">
-        <v>66.85986328125</v>
+        <v>50.260009765625</v>
       </c>
       <c r="C13">
-        <v>92.7001953125</v>
+        <v>57.550048828125</v>
       </c>
       <c r="D13">
-        <v>72.740234375</v>
+        <v>70.83984375</v>
       </c>
       <c r="E13">
-        <v>50.590087890625</v>
+        <v>27.4300537109375</v>
       </c>
       <c r="F13">
-        <v>81.169921875</v>
+        <v>39.340087890625</v>
       </c>
       <c r="G13">
-        <v>62.919921875</v>
+        <v>71.66015625</v>
       </c>
       <c r="H13">
-        <v>87.009765625</v>
+        <v>34.469970703125</v>
       </c>
       <c r="I13">
-        <v>69.89990234375</v>
+        <v>40.280029296875</v>
       </c>
       <c r="J13">
-        <v>91.14013671875</v>
+        <v>43.659912109375</v>
       </c>
       <c r="K13">
-        <v>47.8701171875</v>
+        <v>55.1201171875</v>
       </c>
       <c r="L13">
-        <v>83.47998046875</v>
+        <v>59.659912109375</v>
       </c>
       <c r="M13">
-        <v>63.800048828125</v>
+        <v>69.31982421875</v>
       </c>
       <c r="N13">
-        <v>110.35009765625</v>
+        <v>57.9599609375</v>
       </c>
       <c r="O13">
-        <v>51.080078125</v>
+        <v>44.330078125</v>
       </c>
       <c r="P13">
-        <v>65.60009765625</v>
+        <v>31.43994140625</v>
       </c>
       <c r="Q13">
-        <v>57.679931640625</v>
+        <v>68.68994140625</v>
       </c>
       <c r="R13">
-        <v>78.02001953125</v>
+        <v>33.85009765625</v>
+      </c>
+      <c r="S13">
+        <v>23.260009765625</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -1230,55 +1266,58 @@
         <v>31</v>
       </c>
       <c r="B14">
-        <v>58.9599609375</v>
+        <v>64.56005859375</v>
       </c>
       <c r="C14">
-        <v>79.27978515625</v>
+        <v>86.60009765625</v>
       </c>
       <c r="D14">
-        <v>86.66015625</v>
+        <v>70.35986328125</v>
       </c>
       <c r="E14">
-        <v>80.35986328125</v>
+        <v>34.89990234375</v>
       </c>
       <c r="F14">
-        <v>98.52001953125</v>
+        <v>88.6201171875</v>
       </c>
       <c r="G14">
-        <v>77.41015625</v>
+        <v>58.889892578125</v>
       </c>
       <c r="H14">
-        <v>71.3701171875</v>
+        <v>60.070068359375</v>
       </c>
       <c r="I14">
-        <v>80.75</v>
+        <v>79.85009765625</v>
       </c>
       <c r="J14">
-        <v>84.43994140625</v>
+        <v>101.9599609375</v>
       </c>
       <c r="K14">
-        <v>67.27001953125</v>
+        <v>82.169921875</v>
       </c>
       <c r="L14">
-        <v>94.06005859375</v>
+        <v>101.35986328125</v>
       </c>
       <c r="M14">
-        <v>84.5</v>
+        <v>64.2001953125</v>
       </c>
       <c r="N14">
-        <v>97.7900390625</v>
+        <v>121.08984375</v>
       </c>
       <c r="O14">
-        <v>62.050048828125</v>
+        <v>78.35009765625</v>
       </c>
       <c r="P14">
-        <v>58.27001953125</v>
+        <v>50.6298828125</v>
       </c>
       <c r="Q14">
-        <v>83.5</v>
+        <v>74.580078125</v>
       </c>
       <c r="R14">
-        <v>62.6201171875</v>
+        <v>84.919921875</v>
+      </c>
+      <c r="S14">
+        <v>122.75</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -1286,55 +1325,58 @@
         <v>32</v>
       </c>
       <c r="B15">
-        <v>68.06005859375</v>
+        <v>59.25</v>
       </c>
       <c r="C15">
-        <v>82.18017578125</v>
+        <v>73.77978515625</v>
       </c>
       <c r="D15">
-        <v>105.759765625</v>
+        <v>93.759765625</v>
       </c>
       <c r="E15">
-        <v>65.14990234375</v>
+        <v>51.929931640625</v>
       </c>
       <c r="F15">
-        <v>93.02001953125</v>
+        <v>74.77001953125</v>
       </c>
       <c r="G15">
-        <v>83</v>
+        <v>66.509765625</v>
       </c>
       <c r="H15">
-        <v>76.97021484375</v>
+        <v>82.56982421875</v>
       </c>
       <c r="I15">
-        <v>76.4501953125</v>
+        <v>76.25</v>
       </c>
       <c r="J15">
-        <v>85.85009765625</v>
+        <v>56.090087890625</v>
       </c>
       <c r="K15">
-        <v>58.090087890625</v>
+        <v>40.8701171875</v>
       </c>
       <c r="L15">
-        <v>88.759765625</v>
+        <v>82.4599609375</v>
       </c>
       <c r="M15">
-        <v>86.66015625</v>
+        <v>92.35009765625</v>
       </c>
       <c r="N15">
-        <v>106.39013671875</v>
+        <v>97.68994140625</v>
       </c>
       <c r="O15">
-        <v>53.780029296875</v>
+        <v>57.239990234375</v>
       </c>
       <c r="P15">
-        <v>63.75</v>
+        <v>65.33984375</v>
       </c>
       <c r="Q15">
-        <v>73.080078125</v>
+        <v>72.10009765625</v>
       </c>
       <c r="R15">
-        <v>65.6201171875</v>
+        <v>74.1201171875</v>
+      </c>
+      <c r="S15">
+        <v>99.830078125</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -1342,391 +1384,412 @@
         <v>33</v>
       </c>
       <c r="B16">
-        <v>51.260009765625</v>
+        <v>60.159912109375</v>
       </c>
       <c r="C16">
-        <v>95.5</v>
+        <v>64.580078125</v>
       </c>
       <c r="D16">
-        <v>61.159912109375</v>
+        <v>88.759765625</v>
       </c>
       <c r="E16">
-        <v>67.75</v>
+        <v>109.75</v>
       </c>
       <c r="F16">
-        <v>75.419921875</v>
+        <v>81.47021484375</v>
       </c>
       <c r="G16">
-        <v>54.2099609375</v>
+        <v>56.39990234375</v>
       </c>
       <c r="H16">
-        <v>56.669921875</v>
+        <v>59.56005859375</v>
       </c>
       <c r="I16">
-        <v>67.64990234375</v>
+        <v>75.0498046875</v>
       </c>
       <c r="J16">
-        <v>109.43994140625</v>
+        <v>96.27978515625</v>
       </c>
       <c r="K16">
-        <v>63.570068359375</v>
+        <v>78.89013671875</v>
       </c>
       <c r="L16">
-        <v>101.41015625</v>
+        <v>86.66015625</v>
       </c>
       <c r="M16">
-        <v>70.2998046875</v>
+        <v>80.7001953125</v>
       </c>
       <c r="N16">
-        <v>129.16015625</v>
+        <v>108.58984375</v>
       </c>
       <c r="O16">
-        <v>77.14990234375</v>
+        <v>61.679931640625</v>
       </c>
       <c r="P16">
-        <v>53.64990234375</v>
+        <v>49.02001953125</v>
       </c>
       <c r="Q16">
-        <v>61.800048828125</v>
+        <v>69.77978515625</v>
       </c>
       <c r="R16">
-        <v>45.610107421875</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18">
+        <v>93.22021484375</v>
+      </c>
+      <c r="S16">
+        <v>136.400390625</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19">
       <c r="A17" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B17">
-        <v>53.659912109375</v>
+        <v>61.659912109375</v>
       </c>
       <c r="C17">
-        <v>81.47998046875</v>
+        <v>69.5</v>
       </c>
       <c r="D17">
-        <v>79.259765625</v>
+        <v>83.64990234375</v>
       </c>
       <c r="E17">
-        <v>86.43017578125</v>
+        <v>51.72998046875</v>
       </c>
       <c r="F17">
-        <v>86.419921875</v>
+        <v>82.1298828125</v>
       </c>
       <c r="G17">
-        <v>47.389892578125</v>
+        <v>76.68994140625</v>
       </c>
       <c r="H17">
-        <v>67.27001953125</v>
+        <v>50.969970703125</v>
       </c>
       <c r="I17">
-        <v>75.75</v>
+        <v>74.85009765625</v>
       </c>
       <c r="J17">
-        <v>85.9599609375</v>
+        <v>90.0400390625</v>
       </c>
       <c r="K17">
-        <v>39.469970703125</v>
+        <v>38.3701171875</v>
       </c>
       <c r="L17">
-        <v>85.16015625</v>
+        <v>70.35986328125</v>
       </c>
       <c r="M17">
-        <v>81.4501953125</v>
+        <v>71.60009765625</v>
       </c>
       <c r="N17">
-        <v>113.2900390625</v>
+        <v>92.490234375</v>
       </c>
       <c r="O17">
-        <v>61.949951171875</v>
+        <v>49.9599609375</v>
       </c>
       <c r="P17">
-        <v>60.169921875</v>
+        <v>44.8798828125</v>
       </c>
       <c r="Q17">
-        <v>72.27978515625</v>
+        <v>76.68994140625</v>
       </c>
       <c r="R17">
-        <v>65.31982421875</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18">
+        <v>58.64990234375</v>
+      </c>
+      <c r="S17">
+        <v>117.14990234375</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19">
       <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B18">
-        <v>47.860107421875</v>
+        <v>66.85986328125</v>
       </c>
       <c r="C18">
-        <v>72.18017578125</v>
+        <v>92.7001953125</v>
       </c>
       <c r="D18">
-        <v>97.39990234375</v>
+        <v>72.740234375</v>
       </c>
       <c r="E18">
-        <v>81.64990234375</v>
+        <v>50.590087890625</v>
       </c>
       <c r="F18">
-        <v>84.81982421875</v>
+        <v>81.169921875</v>
       </c>
       <c r="G18">
-        <v>62.010009765625</v>
+        <v>62.919921875</v>
       </c>
       <c r="H18">
-        <v>77.06982421875</v>
+        <v>87.009765625</v>
       </c>
       <c r="I18">
-        <v>80.0498046875</v>
+        <v>69.89990234375</v>
       </c>
       <c r="J18">
-        <v>59.010009765625</v>
+        <v>91.14013671875</v>
       </c>
       <c r="K18">
-        <v>60.169921875</v>
+        <v>47.8701171875</v>
       </c>
       <c r="L18">
-        <v>82.81005859375</v>
+        <v>83.47998046875</v>
       </c>
       <c r="M18">
-        <v>77.35009765625</v>
+        <v>63.800048828125</v>
       </c>
       <c r="N18">
-        <v>115.43994140625</v>
+        <v>110.35009765625</v>
       </c>
       <c r="O18">
-        <v>57.72998046875</v>
+        <v>51.080078125</v>
       </c>
       <c r="P18">
-        <v>55.89990234375</v>
+        <v>65.60009765625</v>
       </c>
       <c r="Q18">
-        <v>103.39013671875</v>
+        <v>57.679931640625</v>
       </c>
       <c r="R18">
-        <v>60.1201171875</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18">
+        <v>78.02001953125</v>
+      </c>
+      <c r="S18">
+        <v>92.39990234375</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19">
       <c r="A19" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B19">
-        <v>73.9599609375</v>
+        <v>58.9599609375</v>
       </c>
       <c r="C19">
-        <v>92.89990234375</v>
+        <v>79.27978515625</v>
       </c>
       <c r="D19">
-        <v>81.759765625</v>
+        <v>86.66015625</v>
       </c>
       <c r="E19">
-        <v>53.25</v>
+        <v>80.35986328125</v>
       </c>
       <c r="F19">
-        <v>83.31982421875</v>
+        <v>98.52001953125</v>
       </c>
       <c r="G19">
-        <v>54.81005859375</v>
+        <v>77.41015625</v>
       </c>
       <c r="H19">
-        <v>79.919921875</v>
+        <v>71.3701171875</v>
       </c>
       <c r="I19">
-        <v>72.25</v>
+        <v>80.75</v>
       </c>
       <c r="J19">
-        <v>59.3798828125</v>
+        <v>84.43994140625</v>
       </c>
       <c r="K19">
-        <v>66.27001953125</v>
+        <v>67.27001953125</v>
       </c>
       <c r="L19">
-        <v>105.9599609375</v>
+        <v>94.06005859375</v>
       </c>
       <c r="M19">
-        <v>77.25</v>
+        <v>84.5</v>
       </c>
       <c r="N19">
-        <v>122.490234375</v>
+        <v>97.7900390625</v>
       </c>
       <c r="O19">
-        <v>53.47998046875</v>
+        <v>62.050048828125</v>
       </c>
       <c r="P19">
-        <v>68.35009765625</v>
+        <v>58.27001953125</v>
       </c>
       <c r="Q19">
-        <v>74.27978515625</v>
+        <v>83.5</v>
       </c>
       <c r="R19">
-        <v>71.6201171875</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18">
+        <v>62.6201171875</v>
+      </c>
+      <c r="S19">
+        <v>106.85009765625</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19">
       <c r="A20" s="1" t="s">
         <v>37</v>
       </c>
       <c r="B20">
-        <v>59.25</v>
+        <v>68.06005859375</v>
       </c>
       <c r="C20">
-        <v>73.77978515625</v>
+        <v>82.18017578125</v>
       </c>
       <c r="D20">
-        <v>93.759765625</v>
+        <v>105.759765625</v>
       </c>
       <c r="E20">
-        <v>51.929931640625</v>
+        <v>65.14990234375</v>
       </c>
       <c r="F20">
-        <v>74.77001953125</v>
+        <v>93.02001953125</v>
       </c>
       <c r="G20">
-        <v>66.509765625</v>
+        <v>83</v>
       </c>
       <c r="H20">
-        <v>82.56982421875</v>
+        <v>76.97021484375</v>
       </c>
       <c r="I20">
-        <v>76.25</v>
+        <v>76.4501953125</v>
       </c>
       <c r="J20">
-        <v>56.090087890625</v>
+        <v>85.85009765625</v>
       </c>
       <c r="K20">
-        <v>40.8701171875</v>
+        <v>58.090087890625</v>
       </c>
       <c r="L20">
-        <v>82.4599609375</v>
+        <v>88.759765625</v>
       </c>
       <c r="M20">
-        <v>92.35009765625</v>
+        <v>86.66015625</v>
       </c>
       <c r="N20">
-        <v>97.68994140625</v>
+        <v>106.39013671875</v>
       </c>
       <c r="O20">
-        <v>57.239990234375</v>
+        <v>53.780029296875</v>
       </c>
       <c r="P20">
-        <v>65.33984375</v>
+        <v>63.75</v>
       </c>
       <c r="Q20">
-        <v>72.10009765625</v>
+        <v>73.080078125</v>
       </c>
       <c r="R20">
-        <v>74.1201171875</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18">
+        <v>65.6201171875</v>
+      </c>
+      <c r="S20">
+        <v>111.64990234375</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19">
       <c r="A21" s="1" t="s">
         <v>38</v>
       </c>
       <c r="B21">
-        <v>61.659912109375</v>
+        <v>51.260009765625</v>
       </c>
       <c r="C21">
-        <v>69.5</v>
+        <v>95.5</v>
       </c>
       <c r="D21">
-        <v>83.64990234375</v>
+        <v>61.159912109375</v>
       </c>
       <c r="E21">
-        <v>51.72998046875</v>
+        <v>67.75</v>
       </c>
       <c r="F21">
-        <v>82.1298828125</v>
+        <v>75.419921875</v>
       </c>
       <c r="G21">
-        <v>76.68994140625</v>
+        <v>54.2099609375</v>
       </c>
       <c r="H21">
-        <v>50.969970703125</v>
+        <v>56.669921875</v>
       </c>
       <c r="I21">
-        <v>74.85009765625</v>
+        <v>67.64990234375</v>
       </c>
       <c r="J21">
-        <v>90.0400390625</v>
+        <v>109.43994140625</v>
       </c>
       <c r="K21">
-        <v>38.3701171875</v>
+        <v>63.570068359375</v>
       </c>
       <c r="L21">
-        <v>70.35986328125</v>
+        <v>101.41015625</v>
       </c>
       <c r="M21">
-        <v>71.60009765625</v>
+        <v>70.2998046875</v>
       </c>
       <c r="N21">
-        <v>92.490234375</v>
+        <v>129.16015625</v>
       </c>
       <c r="O21">
-        <v>49.9599609375</v>
+        <v>77.14990234375</v>
       </c>
       <c r="P21">
-        <v>44.8798828125</v>
+        <v>53.64990234375</v>
       </c>
       <c r="Q21">
-        <v>76.68994140625</v>
+        <v>61.800048828125</v>
       </c>
       <c r="R21">
-        <v>58.64990234375</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18">
+        <v>45.610107421875</v>
+      </c>
+      <c r="S21">
+        <v>85.2099609375</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19">
       <c r="A22" s="1" t="s">
         <v>39</v>
       </c>
       <c r="B22" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C22" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D22" t="s">
         <v>20</v>
       </c>
       <c r="E22" t="s">
+        <v>33</v>
+      </c>
+      <c r="F22" t="s">
         <v>29</v>
-      </c>
-      <c r="F22" t="s">
-        <v>26</v>
       </c>
       <c r="G22" t="s">
         <v>20</v>
       </c>
       <c r="H22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I22" t="s">
+        <v>36</v>
+      </c>
+      <c r="J22" t="s">
+        <v>38</v>
+      </c>
+      <c r="K22" t="s">
+        <v>28</v>
+      </c>
+      <c r="L22" t="s">
+        <v>27</v>
+      </c>
+      <c r="M22" t="s">
+        <v>32</v>
+      </c>
+      <c r="N22" t="s">
+        <v>23</v>
+      </c>
+      <c r="O22" t="s">
         <v>31</v>
       </c>
-      <c r="J22" t="s">
+      <c r="P22" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>25</v>
+      </c>
+      <c r="R22" t="s">
         <v>33</v>
       </c>
-      <c r="K22" t="s">
-        <v>25</v>
-      </c>
-      <c r="L22" t="s">
-        <v>36</v>
-      </c>
-      <c r="M22" t="s">
-        <v>37</v>
-      </c>
-      <c r="N22" t="s">
-        <v>22</v>
-      </c>
-      <c r="O22" t="s">
-        <v>28</v>
-      </c>
-      <c r="P22" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>35</v>
-      </c>
-      <c r="R22" t="s">
-        <v>29</v>
+      <c r="S22" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
